--- a/output/2024-10-27.xlsx
+++ b/output/2024-10-27.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="F14" t="n">
-        <v>4.43</v>
+        <v>4.33</v>
       </c>
       <c r="G14" t="n">
-        <v>183.2</v>
+        <v>217.8</v>
       </c>
       <c r="H14" t="n">
-        <v>70.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="I14" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>90.25</v>
+        <v>-23.99</v>
       </c>
       <c r="K14" t="n">
-        <v>-36.1</v>
+        <v>85.40000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>97.20999999999999</v>
+        <v>88.70999999999999</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08:13:51</t>
+          <t>08:13:27</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2</v>
+        <v>1.29</v>
       </c>
       <c r="F15" t="n">
-        <v>4.57</v>
+        <v>4.2</v>
       </c>
       <c r="G15" t="n">
-        <v>229.3</v>
+        <v>201.6</v>
       </c>
       <c r="H15" t="n">
-        <v>77.7</v>
+        <v>75.8</v>
       </c>
       <c r="I15" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>25.42</v>
+        <v>36.74</v>
       </c>
       <c r="K15" t="n">
-        <v>-73.02</v>
+        <v>3.38</v>
       </c>
       <c r="L15" t="n">
-        <v>77.31999999999999</v>
+        <v>36.89</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08:15:35</t>
+          <t>08:15:57</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.52</v>
+        <v>1.19</v>
       </c>
       <c r="F16" t="n">
-        <v>4.1</v>
+        <v>4.66</v>
       </c>
       <c r="G16" t="n">
-        <v>216.5</v>
+        <v>219.1</v>
       </c>
       <c r="H16" t="n">
-        <v>76.5</v>
+        <v>70.8</v>
       </c>
       <c r="I16" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>9.710000000000001</v>
+        <v>4.68</v>
       </c>
       <c r="K16" t="n">
-        <v>-63.55</v>
+        <v>62.35</v>
       </c>
       <c r="L16" t="n">
-        <v>64.29000000000001</v>
+        <v>62.52</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08:20:55</t>
+          <t>08:20:57</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="F17" t="n">
-        <v>4.77</v>
+        <v>4.84</v>
       </c>
       <c r="G17" t="n">
-        <v>194.2</v>
+        <v>220.6</v>
       </c>
       <c r="H17" t="n">
-        <v>72.5</v>
+        <v>71.7</v>
       </c>
       <c r="I17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>17.3</v>
+        <v>-45.29</v>
       </c>
       <c r="K17" t="n">
-        <v>-31.92</v>
+        <v>22.29</v>
       </c>
       <c r="L17" t="n">
-        <v>36.31</v>
+        <v>50.47</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08:21:52</t>
+          <t>08:22:03</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.39</v>
+        <v>1.33</v>
       </c>
       <c r="F18" t="n">
-        <v>4.34</v>
+        <v>4.16</v>
       </c>
       <c r="G18" t="n">
-        <v>217.6</v>
+        <v>199.2</v>
       </c>
       <c r="H18" t="n">
-        <v>72.3</v>
+        <v>75.8</v>
       </c>
       <c r="I18" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>21.71</v>
+        <v>-110.72</v>
       </c>
       <c r="K18" t="n">
-        <v>-15.31</v>
+        <v>51.94</v>
       </c>
       <c r="L18" t="n">
-        <v>26.56</v>
+        <v>122.3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08:23:59</t>
+          <t>08:24:39</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="F19" t="n">
-        <v>4.21</v>
+        <v>4.32</v>
       </c>
       <c r="G19" t="n">
-        <v>222</v>
+        <v>200.2</v>
       </c>
       <c r="H19" t="n">
-        <v>64</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>-46.56</v>
+        <v>72.73999999999999</v>
       </c>
       <c r="K19" t="n">
-        <v>64.39</v>
+        <v>5.1</v>
       </c>
       <c r="L19" t="n">
-        <v>79.45999999999999</v>
+        <v>72.91</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08:27:49</t>
+          <t>08:30:04</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.33</v>
+        <v>1.67</v>
       </c>
       <c r="F20" t="n">
-        <v>4.03</v>
+        <v>4.51</v>
       </c>
       <c r="G20" t="n">
-        <v>216.2</v>
+        <v>198.8</v>
       </c>
       <c r="H20" t="n">
-        <v>77.3</v>
+        <v>69.8</v>
       </c>
       <c r="I20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>234.88</v>
+        <v>83.42</v>
       </c>
       <c r="K20" t="n">
-        <v>-36.09</v>
+        <v>122.89</v>
       </c>
       <c r="L20" t="n">
-        <v>237.64</v>
+        <v>148.53</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08:29:07</t>
+          <t>08:31:52</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.33</v>
+        <v>1.51</v>
       </c>
       <c r="F21" t="n">
-        <v>4.51</v>
+        <v>4.24</v>
       </c>
       <c r="G21" t="n">
-        <v>208.5</v>
+        <v>202.5</v>
       </c>
       <c r="H21" t="n">
-        <v>66.8</v>
+        <v>75</v>
       </c>
       <c r="I21" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>43.16</v>
+        <v>-95.7</v>
       </c>
       <c r="K21" t="n">
-        <v>21.46</v>
+        <v>37.26</v>
       </c>
       <c r="L21" t="n">
-        <v>48.2</v>
+        <v>102.7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08:31:43</t>
+          <t>08:33:26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>2.06</v>
+        <v>1.58</v>
       </c>
       <c r="F22" t="n">
-        <v>4.49</v>
+        <v>4.08</v>
       </c>
       <c r="G22" t="n">
-        <v>212</v>
+        <v>209.3</v>
       </c>
       <c r="H22" t="n">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="I22" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>20.48</v>
+        <v>-210.45</v>
       </c>
       <c r="K22" t="n">
-        <v>-202.43</v>
+        <v>29.37</v>
       </c>
       <c r="L22" t="n">
-        <v>203.47</v>
+        <v>212.49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08:35:58</t>
+          <t>08:37:25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.68</v>
+        <v>1.49</v>
       </c>
       <c r="F23" t="n">
-        <v>5.11</v>
+        <v>4.66</v>
       </c>
       <c r="G23" t="n">
-        <v>192.2</v>
+        <v>218.1</v>
       </c>
       <c r="H23" t="n">
-        <v>75.40000000000001</v>
+        <v>74</v>
       </c>
       <c r="I23" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>97.86</v>
+        <v>310.27</v>
       </c>
       <c r="K23" t="n">
-        <v>397.43</v>
+        <v>409.2</v>
       </c>
       <c r="L23" t="n">
-        <v>409.3</v>
+        <v>513.53</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08:37:52</t>
+          <t>08:39:34</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="F24" t="n">
-        <v>4.5</v>
+        <v>4.64</v>
       </c>
       <c r="G24" t="n">
-        <v>219.1</v>
+        <v>200.1</v>
       </c>
       <c r="H24" t="n">
-        <v>73</v>
+        <v>76.5</v>
       </c>
       <c r="I24" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>-63.56</v>
+        <v>59.2</v>
       </c>
       <c r="K24" t="n">
-        <v>-165.96</v>
+        <v>-103.72</v>
       </c>
       <c r="L24" t="n">
-        <v>177.72</v>
+        <v>119.43</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08:39:51</t>
+          <t>08:40:32</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="F25" t="n">
-        <v>4.4</v>
+        <v>4.44</v>
       </c>
       <c r="G25" t="n">
-        <v>190.2</v>
+        <v>212.8</v>
       </c>
       <c r="H25" t="n">
-        <v>76.90000000000001</v>
+        <v>77.5</v>
       </c>
       <c r="I25" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>293.3</v>
+        <v>-136.17</v>
       </c>
       <c r="K25" t="n">
-        <v>271.59</v>
+        <v>-51.9</v>
       </c>
       <c r="L25" t="n">
-        <v>399.73</v>
+        <v>145.73</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08:45:46</t>
+          <t>08:45:28</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.36</v>
+        <v>1.26</v>
       </c>
       <c r="F26" t="n">
-        <v>3.97</v>
+        <v>4.32</v>
       </c>
       <c r="G26" t="n">
-        <v>217.7</v>
+        <v>207.8</v>
       </c>
       <c r="H26" t="n">
-        <v>76.8</v>
+        <v>69.8</v>
       </c>
       <c r="I26" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>-521.86</v>
+        <v>496.24</v>
       </c>
       <c r="K26" t="n">
-        <v>-237.14</v>
+        <v>153.9</v>
       </c>
       <c r="L26" t="n">
-        <v>573.21</v>
+        <v>519.5599999999999</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08:48:10</t>
+          <t>08:46:56</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.48</v>
+        <v>1.39</v>
       </c>
       <c r="F27" t="n">
-        <v>4.04</v>
+        <v>4.62</v>
       </c>
       <c r="G27" t="n">
-        <v>208.6</v>
+        <v>200.3</v>
       </c>
       <c r="H27" t="n">
-        <v>73.2</v>
+        <v>65.40000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-223.64</v>
+        <v>-279.83</v>
       </c>
       <c r="K27" t="n">
-        <v>-78.61</v>
+        <v>-192.19</v>
       </c>
       <c r="L27" t="n">
-        <v>237.05</v>
+        <v>339.47</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08:50:45</t>
+          <t>08:48:53</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.47</v>
+        <v>1.25</v>
       </c>
       <c r="F28" t="n">
-        <v>4.03</v>
+        <v>5.01</v>
       </c>
       <c r="G28" t="n">
-        <v>197.1</v>
+        <v>206.3</v>
       </c>
       <c r="H28" t="n">
-        <v>73.2</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>-22.13</v>
+        <v>144.37</v>
       </c>
       <c r="K28" t="n">
-        <v>303.62</v>
+        <v>53.51</v>
       </c>
       <c r="L28" t="n">
-        <v>304.42</v>
+        <v>153.97</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09:01:13</t>
+          <t>08:58:58</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.69</v>
+        <v>2.48</v>
       </c>
       <c r="F29" t="n">
-        <v>4.36</v>
+        <v>4.26</v>
       </c>
       <c r="G29" t="n">
-        <v>202.8</v>
+        <v>213.3</v>
       </c>
       <c r="H29" t="n">
-        <v>71.59999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="I29" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>-26.43</v>
+        <v>61.46</v>
       </c>
       <c r="K29" t="n">
-        <v>-72.59999999999999</v>
+        <v>81.43000000000001</v>
       </c>
       <c r="L29" t="n">
-        <v>77.26000000000001</v>
+        <v>102.02</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09:03:13</t>
+          <t>09:00:07</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.79</v>
+        <v>1.38</v>
       </c>
       <c r="F30" t="n">
-        <v>3.97</v>
+        <v>4.2</v>
       </c>
       <c r="G30" t="n">
-        <v>198.5</v>
+        <v>193</v>
       </c>
       <c r="H30" t="n">
-        <v>73.7</v>
+        <v>68.2</v>
       </c>
       <c r="I30" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>24.54</v>
+        <v>-31.79</v>
       </c>
       <c r="K30" t="n">
-        <v>-65.14</v>
+        <v>78.31</v>
       </c>
       <c r="L30" t="n">
-        <v>69.61</v>
+        <v>84.52</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09:05:30</t>
+          <t>09:01:56</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.49</v>
+        <v>1.42</v>
       </c>
       <c r="F31" t="n">
-        <v>4.76</v>
+        <v>4.25</v>
       </c>
       <c r="G31" t="n">
-        <v>205.6</v>
+        <v>199.7</v>
       </c>
       <c r="H31" t="n">
-        <v>73.3</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I31" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>-127.83</v>
+        <v>-34.72</v>
       </c>
       <c r="K31" t="n">
-        <v>-37.9</v>
+        <v>1.55</v>
       </c>
       <c r="L31" t="n">
-        <v>133.33</v>
+        <v>34.76</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09:09:42</t>
+          <t>09:05:49</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.39</v>
+        <v>1.44</v>
       </c>
       <c r="F32" t="n">
-        <v>4.15</v>
+        <v>4.37</v>
       </c>
       <c r="G32" t="n">
-        <v>205.7</v>
+        <v>211.8</v>
       </c>
       <c r="H32" t="n">
-        <v>73.3</v>
+        <v>73.7</v>
       </c>
       <c r="I32" t="n">
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>-95.25</v>
+        <v>-33.41</v>
       </c>
       <c r="K32" t="n">
-        <v>136.88</v>
+        <v>-33.72</v>
       </c>
       <c r="L32" t="n">
-        <v>166.76</v>
+        <v>47.47</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09:11:22</t>
+          <t>09:08:02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="F33" t="n">
-        <v>4.16</v>
+        <v>4.91</v>
       </c>
       <c r="G33" t="n">
-        <v>206.8</v>
+        <v>199.6</v>
       </c>
       <c r="H33" t="n">
-        <v>75.90000000000001</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="I33" t="n">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>128.48</v>
+        <v>104.02</v>
       </c>
       <c r="K33" t="n">
-        <v>-103.76</v>
+        <v>52.19</v>
       </c>
       <c r="L33" t="n">
-        <v>165.14</v>
+        <v>116.38</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09:13:31</t>
+          <t>09:09:13</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.41</v>
+        <v>2.41</v>
       </c>
       <c r="F34" t="n">
-        <v>3.77</v>
+        <v>4.23</v>
       </c>
       <c r="G34" t="n">
-        <v>214.6</v>
+        <v>207.5</v>
       </c>
       <c r="H34" t="n">
-        <v>75.8</v>
+        <v>70.8</v>
       </c>
       <c r="I34" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>74.59</v>
+        <v>-160.72</v>
       </c>
       <c r="K34" t="n">
-        <v>8.460000000000001</v>
+        <v>-0.41</v>
       </c>
       <c r="L34" t="n">
-        <v>75.06999999999999</v>
+        <v>160.72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09:17:13</t>
+          <t>09:13:17</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.52</v>
+        <v>1.65</v>
       </c>
       <c r="F35" t="n">
-        <v>3.77</v>
+        <v>4.27</v>
       </c>
       <c r="G35" t="n">
-        <v>218.3</v>
+        <v>202.8</v>
       </c>
       <c r="H35" t="n">
-        <v>70.3</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>17</v>
+        <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>146.19</v>
+        <v>-48.18</v>
       </c>
       <c r="K35" t="n">
-        <v>-264.63</v>
+        <v>201.09</v>
       </c>
       <c r="L35" t="n">
-        <v>302.33</v>
+        <v>206.78</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09:18:10</t>
+          <t>09:15:19</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="F36" t="n">
-        <v>4.36</v>
+        <v>4.63</v>
       </c>
       <c r="G36" t="n">
-        <v>195.9</v>
+        <v>210.5</v>
       </c>
       <c r="H36" t="n">
-        <v>72.59999999999999</v>
+        <v>77.2</v>
       </c>
       <c r="I36" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>6.51</v>
+        <v>-123.68</v>
       </c>
       <c r="K36" t="n">
-        <v>130.84</v>
+        <v>-25.82</v>
       </c>
       <c r="L36" t="n">
-        <v>131</v>
+        <v>126.34</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09:20:13</t>
+          <t>09:16:41</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.68</v>
+        <v>1.56</v>
       </c>
       <c r="F37" t="n">
-        <v>4.42</v>
+        <v>4.3</v>
       </c>
       <c r="G37" t="n">
-        <v>199.6</v>
+        <v>210.8</v>
       </c>
       <c r="H37" t="n">
-        <v>73.59999999999999</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>234.42</v>
+        <v>16.98</v>
       </c>
       <c r="K37" t="n">
-        <v>33.14</v>
+        <v>-59.23</v>
       </c>
       <c r="L37" t="n">
-        <v>236.75</v>
+        <v>61.62</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09:26:18</t>
+          <t>09:21:53</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.7</v>
+        <v>1.57</v>
       </c>
       <c r="F38" t="n">
-        <v>4.69</v>
+        <v>3.91</v>
       </c>
       <c r="G38" t="n">
-        <v>193.9</v>
+        <v>194.3</v>
       </c>
       <c r="H38" t="n">
-        <v>70.5</v>
+        <v>75.7</v>
       </c>
       <c r="I38" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>262.54</v>
+        <v>-128.95</v>
       </c>
       <c r="K38" t="n">
-        <v>-51.99</v>
+        <v>-95.29000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>267.64</v>
+        <v>160.34</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09:27:46</t>
+          <t>09:23:52</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.48</v>
+        <v>1.62</v>
       </c>
       <c r="F39" t="n">
-        <v>4.33</v>
+        <v>4.29</v>
       </c>
       <c r="G39" t="n">
-        <v>196.1</v>
+        <v>210</v>
       </c>
       <c r="H39" t="n">
-        <v>75.90000000000001</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>300.93</v>
+        <v>-131.98</v>
       </c>
       <c r="K39" t="n">
-        <v>215</v>
+        <v>0.18</v>
       </c>
       <c r="L39" t="n">
-        <v>369.84</v>
+        <v>131.98</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09:29:56</t>
+          <t>09:26:13</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.91</v>
+        <v>1.35</v>
       </c>
       <c r="F40" t="n">
-        <v>4.07</v>
+        <v>4.33</v>
       </c>
       <c r="G40" t="n">
-        <v>203.4</v>
+        <v>199.5</v>
       </c>
       <c r="H40" t="n">
-        <v>71.8</v>
+        <v>68.3</v>
       </c>
       <c r="I40" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-203.41</v>
+        <v>-57.57</v>
       </c>
       <c r="K40" t="n">
-        <v>403.37</v>
+        <v>-69.55</v>
       </c>
       <c r="L40" t="n">
-        <v>451.75</v>
+        <v>90.29000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09:35:27</t>
+          <t>09:30:10</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.46</v>
+        <v>1.75</v>
       </c>
       <c r="F41" t="n">
-        <v>3.83</v>
+        <v>4.51</v>
       </c>
       <c r="G41" t="n">
-        <v>218.1</v>
+        <v>206.8</v>
       </c>
       <c r="H41" t="n">
-        <v>78.2</v>
+        <v>70.3</v>
       </c>
       <c r="I41" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>-106.41</v>
+        <v>225.22</v>
       </c>
       <c r="K41" t="n">
-        <v>408.34</v>
+        <v>-46.03</v>
       </c>
       <c r="L41" t="n">
-        <v>421.98</v>
+        <v>229.88</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09:37:12</t>
+          <t>09:32:19</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.55</v>
+        <v>1.45</v>
       </c>
       <c r="F42" t="n">
-        <v>4.29</v>
+        <v>4.47</v>
       </c>
       <c r="G42" t="n">
-        <v>205.1</v>
+        <v>207.9</v>
       </c>
       <c r="H42" t="n">
-        <v>78.7</v>
+        <v>62.6</v>
       </c>
       <c r="I42" t="n">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>209.14</v>
+        <v>-363.9</v>
       </c>
       <c r="K42" t="n">
-        <v>-268.6</v>
+        <v>-103.81</v>
       </c>
       <c r="L42" t="n">
-        <v>340.42</v>
+        <v>378.42</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09:39:28</t>
+          <t>09:32:57</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.75</v>
+        <v>1.32</v>
       </c>
       <c r="F43" t="n">
-        <v>3.5</v>
+        <v>4.09</v>
       </c>
       <c r="G43" t="n">
-        <v>210.8</v>
+        <v>217</v>
       </c>
       <c r="H43" t="n">
-        <v>75.7</v>
+        <v>77</v>
       </c>
       <c r="I43" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-4.11</v>
+        <v>-66.73999999999999</v>
       </c>
       <c r="K43" t="n">
-        <v>252.43</v>
+        <v>142.23</v>
       </c>
       <c r="L43" t="n">
-        <v>252.46</v>
+        <v>157.11</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09:51:22</t>
+          <t>09:46:02</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="F44" t="n">
-        <v>4.46</v>
+        <v>4.56</v>
       </c>
       <c r="G44" t="n">
-        <v>209.6</v>
+        <v>197.7</v>
       </c>
       <c r="H44" t="n">
-        <v>73.8</v>
+        <v>78</v>
       </c>
       <c r="I44" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>-36.26</v>
+        <v>60.09</v>
       </c>
       <c r="K44" t="n">
-        <v>36.01</v>
+        <v>-77.63</v>
       </c>
       <c r="L44" t="n">
-        <v>51.1</v>
+        <v>98.17</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09:53:16</t>
+          <t>09:48:03</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.72</v>
+        <v>2.28</v>
       </c>
       <c r="F45" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="G45" t="n">
-        <v>210.8</v>
+        <v>197</v>
       </c>
       <c r="H45" t="n">
-        <v>74.40000000000001</v>
+        <v>79.40000000000001</v>
       </c>
       <c r="I45" t="n">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>-26.57</v>
+        <v>59.53</v>
       </c>
       <c r="K45" t="n">
-        <v>105.02</v>
+        <v>52.01</v>
       </c>
       <c r="L45" t="n">
-        <v>108.33</v>
+        <v>79.05</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09:55:10</t>
+          <t>09:50:42</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.61</v>
+        <v>2</v>
       </c>
       <c r="F46" t="n">
-        <v>4.21</v>
+        <v>4.17</v>
       </c>
       <c r="G46" t="n">
-        <v>218.7</v>
+        <v>209.4</v>
       </c>
       <c r="H46" t="n">
-        <v>71.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="I46" t="n">
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>79.87</v>
+        <v>20.75</v>
       </c>
       <c r="K46" t="n">
-        <v>-62.77</v>
+        <v>-152.55</v>
       </c>
       <c r="L46" t="n">
-        <v>101.58</v>
+        <v>153.96</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:59:18</t>
+          <t>09:54:47</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="F47" t="n">
-        <v>4.69</v>
+        <v>4.41</v>
       </c>
       <c r="G47" t="n">
-        <v>213.2</v>
+        <v>201.3</v>
       </c>
       <c r="H47" t="n">
-        <v>75.7</v>
+        <v>73.2</v>
       </c>
       <c r="I47" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>-66.47</v>
+        <v>-10.94</v>
       </c>
       <c r="K47" t="n">
-        <v>-25.27</v>
+        <v>-103.07</v>
       </c>
       <c r="L47" t="n">
-        <v>71.12</v>
+        <v>103.65</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>10:00:56</t>
+          <t>09:56:45</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="F48" t="n">
-        <v>3.67</v>
+        <v>4.03</v>
       </c>
       <c r="G48" t="n">
-        <v>210.9</v>
+        <v>213.3</v>
       </c>
       <c r="H48" t="n">
-        <v>69.7</v>
+        <v>72.8</v>
       </c>
       <c r="I48" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>83.31999999999999</v>
+        <v>52.27</v>
       </c>
       <c r="K48" t="n">
-        <v>70.22</v>
+        <v>-28.08</v>
       </c>
       <c r="L48" t="n">
-        <v>108.96</v>
+        <v>59.33</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>10:02:52</t>
+          <t>09:58:28</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="F49" t="n">
-        <v>3.79</v>
+        <v>3.97</v>
       </c>
       <c r="G49" t="n">
-        <v>208.7</v>
+        <v>199.9</v>
       </c>
       <c r="H49" t="n">
-        <v>74.59999999999999</v>
+        <v>70.3</v>
       </c>
       <c r="I49" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-29.12</v>
+        <v>-103.13</v>
       </c>
       <c r="K49" t="n">
-        <v>-63.32</v>
+        <v>-32.7</v>
       </c>
       <c r="L49" t="n">
-        <v>69.7</v>
+        <v>108.19</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10:08:23</t>
+          <t>10:03:11</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="F50" t="n">
-        <v>4.07</v>
+        <v>4.15</v>
       </c>
       <c r="G50" t="n">
-        <v>214.4</v>
+        <v>193.9</v>
       </c>
       <c r="H50" t="n">
-        <v>69.40000000000001</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I50" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>-111.49</v>
+        <v>38.77</v>
       </c>
       <c r="K50" t="n">
-        <v>-49.43</v>
+        <v>-144.03</v>
       </c>
       <c r="L50" t="n">
-        <v>121.96</v>
+        <v>149.15</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10:10:07</t>
+          <t>10:04:20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.33</v>
+        <v>1.85</v>
       </c>
       <c r="F51" t="n">
-        <v>4.94</v>
+        <v>4.32</v>
       </c>
       <c r="G51" t="n">
-        <v>212.3</v>
+        <v>209.9</v>
       </c>
       <c r="H51" t="n">
-        <v>77.3</v>
+        <v>77.2</v>
       </c>
       <c r="I51" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>309.18</v>
+        <v>301.8</v>
       </c>
       <c r="K51" t="n">
-        <v>-171</v>
+        <v>-30.42</v>
       </c>
       <c r="L51" t="n">
-        <v>353.32</v>
+        <v>303.33</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10:11:28</t>
+          <t>10:06:20</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>1.32</v>
+        <v>2.49</v>
       </c>
       <c r="F52" t="n">
-        <v>3.76</v>
+        <v>3.66</v>
       </c>
       <c r="G52" t="n">
-        <v>192.4</v>
+        <v>209.4</v>
       </c>
       <c r="H52" t="n">
-        <v>76.09999999999999</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I52" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>290.17</v>
+        <v>47.84</v>
       </c>
       <c r="K52" t="n">
-        <v>318.49</v>
+        <v>-123.77</v>
       </c>
       <c r="L52" t="n">
-        <v>430.86</v>
+        <v>132.69</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10:16:13</t>
+          <t>10:10:06</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.6</v>
+        <v>1.48</v>
       </c>
       <c r="F53" t="n">
-        <v>3.2</v>
+        <v>3.97</v>
       </c>
       <c r="G53" t="n">
-        <v>189.6</v>
+        <v>213.6</v>
       </c>
       <c r="H53" t="n">
-        <v>71.5</v>
+        <v>75.3</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>169.21</v>
+        <v>89.37</v>
       </c>
       <c r="K53" t="n">
-        <v>180.03</v>
+        <v>-217.15</v>
       </c>
       <c r="L53" t="n">
-        <v>247.07</v>
+        <v>234.82</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10:18:47</t>
+          <t>10:12:48</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.78</v>
+        <v>1.61</v>
       </c>
       <c r="F54" t="n">
-        <v>4.2</v>
+        <v>4.32</v>
       </c>
       <c r="G54" t="n">
-        <v>207.1</v>
+        <v>210</v>
       </c>
       <c r="H54" t="n">
-        <v>74.8</v>
+        <v>73.5</v>
       </c>
       <c r="I54" t="n">
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-77.44</v>
+        <v>-209.86</v>
       </c>
       <c r="K54" t="n">
-        <v>-113.67</v>
+        <v>-24.64</v>
       </c>
       <c r="L54" t="n">
-        <v>137.54</v>
+        <v>211.3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10:19:57</t>
+          <t>10:14:02</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.41</v>
+        <v>1.76</v>
       </c>
       <c r="F55" t="n">
-        <v>4.15</v>
+        <v>4.12</v>
       </c>
       <c r="G55" t="n">
-        <v>215.7</v>
+        <v>203.9</v>
       </c>
       <c r="H55" t="n">
-        <v>70.90000000000001</v>
+        <v>72.2</v>
       </c>
       <c r="I55" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>225.2</v>
+        <v>168.66</v>
       </c>
       <c r="K55" t="n">
-        <v>216.59</v>
+        <v>360.4</v>
       </c>
       <c r="L55" t="n">
-        <v>312.45</v>
+        <v>397.91</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10:23:49</t>
+          <t>10:18:34</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2392,31 +2392,31 @@
         <v>1.47</v>
       </c>
       <c r="F56" t="n">
-        <v>4.33</v>
+        <v>3.89</v>
       </c>
       <c r="G56" t="n">
-        <v>222.1</v>
+        <v>204.8</v>
       </c>
       <c r="H56" t="n">
-        <v>77.8</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>130.99</v>
+        <v>478.53</v>
       </c>
       <c r="K56" t="n">
-        <v>-146.46</v>
+        <v>46.57</v>
       </c>
       <c r="L56" t="n">
-        <v>196.49</v>
+        <v>480.79</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10:24:55</t>
+          <t>10:20:22</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.63</v>
+        <v>1.48</v>
       </c>
       <c r="F57" t="n">
-        <v>4.37</v>
+        <v>4.02</v>
       </c>
       <c r="G57" t="n">
-        <v>212.7</v>
+        <v>212.9</v>
       </c>
       <c r="H57" t="n">
-        <v>71.2</v>
+        <v>73.8</v>
       </c>
       <c r="I57" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>186.54</v>
+        <v>71.14</v>
       </c>
       <c r="K57" t="n">
-        <v>271.04</v>
+        <v>-168.69</v>
       </c>
       <c r="L57" t="n">
-        <v>329.03</v>
+        <v>183.07</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10:26:38</t>
+          <t>10:22:05</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="F58" t="n">
-        <v>5.04</v>
+        <v>4.67</v>
       </c>
       <c r="G58" t="n">
-        <v>214.7</v>
+        <v>204.1</v>
       </c>
       <c r="H58" t="n">
-        <v>70.40000000000001</v>
+        <v>75.3</v>
       </c>
       <c r="I58" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-11.94</v>
+        <v>-80.23999999999999</v>
       </c>
       <c r="K58" t="n">
-        <v>301.71</v>
+        <v>-156.92</v>
       </c>
       <c r="L58" t="n">
-        <v>301.94</v>
+        <v>176.25</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10:34:43</t>
+          <t>10:33:16</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="F59" t="n">
-        <v>4.07</v>
+        <v>4.11</v>
       </c>
       <c r="G59" t="n">
-        <v>201.5</v>
+        <v>213.1</v>
       </c>
       <c r="H59" t="n">
-        <v>68.90000000000001</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="I59" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>-66.75</v>
+        <v>-12.57</v>
       </c>
       <c r="K59" t="n">
-        <v>-48.31</v>
+        <v>-40.21</v>
       </c>
       <c r="L59" t="n">
-        <v>82.39</v>
+        <v>42.12</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10:35:59</t>
+          <t>10:35:12</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="F60" t="n">
-        <v>3.83</v>
+        <v>4.22</v>
       </c>
       <c r="G60" t="n">
-        <v>218.3</v>
+        <v>204.1</v>
       </c>
       <c r="H60" t="n">
-        <v>76.40000000000001</v>
+        <v>71.8</v>
       </c>
       <c r="I60" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>116.08</v>
+        <v>2.67</v>
       </c>
       <c r="K60" t="n">
-        <v>-12.07</v>
+        <v>85.02</v>
       </c>
       <c r="L60" t="n">
-        <v>116.7</v>
+        <v>85.06</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10:37:28</t>
+          <t>10:36:29</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="F61" t="n">
-        <v>4.49</v>
+        <v>4.68</v>
       </c>
       <c r="G61" t="n">
-        <v>207.8</v>
+        <v>196.2</v>
       </c>
       <c r="H61" t="n">
-        <v>75.5</v>
+        <v>71.7</v>
       </c>
       <c r="I61" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>-29.73</v>
+        <v>53.13</v>
       </c>
       <c r="K61" t="n">
-        <v>73.2</v>
+        <v>82.56</v>
       </c>
       <c r="L61" t="n">
-        <v>79</v>
+        <v>98.18000000000001</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10:43:05</t>
+          <t>10:39:46</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="F62" t="n">
-        <v>4.82</v>
+        <v>4.51</v>
       </c>
       <c r="G62" t="n">
-        <v>203.9</v>
+        <v>208.9</v>
       </c>
       <c r="H62" t="n">
-        <v>74.8</v>
+        <v>79</v>
       </c>
       <c r="I62" t="n">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>9.050000000000001</v>
+        <v>70.29000000000001</v>
       </c>
       <c r="K62" t="n">
-        <v>-149.09</v>
+        <v>31.22</v>
       </c>
       <c r="L62" t="n">
-        <v>149.36</v>
+        <v>76.91</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10:44:28</t>
+          <t>10:40:28</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.51</v>
+        <v>1.81</v>
       </c>
       <c r="F63" t="n">
-        <v>5.46</v>
+        <v>4.02</v>
       </c>
       <c r="G63" t="n">
-        <v>204.3</v>
+        <v>215.6</v>
       </c>
       <c r="H63" t="n">
-        <v>70.7</v>
+        <v>73</v>
       </c>
       <c r="I63" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>37.09</v>
+        <v>60.82</v>
       </c>
       <c r="K63" t="n">
-        <v>-160.56</v>
+        <v>-98.36</v>
       </c>
       <c r="L63" t="n">
-        <v>164.79</v>
+        <v>115.64</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10:46:36</t>
+          <t>10:41:36</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="F64" t="n">
-        <v>4.49</v>
+        <v>3.08</v>
       </c>
       <c r="G64" t="n">
-        <v>210.5</v>
+        <v>204.7</v>
       </c>
       <c r="H64" t="n">
-        <v>68</v>
+        <v>77.59999999999999</v>
       </c>
       <c r="I64" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>-28.79</v>
+        <v>55.94</v>
       </c>
       <c r="K64" t="n">
-        <v>-26.18</v>
+        <v>42.74</v>
       </c>
       <c r="L64" t="n">
-        <v>38.92</v>
+        <v>70.40000000000001</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10:51:14</t>
+          <t>10:47:40</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="F65" t="n">
-        <v>4.16</v>
+        <v>4.43</v>
       </c>
       <c r="G65" t="n">
-        <v>209.3</v>
+        <v>201.8</v>
       </c>
       <c r="H65" t="n">
-        <v>80.09999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="I65" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>-21.12</v>
+        <v>99.26000000000001</v>
       </c>
       <c r="K65" t="n">
-        <v>-42</v>
+        <v>-185.23</v>
       </c>
       <c r="L65" t="n">
-        <v>47.02</v>
+        <v>210.15</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10:53:32</t>
+          <t>10:49:14</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>2.79</v>
+        <v>1.4</v>
       </c>
       <c r="F66" t="n">
-        <v>4</v>
+        <v>3.78</v>
       </c>
       <c r="G66" t="n">
-        <v>202.6</v>
+        <v>208.9</v>
       </c>
       <c r="H66" t="n">
-        <v>74.2</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I66" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>206.4</v>
+        <v>-93.45</v>
       </c>
       <c r="K66" t="n">
-        <v>-87.64</v>
+        <v>174.09</v>
       </c>
       <c r="L66" t="n">
-        <v>224.24</v>
+        <v>197.58</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10:55:14</t>
+          <t>10:50:18</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="F67" t="n">
-        <v>5.09</v>
+        <v>4.27</v>
       </c>
       <c r="G67" t="n">
-        <v>201.7</v>
+        <v>208.7</v>
       </c>
       <c r="H67" t="n">
-        <v>78.3</v>
+        <v>74.8</v>
       </c>
       <c r="I67" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>38.96</v>
+        <v>66.89</v>
       </c>
       <c r="K67" t="n">
-        <v>-30.72</v>
+        <v>-119.36</v>
       </c>
       <c r="L67" t="n">
-        <v>49.62</v>
+        <v>136.83</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>11:00:51</t>
+          <t>10:54:20</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.51</v>
+        <v>1.6</v>
       </c>
       <c r="F68" t="n">
-        <v>4.92</v>
+        <v>4.37</v>
       </c>
       <c r="G68" t="n">
-        <v>197.9</v>
+        <v>212.2</v>
       </c>
       <c r="H68" t="n">
-        <v>77.8</v>
+        <v>76</v>
       </c>
       <c r="I68" t="n">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>396.38</v>
+        <v>-98.56999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>196.72</v>
+        <v>-193.29</v>
       </c>
       <c r="L68" t="n">
-        <v>442.51</v>
+        <v>216.98</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>11:02:46</t>
+          <t>10:56:33</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.8</v>
+        <v>1.72</v>
       </c>
       <c r="F69" t="n">
-        <v>4.34</v>
+        <v>4.3</v>
       </c>
       <c r="G69" t="n">
-        <v>206</v>
+        <v>207.4</v>
       </c>
       <c r="H69" t="n">
-        <v>75.09999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="I69" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>-253.69</v>
+        <v>46.89</v>
       </c>
       <c r="K69" t="n">
-        <v>334.76</v>
+        <v>-72.25</v>
       </c>
       <c r="L69" t="n">
-        <v>420.03</v>
+        <v>86.13</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>11:04:04</t>
+          <t>10:57:37</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.87</v>
+        <v>1.62</v>
       </c>
       <c r="F70" t="n">
-        <v>3.94</v>
+        <v>4.24</v>
       </c>
       <c r="G70" t="n">
-        <v>210</v>
+        <v>202.8</v>
       </c>
       <c r="H70" t="n">
-        <v>80.90000000000001</v>
+        <v>75.7</v>
       </c>
       <c r="I70" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-111.09</v>
+        <v>-77.40000000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>-120.93</v>
+        <v>-3.57</v>
       </c>
       <c r="L70" t="n">
-        <v>164.21</v>
+        <v>77.48</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>11:07:17</t>
+          <t>11:03:20</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.63</v>
+        <v>2.49</v>
       </c>
       <c r="F71" t="n">
-        <v>4.67</v>
+        <v>4.83</v>
       </c>
       <c r="G71" t="n">
-        <v>203.6</v>
+        <v>212.7</v>
       </c>
       <c r="H71" t="n">
-        <v>70.8</v>
+        <v>73.7</v>
       </c>
       <c r="I71" t="n">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>827.03</v>
+        <v>470.13</v>
       </c>
       <c r="K71" t="n">
-        <v>207.3</v>
+        <v>-108.5</v>
       </c>
       <c r="L71" t="n">
-        <v>852.62</v>
+        <v>482.48</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>11:09:06</t>
+          <t>11:04:28</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="F72" t="n">
-        <v>4.66</v>
+        <v>4.17</v>
       </c>
       <c r="G72" t="n">
-        <v>207.9</v>
+        <v>196.9</v>
       </c>
       <c r="H72" t="n">
-        <v>75.2</v>
+        <v>67.3</v>
       </c>
       <c r="I72" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>538.35</v>
+        <v>1.99</v>
       </c>
       <c r="K72" t="n">
-        <v>449.29</v>
+        <v>-113.28</v>
       </c>
       <c r="L72" t="n">
-        <v>701.2</v>
+        <v>113.3</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>11:11:08</t>
+          <t>11:05:49</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.82</v>
+        <v>2.12</v>
       </c>
       <c r="F73" t="n">
-        <v>4.22</v>
+        <v>4.49</v>
       </c>
       <c r="G73" t="n">
-        <v>201.2</v>
+        <v>201.8</v>
       </c>
       <c r="H73" t="n">
-        <v>76.59999999999999</v>
+        <v>73.7</v>
       </c>
       <c r="I73" t="n">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>117.53</v>
+        <v>107.7</v>
       </c>
       <c r="K73" t="n">
-        <v>-26.07</v>
+        <v>24.65</v>
       </c>
       <c r="L73" t="n">
-        <v>120.39</v>
+        <v>110.49</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>11:22:20</t>
+          <t>11:16:18</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.36</v>
+        <v>1.86</v>
       </c>
       <c r="F74" t="n">
-        <v>4.26</v>
+        <v>4.47</v>
       </c>
       <c r="G74" t="n">
-        <v>200</v>
+        <v>202.3</v>
       </c>
       <c r="H74" t="n">
-        <v>76.2</v>
+        <v>73.2</v>
       </c>
       <c r="I74" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>69.2</v>
+        <v>65.12</v>
       </c>
       <c r="K74" t="n">
-        <v>87.56</v>
+        <v>30.44</v>
       </c>
       <c r="L74" t="n">
-        <v>111.6</v>
+        <v>71.89</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>11:24:14</t>
+          <t>11:17:31</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.56</v>
+        <v>2.02</v>
       </c>
       <c r="F75" t="n">
-        <v>4.27</v>
+        <v>3.44</v>
       </c>
       <c r="G75" t="n">
-        <v>215</v>
+        <v>192.1</v>
       </c>
       <c r="H75" t="n">
-        <v>73.90000000000001</v>
+        <v>71.59999999999999</v>
       </c>
       <c r="I75" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-13.75</v>
+        <v>-92.42</v>
       </c>
       <c r="K75" t="n">
-        <v>-34.49</v>
+        <v>125.74</v>
       </c>
       <c r="L75" t="n">
-        <v>37.13</v>
+        <v>156.05</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>11:27:01</t>
+          <t>11:19:03</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.46</v>
+        <v>1.82</v>
       </c>
       <c r="F76" t="n">
-        <v>3.87</v>
+        <v>4.99</v>
       </c>
       <c r="G76" t="n">
-        <v>219.5</v>
+        <v>219.3</v>
       </c>
       <c r="H76" t="n">
-        <v>77.7</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I76" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>11.25</v>
+        <v>-80.18000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>-35.48</v>
+        <v>-23.35</v>
       </c>
       <c r="L76" t="n">
-        <v>37.22</v>
+        <v>83.51000000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>11:31:39</t>
+          <t>11:24:03</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.4</v>
+        <v>1.72</v>
       </c>
       <c r="F77" t="n">
-        <v>4.27</v>
+        <v>4.12</v>
       </c>
       <c r="G77" t="n">
-        <v>208.4</v>
+        <v>196.2</v>
       </c>
       <c r="H77" t="n">
-        <v>69.3</v>
+        <v>81.5</v>
       </c>
       <c r="I77" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>71.14</v>
+        <v>-75.27</v>
       </c>
       <c r="K77" t="n">
-        <v>-100.21</v>
+        <v>-28.14</v>
       </c>
       <c r="L77" t="n">
-        <v>122.89</v>
+        <v>80.36</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>11:33:51</t>
+          <t>11:25:39</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="F78" t="n">
-        <v>4.11</v>
+        <v>4.18</v>
       </c>
       <c r="G78" t="n">
-        <v>206.7</v>
+        <v>209.8</v>
       </c>
       <c r="H78" t="n">
-        <v>71.5</v>
+        <v>74.3</v>
       </c>
       <c r="I78" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>42.71</v>
+        <v>-37.36</v>
       </c>
       <c r="K78" t="n">
-        <v>98.25</v>
+        <v>-27.52</v>
       </c>
       <c r="L78" t="n">
-        <v>107.14</v>
+        <v>46.4</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>11:35:06</t>
+          <t>11:27:15</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="F79" t="n">
-        <v>4.47</v>
+        <v>3.68</v>
       </c>
       <c r="G79" t="n">
-        <v>210.7</v>
+        <v>204.7</v>
       </c>
       <c r="H79" t="n">
-        <v>71.5</v>
+        <v>70.2</v>
       </c>
       <c r="I79" t="n">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>-27.91</v>
+        <v>29.91</v>
       </c>
       <c r="K79" t="n">
-        <v>92.62</v>
+        <v>48.67</v>
       </c>
       <c r="L79" t="n">
-        <v>96.73</v>
+        <v>57.12</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>11:40:25</t>
+          <t>11:31:31</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3397,34 +3397,34 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="F80" t="n">
-        <v>3.62</v>
+        <v>4.3</v>
       </c>
       <c r="G80" t="n">
-        <v>204.4</v>
+        <v>203.5</v>
       </c>
       <c r="H80" t="n">
-        <v>77.8</v>
+        <v>78.3</v>
       </c>
       <c r="I80" t="n">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-68.2</v>
+        <v>-111.3</v>
       </c>
       <c r="K80" t="n">
-        <v>-128.05</v>
+        <v>28.89</v>
       </c>
       <c r="L80" t="n">
-        <v>145.08</v>
+        <v>114.99</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>11:42:12</t>
+          <t>11:32:39</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.55</v>
+        <v>1.8</v>
       </c>
       <c r="F81" t="n">
-        <v>4.26</v>
+        <v>4.81</v>
       </c>
       <c r="G81" t="n">
-        <v>207.8</v>
+        <v>197.2</v>
       </c>
       <c r="H81" t="n">
-        <v>71.59999999999999</v>
+        <v>75</v>
       </c>
       <c r="I81" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>-87.45999999999999</v>
+        <v>45.94</v>
       </c>
       <c r="K81" t="n">
-        <v>99.97</v>
+        <v>-141.54</v>
       </c>
       <c r="L81" t="n">
-        <v>132.83</v>
+        <v>148.81</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>11:42:49</t>
+          <t>11:34:18</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.67</v>
+        <v>1.48</v>
       </c>
       <c r="F82" t="n">
-        <v>4.48</v>
+        <v>3.89</v>
       </c>
       <c r="G82" t="n">
-        <v>204.7</v>
+        <v>221.2</v>
       </c>
       <c r="H82" t="n">
-        <v>76.09999999999999</v>
+        <v>72.7</v>
       </c>
       <c r="I82" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>151.07</v>
+        <v>-56.47</v>
       </c>
       <c r="K82" t="n">
-        <v>-258.78</v>
+        <v>321.03</v>
       </c>
       <c r="L82" t="n">
-        <v>299.65</v>
+        <v>325.96</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>11:47:59</t>
+          <t>11:38:50</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="F83" t="n">
-        <v>3.55</v>
+        <v>4.48</v>
       </c>
       <c r="G83" t="n">
-        <v>208.3</v>
+        <v>229.2</v>
       </c>
       <c r="H83" t="n">
-        <v>67.7</v>
+        <v>71.8</v>
       </c>
       <c r="I83" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>-23.64</v>
+        <v>166.32</v>
       </c>
       <c r="K83" t="n">
-        <v>337.3</v>
+        <v>-234.1</v>
       </c>
       <c r="L83" t="n">
-        <v>338.13</v>
+        <v>287.17</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>11:50:10</t>
+          <t>11:41:26</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.72</v>
+        <v>1.55</v>
       </c>
       <c r="F84" t="n">
-        <v>4.3</v>
+        <v>4.27</v>
       </c>
       <c r="G84" t="n">
-        <v>219.6</v>
+        <v>197</v>
       </c>
       <c r="H84" t="n">
-        <v>70.8</v>
+        <v>77.7</v>
       </c>
       <c r="I84" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>96.62</v>
+        <v>-233.66</v>
       </c>
       <c r="K84" t="n">
-        <v>-34.6</v>
+        <v>-82.77</v>
       </c>
       <c r="L84" t="n">
-        <v>102.63</v>
+        <v>247.89</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>11:51:27</t>
+          <t>11:43:56</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.56</v>
+        <v>1.75</v>
       </c>
       <c r="F85" t="n">
-        <v>4.65</v>
+        <v>4.3</v>
       </c>
       <c r="G85" t="n">
-        <v>206.7</v>
+        <v>210.2</v>
       </c>
       <c r="H85" t="n">
-        <v>67.2</v>
+        <v>75.59999999999999</v>
       </c>
       <c r="I85" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-237.53</v>
+        <v>-126.74</v>
       </c>
       <c r="K85" t="n">
-        <v>-98.75</v>
+        <v>56.85</v>
       </c>
       <c r="L85" t="n">
-        <v>257.24</v>
+        <v>138.91</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>11:56:13</t>
+          <t>11:47:08</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.87</v>
+        <v>1.58</v>
       </c>
       <c r="F86" t="n">
         <v>4.51</v>
       </c>
       <c r="G86" t="n">
-        <v>202.4</v>
+        <v>211</v>
       </c>
       <c r="H86" t="n">
-        <v>77.90000000000001</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>411.66</v>
+        <v>6.84</v>
       </c>
       <c r="K86" t="n">
-        <v>-216.65</v>
+        <v>-398.88</v>
       </c>
       <c r="L86" t="n">
-        <v>465.19</v>
+        <v>398.94</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11:57:13</t>
+          <t>11:48:21</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="F87" t="n">
-        <v>4.21</v>
+        <v>4.54</v>
       </c>
       <c r="G87" t="n">
-        <v>212.6</v>
+        <v>218.5</v>
       </c>
       <c r="H87" t="n">
-        <v>71.90000000000001</v>
+        <v>76.8</v>
       </c>
       <c r="I87" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>-281.09</v>
+        <v>234</v>
       </c>
       <c r="K87" t="n">
-        <v>-420</v>
+        <v>-190.71</v>
       </c>
       <c r="L87" t="n">
-        <v>505.39</v>
+        <v>301.87</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11:58:41</t>
+          <t>11:50:34</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.56</v>
+        <v>1.74</v>
       </c>
       <c r="F88" t="n">
-        <v>4.19</v>
+        <v>4.37</v>
       </c>
       <c r="G88" t="n">
-        <v>210.7</v>
+        <v>217.3</v>
       </c>
       <c r="H88" t="n">
-        <v>68.7</v>
+        <v>76.5</v>
       </c>
       <c r="I88" t="n">
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>161.75</v>
+        <v>-71.70999999999999</v>
       </c>
       <c r="K88" t="n">
-        <v>-350.99</v>
+        <v>564.98</v>
       </c>
       <c r="L88" t="n">
-        <v>386.47</v>
+        <v>569.52</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-27.xlsx
+++ b/output/2024-10-27.xlsx
@@ -640,13 +640,13 @@
         <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>-23.99</v>
+        <v>-18.35</v>
       </c>
       <c r="K14" t="n">
-        <v>85.40000000000001</v>
+        <v>65.33</v>
       </c>
       <c r="L14" t="n">
-        <v>88.70999999999999</v>
+        <v>67.86</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>36.74</v>
+        <v>45.3</v>
       </c>
       <c r="K15" t="n">
-        <v>3.38</v>
+        <v>4.17</v>
       </c>
       <c r="L15" t="n">
-        <v>36.89</v>
+        <v>45.49</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>4.68</v>
+        <v>4.49</v>
       </c>
       <c r="K16" t="n">
-        <v>62.35</v>
+        <v>59.82</v>
       </c>
       <c r="L16" t="n">
-        <v>62.52</v>
+        <v>59.99</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-45.29</v>
+        <v>-54.45</v>
       </c>
       <c r="K17" t="n">
-        <v>22.29</v>
+        <v>26.79</v>
       </c>
       <c r="L17" t="n">
-        <v>50.47</v>
+        <v>60.69</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-110.72</v>
+        <v>-88.16</v>
       </c>
       <c r="K18" t="n">
-        <v>51.94</v>
+        <v>41.36</v>
       </c>
       <c r="L18" t="n">
-        <v>122.3</v>
+        <v>97.38</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>72.73999999999999</v>
+        <v>81.26000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>5.1</v>
+        <v>5.7</v>
       </c>
       <c r="L19" t="n">
-        <v>72.91</v>
+        <v>81.45999999999999</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>83.42</v>
+        <v>88.17</v>
       </c>
       <c r="K20" t="n">
-        <v>122.89</v>
+        <v>129.87</v>
       </c>
       <c r="L20" t="n">
-        <v>148.53</v>
+        <v>156.97</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-95.7</v>
+        <v>-115.18</v>
       </c>
       <c r="K21" t="n">
-        <v>37.26</v>
+        <v>44.85</v>
       </c>
       <c r="L21" t="n">
-        <v>102.7</v>
+        <v>123.6</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-210.45</v>
+        <v>-203.82</v>
       </c>
       <c r="K22" t="n">
-        <v>29.37</v>
+        <v>28.45</v>
       </c>
       <c r="L22" t="n">
-        <v>212.49</v>
+        <v>205.79</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>310.27</v>
+        <v>287.14</v>
       </c>
       <c r="K23" t="n">
-        <v>409.2</v>
+        <v>378.69</v>
       </c>
       <c r="L23" t="n">
-        <v>513.53</v>
+        <v>475.25</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>59.2</v>
+        <v>77.12</v>
       </c>
       <c r="K24" t="n">
-        <v>-103.72</v>
+        <v>-135.12</v>
       </c>
       <c r="L24" t="n">
-        <v>119.43</v>
+        <v>155.58</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-136.17</v>
+        <v>-182.57</v>
       </c>
       <c r="K25" t="n">
-        <v>-51.9</v>
+        <v>-69.59</v>
       </c>
       <c r="L25" t="n">
-        <v>145.73</v>
+        <v>195.39</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>496.24</v>
+        <v>510.98</v>
       </c>
       <c r="K26" t="n">
-        <v>153.9</v>
+        <v>158.47</v>
       </c>
       <c r="L26" t="n">
-        <v>519.5599999999999</v>
+        <v>534.99</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-279.83</v>
+        <v>-306.2</v>
       </c>
       <c r="K27" t="n">
-        <v>-192.19</v>
+        <v>-210.31</v>
       </c>
       <c r="L27" t="n">
-        <v>339.47</v>
+        <v>371.46</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>144.37</v>
+        <v>246.44</v>
       </c>
       <c r="K28" t="n">
-        <v>53.51</v>
+        <v>91.34</v>
       </c>
       <c r="L28" t="n">
-        <v>153.97</v>
+        <v>262.82</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>61.46</v>
+        <v>50.78</v>
       </c>
       <c r="K29" t="n">
-        <v>81.43000000000001</v>
+        <v>67.28</v>
       </c>
       <c r="L29" t="n">
-        <v>102.02</v>
+        <v>84.29000000000001</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-31.79</v>
+        <v>-26.53</v>
       </c>
       <c r="K30" t="n">
-        <v>78.31</v>
+        <v>65.36</v>
       </c>
       <c r="L30" t="n">
-        <v>84.52</v>
+        <v>70.54000000000001</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>-34.72</v>
+        <v>-38.4</v>
       </c>
       <c r="K31" t="n">
-        <v>1.55</v>
+        <v>1.72</v>
       </c>
       <c r="L31" t="n">
-        <v>34.76</v>
+        <v>38.44</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>-33.41</v>
+        <v>-46.5</v>
       </c>
       <c r="K32" t="n">
-        <v>-33.72</v>
+        <v>-46.94</v>
       </c>
       <c r="L32" t="n">
-        <v>47.47</v>
+        <v>66.06999999999999</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>104.02</v>
+        <v>82.06</v>
       </c>
       <c r="K33" t="n">
-        <v>52.19</v>
+        <v>41.18</v>
       </c>
       <c r="L33" t="n">
-        <v>116.38</v>
+        <v>91.81</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-160.72</v>
+        <v>-142.82</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.41</v>
+        <v>-0.37</v>
       </c>
       <c r="L34" t="n">
-        <v>160.72</v>
+        <v>142.82</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-48.18</v>
+        <v>-39.29</v>
       </c>
       <c r="K35" t="n">
-        <v>201.09</v>
+        <v>163.98</v>
       </c>
       <c r="L35" t="n">
-        <v>206.78</v>
+        <v>168.62</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-123.68</v>
+        <v>-128.95</v>
       </c>
       <c r="K36" t="n">
-        <v>-25.82</v>
+        <v>-26.92</v>
       </c>
       <c r="L36" t="n">
-        <v>126.34</v>
+        <v>131.73</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>16.98</v>
+        <v>23.03</v>
       </c>
       <c r="K37" t="n">
-        <v>-59.23</v>
+        <v>-80.36</v>
       </c>
       <c r="L37" t="n">
-        <v>61.62</v>
+        <v>83.59999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-128.95</v>
+        <v>-151.51</v>
       </c>
       <c r="K38" t="n">
-        <v>-95.29000000000001</v>
+        <v>-111.96</v>
       </c>
       <c r="L38" t="n">
-        <v>160.34</v>
+        <v>188.39</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-131.98</v>
+        <v>-193.41</v>
       </c>
       <c r="K39" t="n">
-        <v>0.18</v>
+        <v>0.27</v>
       </c>
       <c r="L39" t="n">
-        <v>131.98</v>
+        <v>193.41</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-57.57</v>
+        <v>-103.65</v>
       </c>
       <c r="K40" t="n">
-        <v>-69.55</v>
+        <v>-125.23</v>
       </c>
       <c r="L40" t="n">
-        <v>90.29000000000001</v>
+        <v>162.56</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>225.22</v>
+        <v>256.63</v>
       </c>
       <c r="K41" t="n">
-        <v>-46.03</v>
+        <v>-52.45</v>
       </c>
       <c r="L41" t="n">
-        <v>229.88</v>
+        <v>261.93</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-363.9</v>
+        <v>-354.41</v>
       </c>
       <c r="K42" t="n">
-        <v>-103.81</v>
+        <v>-101.1</v>
       </c>
       <c r="L42" t="n">
-        <v>378.42</v>
+        <v>368.55</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-66.73999999999999</v>
+        <v>-107.32</v>
       </c>
       <c r="K43" t="n">
-        <v>142.23</v>
+        <v>228.7</v>
       </c>
       <c r="L43" t="n">
-        <v>157.11</v>
+        <v>252.63</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>60.09</v>
+        <v>47.62</v>
       </c>
       <c r="K44" t="n">
-        <v>-77.63</v>
+        <v>-61.53</v>
       </c>
       <c r="L44" t="n">
-        <v>98.17</v>
+        <v>77.81</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>59.53</v>
+        <v>55.35</v>
       </c>
       <c r="K45" t="n">
-        <v>52.01</v>
+        <v>48.36</v>
       </c>
       <c r="L45" t="n">
-        <v>79.05</v>
+        <v>73.5</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>20.75</v>
+        <v>14.31</v>
       </c>
       <c r="K46" t="n">
-        <v>-152.55</v>
+        <v>-105.17</v>
       </c>
       <c r="L46" t="n">
-        <v>153.96</v>
+        <v>106.14</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>-10.94</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-103.07</v>
+        <v>-81.19</v>
       </c>
       <c r="L47" t="n">
-        <v>103.65</v>
+        <v>81.65000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>52.27</v>
+        <v>61.23</v>
       </c>
       <c r="K48" t="n">
-        <v>-28.08</v>
+        <v>-32.89</v>
       </c>
       <c r="L48" t="n">
-        <v>59.33</v>
+        <v>69.51000000000001</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-103.13</v>
+        <v>-83.14</v>
       </c>
       <c r="K49" t="n">
-        <v>-32.7</v>
+        <v>-26.37</v>
       </c>
       <c r="L49" t="n">
-        <v>108.19</v>
+        <v>87.22</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>38.77</v>
+        <v>37.86</v>
       </c>
       <c r="K50" t="n">
-        <v>-144.03</v>
+        <v>-140.67</v>
       </c>
       <c r="L50" t="n">
-        <v>149.15</v>
+        <v>145.68</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>301.8</v>
+        <v>219.09</v>
       </c>
       <c r="K51" t="n">
-        <v>-30.42</v>
+        <v>-22.08</v>
       </c>
       <c r="L51" t="n">
-        <v>303.33</v>
+        <v>220.2</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>47.84</v>
+        <v>57.7</v>
       </c>
       <c r="K52" t="n">
-        <v>-123.77</v>
+        <v>-149.28</v>
       </c>
       <c r="L52" t="n">
-        <v>132.69</v>
+        <v>160.05</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>89.37</v>
+        <v>96.76000000000001</v>
       </c>
       <c r="K53" t="n">
-        <v>-217.15</v>
+        <v>-235.11</v>
       </c>
       <c r="L53" t="n">
-        <v>234.82</v>
+        <v>254.24</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-209.86</v>
+        <v>-246.51</v>
       </c>
       <c r="K54" t="n">
-        <v>-24.64</v>
+        <v>-28.94</v>
       </c>
       <c r="L54" t="n">
-        <v>211.3</v>
+        <v>248.2</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>168.66</v>
+        <v>149.9</v>
       </c>
       <c r="K55" t="n">
-        <v>360.4</v>
+        <v>320.3</v>
       </c>
       <c r="L55" t="n">
-        <v>397.91</v>
+        <v>353.64</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>478.53</v>
+        <v>473.67</v>
       </c>
       <c r="K56" t="n">
-        <v>46.57</v>
+        <v>46.1</v>
       </c>
       <c r="L56" t="n">
-        <v>480.79</v>
+        <v>475.91</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>71.14</v>
+        <v>115.62</v>
       </c>
       <c r="K57" t="n">
-        <v>-168.69</v>
+        <v>-274.18</v>
       </c>
       <c r="L57" t="n">
-        <v>183.07</v>
+        <v>297.56</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-80.23999999999999</v>
+        <v>-114.48</v>
       </c>
       <c r="K58" t="n">
-        <v>-156.92</v>
+        <v>-223.88</v>
       </c>
       <c r="L58" t="n">
-        <v>176.25</v>
+        <v>251.45</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>-12.57</v>
+        <v>-13.05</v>
       </c>
       <c r="K59" t="n">
-        <v>-40.21</v>
+        <v>-41.74</v>
       </c>
       <c r="L59" t="n">
-        <v>42.12</v>
+        <v>43.73</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>2.67</v>
+        <v>2.01</v>
       </c>
       <c r="K60" t="n">
-        <v>85.02</v>
+        <v>64.08</v>
       </c>
       <c r="L60" t="n">
-        <v>85.06</v>
+        <v>64.11</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>53.13</v>
+        <v>42.25</v>
       </c>
       <c r="K61" t="n">
-        <v>82.56</v>
+        <v>65.64</v>
       </c>
       <c r="L61" t="n">
-        <v>98.18000000000001</v>
+        <v>78.06</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>70.29000000000001</v>
+        <v>61.82</v>
       </c>
       <c r="K62" t="n">
-        <v>31.22</v>
+        <v>27.45</v>
       </c>
       <c r="L62" t="n">
-        <v>76.91</v>
+        <v>67.64</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>60.82</v>
+        <v>53.5</v>
       </c>
       <c r="K63" t="n">
-        <v>-98.36</v>
+        <v>-86.52</v>
       </c>
       <c r="L63" t="n">
-        <v>115.64</v>
+        <v>101.73</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>55.94</v>
+        <v>55.36</v>
       </c>
       <c r="K64" t="n">
-        <v>42.74</v>
+        <v>42.3</v>
       </c>
       <c r="L64" t="n">
-        <v>70.40000000000001</v>
+        <v>69.68000000000001</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>99.26000000000001</v>
+        <v>89.42</v>
       </c>
       <c r="K65" t="n">
-        <v>-185.23</v>
+        <v>-166.86</v>
       </c>
       <c r="L65" t="n">
-        <v>210.15</v>
+        <v>189.31</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-93.45</v>
+        <v>-80.66</v>
       </c>
       <c r="K66" t="n">
-        <v>174.09</v>
+        <v>150.27</v>
       </c>
       <c r="L66" t="n">
-        <v>197.58</v>
+        <v>170.55</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>66.89</v>
+        <v>67.43000000000001</v>
       </c>
       <c r="K67" t="n">
-        <v>-119.36</v>
+        <v>-120.32</v>
       </c>
       <c r="L67" t="n">
-        <v>136.83</v>
+        <v>137.92</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-98.56999999999999</v>
+        <v>-103.33</v>
       </c>
       <c r="K68" t="n">
-        <v>-193.29</v>
+        <v>-202.64</v>
       </c>
       <c r="L68" t="n">
-        <v>216.98</v>
+        <v>227.47</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>46.89</v>
+        <v>69.70999999999999</v>
       </c>
       <c r="K69" t="n">
-        <v>-72.25</v>
+        <v>-107.41</v>
       </c>
       <c r="L69" t="n">
-        <v>86.13</v>
+        <v>128.05</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-77.40000000000001</v>
+        <v>-151.7</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.57</v>
+        <v>-7</v>
       </c>
       <c r="L70" t="n">
-        <v>77.48</v>
+        <v>151.87</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>470.13</v>
+        <v>439.89</v>
       </c>
       <c r="K71" t="n">
-        <v>-108.5</v>
+        <v>-101.53</v>
       </c>
       <c r="L71" t="n">
-        <v>482.48</v>
+        <v>451.46</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>1.99</v>
+        <v>3.57</v>
       </c>
       <c r="K72" t="n">
-        <v>-113.28</v>
+        <v>-203.29</v>
       </c>
       <c r="L72" t="n">
-        <v>113.3</v>
+        <v>203.32</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>107.7</v>
+        <v>205.19</v>
       </c>
       <c r="K73" t="n">
-        <v>24.65</v>
+        <v>46.96</v>
       </c>
       <c r="L73" t="n">
-        <v>110.49</v>
+        <v>210.5</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>65.12</v>
+        <v>53.77</v>
       </c>
       <c r="K74" t="n">
-        <v>30.44</v>
+        <v>25.14</v>
       </c>
       <c r="L74" t="n">
-        <v>71.89</v>
+        <v>59.36</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-92.42</v>
+        <v>-61.37</v>
       </c>
       <c r="K75" t="n">
-        <v>125.74</v>
+        <v>83.51000000000001</v>
       </c>
       <c r="L75" t="n">
-        <v>156.05</v>
+        <v>103.63</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>-80.18000000000001</v>
+        <v>-67.76000000000001</v>
       </c>
       <c r="K76" t="n">
-        <v>-23.35</v>
+        <v>-19.73</v>
       </c>
       <c r="L76" t="n">
-        <v>83.51000000000001</v>
+        <v>70.58</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-75.27</v>
+        <v>-65.5</v>
       </c>
       <c r="K77" t="n">
-        <v>-28.14</v>
+        <v>-24.49</v>
       </c>
       <c r="L77" t="n">
-        <v>80.36</v>
+        <v>69.93000000000001</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-37.36</v>
+        <v>-46.3</v>
       </c>
       <c r="K78" t="n">
-        <v>-27.52</v>
+        <v>-34.1</v>
       </c>
       <c r="L78" t="n">
-        <v>46.4</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>29.91</v>
+        <v>36.2</v>
       </c>
       <c r="K79" t="n">
-        <v>48.67</v>
+        <v>58.91</v>
       </c>
       <c r="L79" t="n">
-        <v>57.12</v>
+        <v>69.14</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-111.3</v>
+        <v>-113.1</v>
       </c>
       <c r="K80" t="n">
-        <v>28.89</v>
+        <v>29.36</v>
       </c>
       <c r="L80" t="n">
-        <v>114.99</v>
+        <v>116.85</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>45.94</v>
+        <v>46.51</v>
       </c>
       <c r="K81" t="n">
-        <v>-141.54</v>
+        <v>-143.29</v>
       </c>
       <c r="L81" t="n">
-        <v>148.81</v>
+        <v>150.65</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-56.47</v>
+        <v>-43.6</v>
       </c>
       <c r="K82" t="n">
-        <v>321.03</v>
+        <v>247.86</v>
       </c>
       <c r="L82" t="n">
-        <v>325.96</v>
+        <v>251.67</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>166.32</v>
+        <v>166.05</v>
       </c>
       <c r="K83" t="n">
-        <v>-234.1</v>
+        <v>-233.72</v>
       </c>
       <c r="L83" t="n">
-        <v>287.17</v>
+        <v>286.7</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-233.66</v>
+        <v>-219.81</v>
       </c>
       <c r="K84" t="n">
-        <v>-82.77</v>
+        <v>-77.87</v>
       </c>
       <c r="L84" t="n">
-        <v>247.89</v>
+        <v>233.2</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-126.74</v>
+        <v>-155.48</v>
       </c>
       <c r="K85" t="n">
-        <v>56.85</v>
+        <v>69.73999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>138.91</v>
+        <v>170.4</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>6.84</v>
+        <v>7.36</v>
       </c>
       <c r="K86" t="n">
-        <v>-398.88</v>
+        <v>-428.86</v>
       </c>
       <c r="L86" t="n">
-        <v>398.94</v>
+        <v>428.92</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>234</v>
+        <v>305.91</v>
       </c>
       <c r="K87" t="n">
-        <v>-190.71</v>
+        <v>-249.32</v>
       </c>
       <c r="L87" t="n">
-        <v>301.87</v>
+        <v>394.64</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-71.70999999999999</v>
+        <v>-75.45</v>
       </c>
       <c r="K88" t="n">
-        <v>564.98</v>
+        <v>594.4299999999999</v>
       </c>
       <c r="L88" t="n">
-        <v>569.52</v>
+        <v>599.2</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-27.xlsx
+++ b/output/2024-10-27.xlsx
@@ -640,13 +640,13 @@
         <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>-18.35</v>
+        <v>-17.89</v>
       </c>
       <c r="K14" t="n">
-        <v>65.33</v>
+        <v>63.71</v>
       </c>
       <c r="L14" t="n">
-        <v>67.86</v>
+        <v>66.17</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>45.3</v>
+        <v>39.1</v>
       </c>
       <c r="K15" t="n">
-        <v>4.17</v>
+        <v>3.6</v>
       </c>
       <c r="L15" t="n">
-        <v>45.49</v>
+        <v>39.26</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>4.49</v>
+        <v>3.88</v>
       </c>
       <c r="K16" t="n">
-        <v>59.82</v>
+        <v>51.76</v>
       </c>
       <c r="L16" t="n">
-        <v>59.99</v>
+        <v>51.91</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-54.45</v>
+        <v>-46.57</v>
       </c>
       <c r="K17" t="n">
-        <v>26.79</v>
+        <v>22.92</v>
       </c>
       <c r="L17" t="n">
-        <v>60.69</v>
+        <v>51.9</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-88.16</v>
+        <v>-78.37</v>
       </c>
       <c r="K18" t="n">
-        <v>41.36</v>
+        <v>36.77</v>
       </c>
       <c r="L18" t="n">
-        <v>97.38</v>
+        <v>86.56999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>81.26000000000001</v>
+        <v>62.76</v>
       </c>
       <c r="K19" t="n">
-        <v>5.7</v>
+        <v>4.4</v>
       </c>
       <c r="L19" t="n">
-        <v>81.45999999999999</v>
+        <v>62.92</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>88.17</v>
+        <v>59.12</v>
       </c>
       <c r="K20" t="n">
-        <v>129.87</v>
+        <v>87.08</v>
       </c>
       <c r="L20" t="n">
-        <v>156.97</v>
+        <v>105.26</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-115.18</v>
+        <v>-80.41</v>
       </c>
       <c r="K21" t="n">
-        <v>44.85</v>
+        <v>31.31</v>
       </c>
       <c r="L21" t="n">
-        <v>123.6</v>
+        <v>86.29000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-203.82</v>
+        <v>-132.85</v>
       </c>
       <c r="K22" t="n">
-        <v>28.45</v>
+        <v>18.54</v>
       </c>
       <c r="L22" t="n">
-        <v>205.79</v>
+        <v>134.14</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>287.14</v>
+        <v>169.53</v>
       </c>
       <c r="K23" t="n">
-        <v>378.69</v>
+        <v>223.58</v>
       </c>
       <c r="L23" t="n">
-        <v>475.25</v>
+        <v>280.59</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>77.12</v>
+        <v>51.21</v>
       </c>
       <c r="K24" t="n">
-        <v>-135.12</v>
+        <v>-89.70999999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>155.58</v>
+        <v>103.3</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-182.57</v>
+        <v>-107.92</v>
       </c>
       <c r="K25" t="n">
-        <v>-69.59</v>
+        <v>-41.13</v>
       </c>
       <c r="L25" t="n">
-        <v>195.39</v>
+        <v>115.49</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>510.98</v>
+        <v>280.28</v>
       </c>
       <c r="K26" t="n">
-        <v>158.47</v>
+        <v>86.92</v>
       </c>
       <c r="L26" t="n">
-        <v>534.99</v>
+        <v>293.45</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-306.2</v>
+        <v>-180.64</v>
       </c>
       <c r="K27" t="n">
-        <v>-210.31</v>
+        <v>-124.07</v>
       </c>
       <c r="L27" t="n">
-        <v>371.46</v>
+        <v>219.15</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>246.44</v>
+        <v>130.69</v>
       </c>
       <c r="K28" t="n">
-        <v>91.34</v>
+        <v>48.44</v>
       </c>
       <c r="L28" t="n">
-        <v>262.82</v>
+        <v>139.38</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>50.78</v>
+        <v>48.17</v>
       </c>
       <c r="K29" t="n">
-        <v>67.28</v>
+        <v>63.82</v>
       </c>
       <c r="L29" t="n">
-        <v>84.29000000000001</v>
+        <v>79.95999999999999</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-26.53</v>
+        <v>-23.76</v>
       </c>
       <c r="K30" t="n">
-        <v>65.36</v>
+        <v>58.52</v>
       </c>
       <c r="L30" t="n">
-        <v>70.54000000000001</v>
+        <v>63.16</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>-38.4</v>
+        <v>-37.45</v>
       </c>
       <c r="K31" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="L31" t="n">
-        <v>38.44</v>
+        <v>37.49</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>-46.5</v>
+        <v>-35.71</v>
       </c>
       <c r="K32" t="n">
-        <v>-46.94</v>
+        <v>-36.04</v>
       </c>
       <c r="L32" t="n">
-        <v>66.06999999999999</v>
+        <v>50.73</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>82.06</v>
+        <v>75.14</v>
       </c>
       <c r="K33" t="n">
-        <v>41.18</v>
+        <v>37.7</v>
       </c>
       <c r="L33" t="n">
-        <v>91.81</v>
+        <v>84.06999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-142.82</v>
+        <v>-113.6</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.37</v>
+        <v>-0.29</v>
       </c>
       <c r="L34" t="n">
-        <v>142.82</v>
+        <v>113.6</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-39.29</v>
+        <v>-30.64</v>
       </c>
       <c r="K35" t="n">
-        <v>163.98</v>
+        <v>127.89</v>
       </c>
       <c r="L35" t="n">
-        <v>168.62</v>
+        <v>131.51</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-128.95</v>
+        <v>-93.64</v>
       </c>
       <c r="K36" t="n">
-        <v>-26.92</v>
+        <v>-19.55</v>
       </c>
       <c r="L36" t="n">
-        <v>131.73</v>
+        <v>95.66</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>23.03</v>
+        <v>18.03</v>
       </c>
       <c r="K37" t="n">
-        <v>-80.36</v>
+        <v>-62.9</v>
       </c>
       <c r="L37" t="n">
-        <v>83.59999999999999</v>
+        <v>65.44</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-151.51</v>
+        <v>-96.37</v>
       </c>
       <c r="K38" t="n">
-        <v>-111.96</v>
+        <v>-71.20999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>188.39</v>
+        <v>119.82</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-193.41</v>
+        <v>-106.84</v>
       </c>
       <c r="K39" t="n">
-        <v>0.27</v>
+        <v>0.15</v>
       </c>
       <c r="L39" t="n">
-        <v>193.41</v>
+        <v>106.85</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-103.65</v>
+        <v>-57.35</v>
       </c>
       <c r="K40" t="n">
-        <v>-125.23</v>
+        <v>-69.29000000000001</v>
       </c>
       <c r="L40" t="n">
-        <v>162.56</v>
+        <v>89.94</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>256.63</v>
+        <v>164.15</v>
       </c>
       <c r="K41" t="n">
-        <v>-52.45</v>
+        <v>-33.55</v>
       </c>
       <c r="L41" t="n">
-        <v>261.93</v>
+        <v>167.54</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-354.41</v>
+        <v>-227.74</v>
       </c>
       <c r="K42" t="n">
-        <v>-101.1</v>
+        <v>-64.95999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>368.55</v>
+        <v>236.82</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-107.32</v>
+        <v>-58.81</v>
       </c>
       <c r="K43" t="n">
-        <v>228.7</v>
+        <v>125.32</v>
       </c>
       <c r="L43" t="n">
-        <v>252.63</v>
+        <v>138.44</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>47.62</v>
+        <v>40.73</v>
       </c>
       <c r="K44" t="n">
-        <v>-61.53</v>
+        <v>-52.62</v>
       </c>
       <c r="L44" t="n">
-        <v>77.81</v>
+        <v>66.54000000000001</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>55.35</v>
+        <v>49.04</v>
       </c>
       <c r="K45" t="n">
-        <v>48.36</v>
+        <v>42.85</v>
       </c>
       <c r="L45" t="n">
-        <v>73.5</v>
+        <v>65.12</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>14.31</v>
+        <v>12.4</v>
       </c>
       <c r="K46" t="n">
-        <v>-105.17</v>
+        <v>-91.13</v>
       </c>
       <c r="L46" t="n">
-        <v>106.14</v>
+        <v>91.97</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>-8.619999999999999</v>
+        <v>-8.24</v>
       </c>
       <c r="K47" t="n">
-        <v>-81.19</v>
+        <v>-77.67</v>
       </c>
       <c r="L47" t="n">
-        <v>81.65000000000001</v>
+        <v>78.11</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>61.23</v>
+        <v>49.98</v>
       </c>
       <c r="K48" t="n">
-        <v>-32.89</v>
+        <v>-26.84</v>
       </c>
       <c r="L48" t="n">
-        <v>69.51000000000001</v>
+        <v>56.73</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-83.14</v>
+        <v>-76.39</v>
       </c>
       <c r="K49" t="n">
-        <v>-26.37</v>
+        <v>-24.22</v>
       </c>
       <c r="L49" t="n">
-        <v>87.22</v>
+        <v>80.14</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>37.86</v>
+        <v>27.18</v>
       </c>
       <c r="K50" t="n">
-        <v>-140.67</v>
+        <v>-100.98</v>
       </c>
       <c r="L50" t="n">
-        <v>145.68</v>
+        <v>104.57</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>219.09</v>
+        <v>169.58</v>
       </c>
       <c r="K51" t="n">
-        <v>-22.08</v>
+        <v>-17.09</v>
       </c>
       <c r="L51" t="n">
-        <v>220.2</v>
+        <v>170.44</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>57.7</v>
+        <v>40.86</v>
       </c>
       <c r="K52" t="n">
-        <v>-149.28</v>
+        <v>-105.69</v>
       </c>
       <c r="L52" t="n">
-        <v>160.05</v>
+        <v>113.31</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>96.76000000000001</v>
+        <v>59.24</v>
       </c>
       <c r="K53" t="n">
-        <v>-235.11</v>
+        <v>-143.93</v>
       </c>
       <c r="L53" t="n">
-        <v>254.24</v>
+        <v>155.64</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-246.51</v>
+        <v>-140.59</v>
       </c>
       <c r="K54" t="n">
-        <v>-28.94</v>
+        <v>-16.51</v>
       </c>
       <c r="L54" t="n">
-        <v>248.2</v>
+        <v>141.56</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>149.9</v>
+        <v>91.62</v>
       </c>
       <c r="K55" t="n">
-        <v>320.3</v>
+        <v>195.78</v>
       </c>
       <c r="L55" t="n">
-        <v>353.64</v>
+        <v>216.15</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>473.67</v>
+        <v>279.1</v>
       </c>
       <c r="K56" t="n">
-        <v>46.1</v>
+        <v>27.16</v>
       </c>
       <c r="L56" t="n">
-        <v>475.91</v>
+        <v>280.42</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>115.62</v>
+        <v>59.18</v>
       </c>
       <c r="K57" t="n">
-        <v>-274.18</v>
+        <v>-140.34</v>
       </c>
       <c r="L57" t="n">
-        <v>297.56</v>
+        <v>152.3</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-114.48</v>
+        <v>-67.43000000000001</v>
       </c>
       <c r="K58" t="n">
-        <v>-223.88</v>
+        <v>-131.87</v>
       </c>
       <c r="L58" t="n">
-        <v>251.45</v>
+        <v>148.11</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>-13.05</v>
+        <v>-12.11</v>
       </c>
       <c r="K59" t="n">
-        <v>-41.74</v>
+        <v>-38.73</v>
       </c>
       <c r="L59" t="n">
-        <v>43.73</v>
+        <v>40.58</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>2.01</v>
+        <v>1.95</v>
       </c>
       <c r="K60" t="n">
-        <v>64.08</v>
+        <v>62.23</v>
       </c>
       <c r="L60" t="n">
-        <v>64.11</v>
+        <v>62.26</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>42.25</v>
+        <v>37.69</v>
       </c>
       <c r="K61" t="n">
-        <v>65.64</v>
+        <v>58.55</v>
       </c>
       <c r="L61" t="n">
-        <v>78.06</v>
+        <v>69.63</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>61.82</v>
+        <v>59.37</v>
       </c>
       <c r="K62" t="n">
-        <v>27.45</v>
+        <v>26.37</v>
       </c>
       <c r="L62" t="n">
-        <v>67.64</v>
+        <v>64.97</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>53.5</v>
+        <v>43.08</v>
       </c>
       <c r="K63" t="n">
-        <v>-86.52</v>
+        <v>-69.67</v>
       </c>
       <c r="L63" t="n">
-        <v>101.73</v>
+        <v>81.91</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>55.36</v>
+        <v>48.88</v>
       </c>
       <c r="K64" t="n">
-        <v>42.3</v>
+        <v>37.35</v>
       </c>
       <c r="L64" t="n">
-        <v>69.68000000000001</v>
+        <v>61.51</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>89.42</v>
+        <v>61.98</v>
       </c>
       <c r="K65" t="n">
-        <v>-166.86</v>
+        <v>-115.65</v>
       </c>
       <c r="L65" t="n">
-        <v>189.31</v>
+        <v>131.21</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-80.66</v>
+        <v>-60.97</v>
       </c>
       <c r="K66" t="n">
-        <v>150.27</v>
+        <v>113.58</v>
       </c>
       <c r="L66" t="n">
-        <v>170.55</v>
+        <v>128.9</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>67.43000000000001</v>
+        <v>48.44</v>
       </c>
       <c r="K67" t="n">
-        <v>-120.32</v>
+        <v>-86.43000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>137.92</v>
+        <v>99.08</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-103.33</v>
+        <v>-65.70999999999999</v>
       </c>
       <c r="K68" t="n">
-        <v>-202.64</v>
+        <v>-128.87</v>
       </c>
       <c r="L68" t="n">
-        <v>227.47</v>
+        <v>144.65</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>69.70999999999999</v>
+        <v>46.18</v>
       </c>
       <c r="K69" t="n">
-        <v>-107.41</v>
+        <v>-71.15000000000001</v>
       </c>
       <c r="L69" t="n">
-        <v>128.05</v>
+        <v>84.83</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-151.7</v>
+        <v>-83.81</v>
       </c>
       <c r="K70" t="n">
-        <v>-7</v>
+        <v>-3.87</v>
       </c>
       <c r="L70" t="n">
-        <v>151.87</v>
+        <v>83.89</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>439.89</v>
+        <v>289.31</v>
       </c>
       <c r="K71" t="n">
-        <v>-101.53</v>
+        <v>-66.77</v>
       </c>
       <c r="L71" t="n">
-        <v>451.46</v>
+        <v>296.92</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>3.57</v>
+        <v>2.09</v>
       </c>
       <c r="K72" t="n">
-        <v>-203.29</v>
+        <v>-119.24</v>
       </c>
       <c r="L72" t="n">
-        <v>203.32</v>
+        <v>119.26</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>205.19</v>
+        <v>122.97</v>
       </c>
       <c r="K73" t="n">
-        <v>46.96</v>
+        <v>28.14</v>
       </c>
       <c r="L73" t="n">
-        <v>210.5</v>
+        <v>126.15</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>53.77</v>
+        <v>47.92</v>
       </c>
       <c r="K74" t="n">
-        <v>25.14</v>
+        <v>22.4</v>
       </c>
       <c r="L74" t="n">
-        <v>59.36</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-61.37</v>
+        <v>-55.61</v>
       </c>
       <c r="K75" t="n">
-        <v>83.51000000000001</v>
+        <v>75.67</v>
       </c>
       <c r="L75" t="n">
-        <v>103.63</v>
+        <v>93.91</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>-67.76000000000001</v>
+        <v>-55.73</v>
       </c>
       <c r="K76" t="n">
-        <v>-19.73</v>
+        <v>-16.23</v>
       </c>
       <c r="L76" t="n">
-        <v>70.58</v>
+        <v>58.05</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-65.5</v>
+        <v>-62.24</v>
       </c>
       <c r="K77" t="n">
-        <v>-24.49</v>
+        <v>-23.27</v>
       </c>
       <c r="L77" t="n">
-        <v>69.93000000000001</v>
+        <v>66.44</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-46.3</v>
+        <v>-40.67</v>
       </c>
       <c r="K78" t="n">
-        <v>-34.1</v>
+        <v>-29.95</v>
       </c>
       <c r="L78" t="n">
-        <v>57.5</v>
+        <v>50.51</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>36.2</v>
+        <v>29.27</v>
       </c>
       <c r="K79" t="n">
-        <v>58.91</v>
+        <v>47.64</v>
       </c>
       <c r="L79" t="n">
-        <v>69.14</v>
+        <v>55.91</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-113.1</v>
+        <v>-88.75</v>
       </c>
       <c r="K80" t="n">
-        <v>29.36</v>
+        <v>23.04</v>
       </c>
       <c r="L80" t="n">
-        <v>116.85</v>
+        <v>91.69</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>46.51</v>
+        <v>32.1</v>
       </c>
       <c r="K81" t="n">
-        <v>-143.29</v>
+        <v>-98.90000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>150.65</v>
+        <v>103.98</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-43.6</v>
+        <v>-32.85</v>
       </c>
       <c r="K82" t="n">
-        <v>247.86</v>
+        <v>186.72</v>
       </c>
       <c r="L82" t="n">
-        <v>251.67</v>
+        <v>189.58</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>166.05</v>
+        <v>97.88</v>
       </c>
       <c r="K83" t="n">
-        <v>-233.72</v>
+        <v>-137.76</v>
       </c>
       <c r="L83" t="n">
-        <v>286.7</v>
+        <v>168.99</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-219.81</v>
+        <v>-152.44</v>
       </c>
       <c r="K84" t="n">
-        <v>-77.87</v>
+        <v>-54</v>
       </c>
       <c r="L84" t="n">
-        <v>233.2</v>
+        <v>161.72</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-155.48</v>
+        <v>-98.79000000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>69.73999999999999</v>
+        <v>44.31</v>
       </c>
       <c r="L85" t="n">
-        <v>170.4</v>
+        <v>108.27</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>7.36</v>
+        <v>4.16</v>
       </c>
       <c r="K86" t="n">
-        <v>-428.86</v>
+        <v>-242.68</v>
       </c>
       <c r="L86" t="n">
-        <v>428.92</v>
+        <v>242.72</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>305.91</v>
+        <v>156.72</v>
       </c>
       <c r="K87" t="n">
-        <v>-249.32</v>
+        <v>-127.73</v>
       </c>
       <c r="L87" t="n">
-        <v>394.64</v>
+        <v>202.18</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-75.45</v>
+        <v>-38.46</v>
       </c>
       <c r="K88" t="n">
-        <v>594.4299999999999</v>
+        <v>303.05</v>
       </c>
       <c r="L88" t="n">
-        <v>599.2</v>
+        <v>305.48</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-27.xlsx
+++ b/output/2024-10-27.xlsx
@@ -640,13 +640,13 @@
         <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>-17.89</v>
+        <v>-17.4</v>
       </c>
       <c r="K14" t="n">
-        <v>63.71</v>
+        <v>61.96</v>
       </c>
       <c r="L14" t="n">
-        <v>66.17</v>
+        <v>64.36</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>39.1</v>
+        <v>38.52</v>
       </c>
       <c r="K15" t="n">
-        <v>3.6</v>
+        <v>3.54</v>
       </c>
       <c r="L15" t="n">
-        <v>39.26</v>
+        <v>38.69</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>3.88</v>
+        <v>3.78</v>
       </c>
       <c r="K16" t="n">
-        <v>51.76</v>
+        <v>50.36</v>
       </c>
       <c r="L16" t="n">
-        <v>51.91</v>
+        <v>50.51</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-46.57</v>
+        <v>-47.68</v>
       </c>
       <c r="K17" t="n">
-        <v>22.92</v>
+        <v>23.46</v>
       </c>
       <c r="L17" t="n">
-        <v>51.9</v>
+        <v>53.14</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-78.37</v>
+        <v>-80.26000000000001</v>
       </c>
       <c r="K18" t="n">
-        <v>36.77</v>
+        <v>37.65</v>
       </c>
       <c r="L18" t="n">
-        <v>86.56999999999999</v>
+        <v>88.66</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>62.76</v>
+        <v>65.25</v>
       </c>
       <c r="K19" t="n">
-        <v>4.4</v>
+        <v>4.58</v>
       </c>
       <c r="L19" t="n">
-        <v>62.92</v>
+        <v>65.41</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>59.12</v>
+        <v>64.73999999999999</v>
       </c>
       <c r="K20" t="n">
-        <v>87.08</v>
+        <v>95.36</v>
       </c>
       <c r="L20" t="n">
-        <v>105.26</v>
+        <v>115.26</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-80.41</v>
+        <v>-88.23</v>
       </c>
       <c r="K21" t="n">
-        <v>31.31</v>
+        <v>34.35</v>
       </c>
       <c r="L21" t="n">
-        <v>86.29000000000001</v>
+        <v>94.69</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-132.85</v>
+        <v>-147</v>
       </c>
       <c r="K22" t="n">
-        <v>18.54</v>
+        <v>20.52</v>
       </c>
       <c r="L22" t="n">
-        <v>134.14</v>
+        <v>148.42</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>169.53</v>
+        <v>192.78</v>
       </c>
       <c r="K23" t="n">
-        <v>223.58</v>
+        <v>254.24</v>
       </c>
       <c r="L23" t="n">
-        <v>280.59</v>
+        <v>319.07</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>51.21</v>
+        <v>57.51</v>
       </c>
       <c r="K24" t="n">
-        <v>-89.70999999999999</v>
+        <v>-100.77</v>
       </c>
       <c r="L24" t="n">
-        <v>103.3</v>
+        <v>116.03</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-107.92</v>
+        <v>-123.32</v>
       </c>
       <c r="K25" t="n">
-        <v>-41.13</v>
+        <v>-47</v>
       </c>
       <c r="L25" t="n">
-        <v>115.49</v>
+        <v>131.97</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>280.28</v>
+        <v>321.01</v>
       </c>
       <c r="K26" t="n">
-        <v>86.92</v>
+        <v>99.55</v>
       </c>
       <c r="L26" t="n">
-        <v>293.45</v>
+        <v>336.09</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-180.64</v>
+        <v>-203.35</v>
       </c>
       <c r="K27" t="n">
-        <v>-124.07</v>
+        <v>-139.67</v>
       </c>
       <c r="L27" t="n">
-        <v>219.15</v>
+        <v>246.7</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>130.69</v>
+        <v>152.49</v>
       </c>
       <c r="K28" t="n">
-        <v>48.44</v>
+        <v>56.51</v>
       </c>
       <c r="L28" t="n">
-        <v>139.38</v>
+        <v>162.62</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>48.17</v>
+        <v>48.22</v>
       </c>
       <c r="K29" t="n">
-        <v>63.82</v>
+        <v>63.9</v>
       </c>
       <c r="L29" t="n">
-        <v>79.95999999999999</v>
+        <v>80.05</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-23.76</v>
+        <v>-23.16</v>
       </c>
       <c r="K30" t="n">
-        <v>58.52</v>
+        <v>57.06</v>
       </c>
       <c r="L30" t="n">
-        <v>63.16</v>
+        <v>61.58</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>-37.45</v>
+        <v>-36.65</v>
       </c>
       <c r="K31" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="L31" t="n">
-        <v>37.49</v>
+        <v>36.69</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>-35.71</v>
+        <v>-37.25</v>
       </c>
       <c r="K32" t="n">
-        <v>-36.04</v>
+        <v>-37.6</v>
       </c>
       <c r="L32" t="n">
-        <v>50.73</v>
+        <v>52.92</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>75.14</v>
+        <v>77.48</v>
       </c>
       <c r="K33" t="n">
-        <v>37.7</v>
+        <v>38.88</v>
       </c>
       <c r="L33" t="n">
-        <v>84.06999999999999</v>
+        <v>86.69</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-113.6</v>
+        <v>-119.56</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.29</v>
+        <v>-0.31</v>
       </c>
       <c r="L34" t="n">
-        <v>113.6</v>
+        <v>119.56</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-30.64</v>
+        <v>-33.49</v>
       </c>
       <c r="K35" t="n">
-        <v>127.89</v>
+        <v>139.79</v>
       </c>
       <c r="L35" t="n">
-        <v>131.51</v>
+        <v>143.75</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-93.64</v>
+        <v>-102.54</v>
       </c>
       <c r="K36" t="n">
-        <v>-19.55</v>
+        <v>-21.4</v>
       </c>
       <c r="L36" t="n">
-        <v>95.66</v>
+        <v>104.75</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>18.03</v>
+        <v>19.38</v>
       </c>
       <c r="K37" t="n">
-        <v>-62.9</v>
+        <v>-67.63</v>
       </c>
       <c r="L37" t="n">
-        <v>65.44</v>
+        <v>70.34999999999999</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-96.37</v>
+        <v>-108.69</v>
       </c>
       <c r="K38" t="n">
-        <v>-71.20999999999999</v>
+        <v>-80.31999999999999</v>
       </c>
       <c r="L38" t="n">
-        <v>119.82</v>
+        <v>135.14</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-106.84</v>
+        <v>-123.01</v>
       </c>
       <c r="K39" t="n">
-        <v>0.15</v>
+        <v>0.17</v>
       </c>
       <c r="L39" t="n">
-        <v>106.85</v>
+        <v>123.01</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-57.35</v>
+        <v>-65.34999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>-69.29000000000001</v>
+        <v>-78.95</v>
       </c>
       <c r="L40" t="n">
-        <v>89.94</v>
+        <v>102.49</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>164.15</v>
+        <v>183.49</v>
       </c>
       <c r="K41" t="n">
-        <v>-33.55</v>
+        <v>-37.51</v>
       </c>
       <c r="L41" t="n">
-        <v>167.54</v>
+        <v>187.29</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-227.74</v>
+        <v>-252.45</v>
       </c>
       <c r="K42" t="n">
-        <v>-64.95999999999999</v>
+        <v>-72.01000000000001</v>
       </c>
       <c r="L42" t="n">
-        <v>236.82</v>
+        <v>262.52</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-58.81</v>
+        <v>-67.98</v>
       </c>
       <c r="K43" t="n">
-        <v>125.32</v>
+        <v>144.87</v>
       </c>
       <c r="L43" t="n">
-        <v>138.44</v>
+        <v>160.03</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>40.73</v>
+        <v>41.14</v>
       </c>
       <c r="K44" t="n">
-        <v>-52.62</v>
+        <v>-53.15</v>
       </c>
       <c r="L44" t="n">
-        <v>66.54000000000001</v>
+        <v>67.20999999999999</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>49.04</v>
+        <v>50.53</v>
       </c>
       <c r="K45" t="n">
-        <v>42.85</v>
+        <v>44.15</v>
       </c>
       <c r="L45" t="n">
-        <v>65.12</v>
+        <v>67.11</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>12.4</v>
+        <v>12.7</v>
       </c>
       <c r="K46" t="n">
-        <v>-91.13</v>
+        <v>-93.36</v>
       </c>
       <c r="L46" t="n">
-        <v>91.97</v>
+        <v>94.22</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>-8.24</v>
+        <v>-8.34</v>
       </c>
       <c r="K47" t="n">
-        <v>-77.67</v>
+        <v>-78.61</v>
       </c>
       <c r="L47" t="n">
-        <v>78.11</v>
+        <v>79.05</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>49.98</v>
+        <v>51.62</v>
       </c>
       <c r="K48" t="n">
-        <v>-26.84</v>
+        <v>-27.73</v>
       </c>
       <c r="L48" t="n">
-        <v>56.73</v>
+        <v>58.6</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-76.39</v>
+        <v>-77.81999999999999</v>
       </c>
       <c r="K49" t="n">
-        <v>-24.22</v>
+        <v>-24.68</v>
       </c>
       <c r="L49" t="n">
-        <v>80.14</v>
+        <v>81.64</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>27.18</v>
+        <v>29.73</v>
       </c>
       <c r="K50" t="n">
-        <v>-100.98</v>
+        <v>-110.45</v>
       </c>
       <c r="L50" t="n">
-        <v>104.57</v>
+        <v>114.38</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>169.58</v>
+        <v>183.71</v>
       </c>
       <c r="K51" t="n">
-        <v>-17.09</v>
+        <v>-18.51</v>
       </c>
       <c r="L51" t="n">
-        <v>170.44</v>
+        <v>184.64</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>40.86</v>
+        <v>44.87</v>
       </c>
       <c r="K52" t="n">
-        <v>-105.69</v>
+        <v>-116.07</v>
       </c>
       <c r="L52" t="n">
-        <v>113.31</v>
+        <v>124.44</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>59.24</v>
+        <v>67.14</v>
       </c>
       <c r="K53" t="n">
-        <v>-143.93</v>
+        <v>-163.12</v>
       </c>
       <c r="L53" t="n">
-        <v>155.64</v>
+        <v>176.4</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-140.59</v>
+        <v>-160.53</v>
       </c>
       <c r="K54" t="n">
-        <v>-16.51</v>
+        <v>-18.85</v>
       </c>
       <c r="L54" t="n">
-        <v>141.56</v>
+        <v>161.63</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>91.62</v>
+        <v>103.37</v>
       </c>
       <c r="K55" t="n">
-        <v>195.78</v>
+        <v>220.89</v>
       </c>
       <c r="L55" t="n">
-        <v>216.15</v>
+        <v>243.88</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>279.1</v>
+        <v>318.49</v>
       </c>
       <c r="K56" t="n">
-        <v>27.16</v>
+        <v>31</v>
       </c>
       <c r="L56" t="n">
-        <v>280.42</v>
+        <v>320</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>59.18</v>
+        <v>68.7</v>
       </c>
       <c r="K57" t="n">
-        <v>-140.34</v>
+        <v>-162.91</v>
       </c>
       <c r="L57" t="n">
-        <v>152.3</v>
+        <v>176.8</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-67.43000000000001</v>
+        <v>-76.88</v>
       </c>
       <c r="K58" t="n">
-        <v>-131.87</v>
+        <v>-150.34</v>
       </c>
       <c r="L58" t="n">
-        <v>148.11</v>
+        <v>168.86</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>-12.11</v>
+        <v>-12.12</v>
       </c>
       <c r="K59" t="n">
-        <v>-38.73</v>
+        <v>-38.75</v>
       </c>
       <c r="L59" t="n">
-        <v>40.58</v>
+        <v>40.6</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="K60" t="n">
-        <v>62.23</v>
+        <v>61.02</v>
       </c>
       <c r="L60" t="n">
-        <v>62.26</v>
+        <v>61.05</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>37.69</v>
+        <v>37.24</v>
       </c>
       <c r="K61" t="n">
-        <v>58.55</v>
+        <v>57.87</v>
       </c>
       <c r="L61" t="n">
-        <v>69.63</v>
+        <v>68.81999999999999</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>59.37</v>
+        <v>60.51</v>
       </c>
       <c r="K62" t="n">
-        <v>26.37</v>
+        <v>26.87</v>
       </c>
       <c r="L62" t="n">
-        <v>64.97</v>
+        <v>66.20999999999999</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>43.08</v>
+        <v>44.64</v>
       </c>
       <c r="K63" t="n">
-        <v>-69.67</v>
+        <v>-72.19</v>
       </c>
       <c r="L63" t="n">
-        <v>81.91</v>
+        <v>84.88</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>48.88</v>
+        <v>50.25</v>
       </c>
       <c r="K64" t="n">
-        <v>37.35</v>
+        <v>38.4</v>
       </c>
       <c r="L64" t="n">
-        <v>61.51</v>
+        <v>63.24</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>61.98</v>
+        <v>67.48999999999999</v>
       </c>
       <c r="K65" t="n">
-        <v>-115.65</v>
+        <v>-125.94</v>
       </c>
       <c r="L65" t="n">
-        <v>131.21</v>
+        <v>142.88</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-60.97</v>
+        <v>-65.73</v>
       </c>
       <c r="K66" t="n">
-        <v>113.58</v>
+        <v>122.45</v>
       </c>
       <c r="L66" t="n">
-        <v>128.9</v>
+        <v>138.98</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>48.44</v>
+        <v>52.87</v>
       </c>
       <c r="K67" t="n">
-        <v>-86.43000000000001</v>
+        <v>-94.34</v>
       </c>
       <c r="L67" t="n">
-        <v>99.08</v>
+        <v>108.14</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-65.70999999999999</v>
+        <v>-74.14</v>
       </c>
       <c r="K68" t="n">
-        <v>-128.87</v>
+        <v>-145.4</v>
       </c>
       <c r="L68" t="n">
-        <v>144.65</v>
+        <v>163.21</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>46.18</v>
+        <v>51.73</v>
       </c>
       <c r="K69" t="n">
-        <v>-71.15000000000001</v>
+        <v>-79.7</v>
       </c>
       <c r="L69" t="n">
-        <v>84.83</v>
+        <v>95.01000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-83.81</v>
+        <v>-96.43000000000001</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.87</v>
+        <v>-4.45</v>
       </c>
       <c r="L70" t="n">
-        <v>83.89</v>
+        <v>96.53</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>289.31</v>
+        <v>322.19</v>
       </c>
       <c r="K71" t="n">
-        <v>-66.77</v>
+        <v>-74.36</v>
       </c>
       <c r="L71" t="n">
-        <v>296.92</v>
+        <v>330.66</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>2.09</v>
+        <v>2.36</v>
       </c>
       <c r="K72" t="n">
-        <v>-119.24</v>
+        <v>-134.22</v>
       </c>
       <c r="L72" t="n">
-        <v>119.26</v>
+        <v>134.24</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>122.97</v>
+        <v>139.78</v>
       </c>
       <c r="K73" t="n">
-        <v>28.14</v>
+        <v>31.99</v>
       </c>
       <c r="L73" t="n">
-        <v>126.15</v>
+        <v>143.4</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>47.92</v>
+        <v>48.23</v>
       </c>
       <c r="K74" t="n">
-        <v>22.4</v>
+        <v>22.55</v>
       </c>
       <c r="L74" t="n">
-        <v>52.9</v>
+        <v>53.24</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-55.61</v>
+        <v>-56.43</v>
       </c>
       <c r="K75" t="n">
-        <v>75.67</v>
+        <v>76.78</v>
       </c>
       <c r="L75" t="n">
-        <v>93.91</v>
+        <v>95.29000000000001</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>-55.73</v>
+        <v>-56.53</v>
       </c>
       <c r="K76" t="n">
-        <v>-16.23</v>
+        <v>-16.46</v>
       </c>
       <c r="L76" t="n">
-        <v>58.05</v>
+        <v>58.88</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-62.24</v>
+        <v>-63.78</v>
       </c>
       <c r="K77" t="n">
-        <v>-23.27</v>
+        <v>-23.85</v>
       </c>
       <c r="L77" t="n">
-        <v>66.44</v>
+        <v>68.09999999999999</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-40.67</v>
+        <v>-41.67</v>
       </c>
       <c r="K78" t="n">
-        <v>-29.95</v>
+        <v>-30.69</v>
       </c>
       <c r="L78" t="n">
-        <v>50.51</v>
+        <v>51.75</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>29.27</v>
+        <v>30.19</v>
       </c>
       <c r="K79" t="n">
-        <v>47.64</v>
+        <v>49.13</v>
       </c>
       <c r="L79" t="n">
-        <v>55.91</v>
+        <v>57.67</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-88.75</v>
+        <v>-96.28</v>
       </c>
       <c r="K80" t="n">
-        <v>23.04</v>
+        <v>24.99</v>
       </c>
       <c r="L80" t="n">
-        <v>91.69</v>
+        <v>99.47</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>32.1</v>
+        <v>35.22</v>
       </c>
       <c r="K81" t="n">
-        <v>-98.90000000000001</v>
+        <v>-108.53</v>
       </c>
       <c r="L81" t="n">
-        <v>103.98</v>
+        <v>114.1</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-32.85</v>
+        <v>-35.56</v>
       </c>
       <c r="K82" t="n">
-        <v>186.72</v>
+        <v>202.15</v>
       </c>
       <c r="L82" t="n">
-        <v>189.58</v>
+        <v>205.25</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>97.88</v>
+        <v>110.93</v>
       </c>
       <c r="K83" t="n">
-        <v>-137.76</v>
+        <v>-156.14</v>
       </c>
       <c r="L83" t="n">
-        <v>168.99</v>
+        <v>191.54</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-152.44</v>
+        <v>-170.49</v>
       </c>
       <c r="K84" t="n">
-        <v>-54</v>
+        <v>-60.4</v>
       </c>
       <c r="L84" t="n">
-        <v>161.72</v>
+        <v>180.87</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-98.79000000000001</v>
+        <v>-111.39</v>
       </c>
       <c r="K85" t="n">
-        <v>44.31</v>
+        <v>49.96</v>
       </c>
       <c r="L85" t="n">
-        <v>108.27</v>
+        <v>122.08</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>4.16</v>
+        <v>4.73</v>
       </c>
       <c r="K86" t="n">
-        <v>-242.68</v>
+        <v>-276.02</v>
       </c>
       <c r="L86" t="n">
-        <v>242.72</v>
+        <v>276.06</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>156.72</v>
+        <v>182.74</v>
       </c>
       <c r="K87" t="n">
-        <v>-127.73</v>
+        <v>-148.94</v>
       </c>
       <c r="L87" t="n">
-        <v>202.18</v>
+        <v>235.75</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-38.46</v>
+        <v>-44.73</v>
       </c>
       <c r="K88" t="n">
-        <v>303.05</v>
+        <v>352.44</v>
       </c>
       <c r="L88" t="n">
-        <v>305.48</v>
+        <v>355.27</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-27.xlsx
+++ b/output/2024-10-27.xlsx
@@ -640,13 +640,13 @@
         <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>-17.4</v>
+        <v>-13.05</v>
       </c>
       <c r="K14" t="n">
-        <v>61.96</v>
+        <v>46.47</v>
       </c>
       <c r="L14" t="n">
-        <v>64.36</v>
+        <v>48.27</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>38.52</v>
+        <v>28.89</v>
       </c>
       <c r="K15" t="n">
-        <v>3.54</v>
+        <v>2.66</v>
       </c>
       <c r="L15" t="n">
-        <v>38.69</v>
+        <v>29.01</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>3.78</v>
+        <v>2.83</v>
       </c>
       <c r="K16" t="n">
-        <v>50.36</v>
+        <v>37.77</v>
       </c>
       <c r="L16" t="n">
-        <v>50.51</v>
+        <v>37.88</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-47.68</v>
+        <v>-35.76</v>
       </c>
       <c r="K17" t="n">
-        <v>23.46</v>
+        <v>17.6</v>
       </c>
       <c r="L17" t="n">
-        <v>53.14</v>
+        <v>39.85</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-80.26000000000001</v>
+        <v>-60.2</v>
       </c>
       <c r="K18" t="n">
-        <v>37.65</v>
+        <v>28.24</v>
       </c>
       <c r="L18" t="n">
-        <v>88.66</v>
+        <v>66.48999999999999</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>65.25</v>
+        <v>48.94</v>
       </c>
       <c r="K19" t="n">
-        <v>4.58</v>
+        <v>3.43</v>
       </c>
       <c r="L19" t="n">
-        <v>65.41</v>
+        <v>49.06</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>64.73999999999999</v>
+        <v>48.55</v>
       </c>
       <c r="K20" t="n">
-        <v>95.36</v>
+        <v>71.52</v>
       </c>
       <c r="L20" t="n">
-        <v>115.26</v>
+        <v>86.44</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-88.23</v>
+        <v>-66.17</v>
       </c>
       <c r="K21" t="n">
-        <v>34.35</v>
+        <v>25.77</v>
       </c>
       <c r="L21" t="n">
-        <v>94.69</v>
+        <v>71.01000000000001</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-147</v>
+        <v>-110.25</v>
       </c>
       <c r="K22" t="n">
-        <v>20.52</v>
+        <v>15.39</v>
       </c>
       <c r="L22" t="n">
-        <v>148.42</v>
+        <v>111.32</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>192.78</v>
+        <v>144.59</v>
       </c>
       <c r="K23" t="n">
-        <v>254.24</v>
+        <v>190.68</v>
       </c>
       <c r="L23" t="n">
-        <v>319.07</v>
+        <v>239.3</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>57.51</v>
+        <v>43.14</v>
       </c>
       <c r="K24" t="n">
-        <v>-100.77</v>
+        <v>-75.58</v>
       </c>
       <c r="L24" t="n">
-        <v>116.03</v>
+        <v>87.02</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-123.32</v>
+        <v>-92.48999999999999</v>
       </c>
       <c r="K25" t="n">
-        <v>-47</v>
+        <v>-35.25</v>
       </c>
       <c r="L25" t="n">
-        <v>131.97</v>
+        <v>98.98</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>321.01</v>
+        <v>240.75</v>
       </c>
       <c r="K26" t="n">
-        <v>99.55</v>
+        <v>74.67</v>
       </c>
       <c r="L26" t="n">
-        <v>336.09</v>
+        <v>252.07</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-203.35</v>
+        <v>-152.51</v>
       </c>
       <c r="K27" t="n">
-        <v>-139.67</v>
+        <v>-104.75</v>
       </c>
       <c r="L27" t="n">
-        <v>246.7</v>
+        <v>185.02</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>152.49</v>
+        <v>114.36</v>
       </c>
       <c r="K28" t="n">
-        <v>56.51</v>
+        <v>42.39</v>
       </c>
       <c r="L28" t="n">
-        <v>162.62</v>
+        <v>121.97</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>48.22</v>
+        <v>30.04</v>
       </c>
       <c r="K29" t="n">
-        <v>63.9</v>
+        <v>39.81</v>
       </c>
       <c r="L29" t="n">
-        <v>80.05</v>
+        <v>49.88</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-23.16</v>
+        <v>-17.37</v>
       </c>
       <c r="K30" t="n">
-        <v>57.06</v>
+        <v>42.8</v>
       </c>
       <c r="L30" t="n">
-        <v>61.58</v>
+        <v>46.19</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>-36.65</v>
+        <v>-27.49</v>
       </c>
       <c r="K31" t="n">
-        <v>1.64</v>
+        <v>1.23</v>
       </c>
       <c r="L31" t="n">
-        <v>36.69</v>
+        <v>27.51</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>-37.25</v>
+        <v>-27.94</v>
       </c>
       <c r="K32" t="n">
-        <v>-37.6</v>
+        <v>-28.2</v>
       </c>
       <c r="L32" t="n">
-        <v>52.92</v>
+        <v>39.69</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>77.48</v>
+        <v>58.11</v>
       </c>
       <c r="K33" t="n">
-        <v>38.88</v>
+        <v>29.16</v>
       </c>
       <c r="L33" t="n">
-        <v>86.69</v>
+        <v>65.01000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-119.56</v>
+        <v>-76.45999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.31</v>
+        <v>-0.2</v>
       </c>
       <c r="L34" t="n">
-        <v>119.56</v>
+        <v>76.45999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-33.49</v>
+        <v>-25.12</v>
       </c>
       <c r="K35" t="n">
-        <v>139.79</v>
+        <v>104.84</v>
       </c>
       <c r="L35" t="n">
-        <v>143.75</v>
+        <v>107.81</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-102.54</v>
+        <v>-76.90000000000001</v>
       </c>
       <c r="K36" t="n">
-        <v>-21.4</v>
+        <v>-16.05</v>
       </c>
       <c r="L36" t="n">
-        <v>104.75</v>
+        <v>78.56</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>19.38</v>
+        <v>14.54</v>
       </c>
       <c r="K37" t="n">
-        <v>-67.63</v>
+        <v>-50.72</v>
       </c>
       <c r="L37" t="n">
-        <v>70.34999999999999</v>
+        <v>52.77</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-108.69</v>
+        <v>-81.52</v>
       </c>
       <c r="K38" t="n">
-        <v>-80.31999999999999</v>
+        <v>-60.24</v>
       </c>
       <c r="L38" t="n">
-        <v>135.14</v>
+        <v>101.36</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-123.01</v>
+        <v>-92.25</v>
       </c>
       <c r="K39" t="n">
-        <v>0.17</v>
+        <v>0.13</v>
       </c>
       <c r="L39" t="n">
-        <v>123.01</v>
+        <v>92.25</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-65.34999999999999</v>
+        <v>-49.01</v>
       </c>
       <c r="K40" t="n">
-        <v>-78.95</v>
+        <v>-59.22</v>
       </c>
       <c r="L40" t="n">
-        <v>102.49</v>
+        <v>76.87</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>183.49</v>
+        <v>137.62</v>
       </c>
       <c r="K41" t="n">
-        <v>-37.51</v>
+        <v>-28.13</v>
       </c>
       <c r="L41" t="n">
-        <v>187.29</v>
+        <v>140.47</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-252.45</v>
+        <v>-189.34</v>
       </c>
       <c r="K42" t="n">
-        <v>-72.01000000000001</v>
+        <v>-54.01</v>
       </c>
       <c r="L42" t="n">
-        <v>262.52</v>
+        <v>196.89</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-67.98</v>
+        <v>-50.99</v>
       </c>
       <c r="K43" t="n">
-        <v>144.87</v>
+        <v>108.65</v>
       </c>
       <c r="L43" t="n">
-        <v>160.03</v>
+        <v>120.02</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>41.14</v>
+        <v>30.85</v>
       </c>
       <c r="K44" t="n">
-        <v>-53.15</v>
+        <v>-39.86</v>
       </c>
       <c r="L44" t="n">
-        <v>67.20999999999999</v>
+        <v>50.4</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>50.53</v>
+        <v>33.04</v>
       </c>
       <c r="K45" t="n">
-        <v>44.15</v>
+        <v>28.87</v>
       </c>
       <c r="L45" t="n">
-        <v>67.11</v>
+        <v>43.88</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>12.7</v>
+        <v>9.02</v>
       </c>
       <c r="K46" t="n">
-        <v>-93.36</v>
+        <v>-66.31999999999999</v>
       </c>
       <c r="L46" t="n">
-        <v>94.22</v>
+        <v>66.93000000000001</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>-8.34</v>
+        <v>-6.26</v>
       </c>
       <c r="K47" t="n">
-        <v>-78.61</v>
+        <v>-58.96</v>
       </c>
       <c r="L47" t="n">
-        <v>79.05</v>
+        <v>59.29</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>51.62</v>
+        <v>38.72</v>
       </c>
       <c r="K48" t="n">
-        <v>-27.73</v>
+        <v>-20.8</v>
       </c>
       <c r="L48" t="n">
-        <v>58.6</v>
+        <v>43.95</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-77.81999999999999</v>
+        <v>-57.05</v>
       </c>
       <c r="K49" t="n">
-        <v>-24.68</v>
+        <v>-18.09</v>
       </c>
       <c r="L49" t="n">
-        <v>81.64</v>
+        <v>59.85</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>29.73</v>
+        <v>22.3</v>
       </c>
       <c r="K50" t="n">
-        <v>-110.45</v>
+        <v>-82.84</v>
       </c>
       <c r="L50" t="n">
-        <v>114.38</v>
+        <v>85.79000000000001</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>183.71</v>
+        <v>137.78</v>
       </c>
       <c r="K51" t="n">
-        <v>-18.51</v>
+        <v>-13.89</v>
       </c>
       <c r="L51" t="n">
-        <v>184.64</v>
+        <v>138.48</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>44.87</v>
+        <v>27.48</v>
       </c>
       <c r="K52" t="n">
-        <v>-116.07</v>
+        <v>-71.09999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>124.44</v>
+        <v>76.23</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>67.14</v>
+        <v>50.35</v>
       </c>
       <c r="K53" t="n">
-        <v>-163.12</v>
+        <v>-122.34</v>
       </c>
       <c r="L53" t="n">
-        <v>176.4</v>
+        <v>132.3</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-160.53</v>
+        <v>-120.4</v>
       </c>
       <c r="K54" t="n">
-        <v>-18.85</v>
+        <v>-14.13</v>
       </c>
       <c r="L54" t="n">
-        <v>161.63</v>
+        <v>121.22</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>103.37</v>
+        <v>77.53</v>
       </c>
       <c r="K55" t="n">
-        <v>220.89</v>
+        <v>165.67</v>
       </c>
       <c r="L55" t="n">
-        <v>243.88</v>
+        <v>182.91</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>318.49</v>
+        <v>238.87</v>
       </c>
       <c r="K56" t="n">
-        <v>31</v>
+        <v>23.25</v>
       </c>
       <c r="L56" t="n">
-        <v>320</v>
+        <v>240</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>68.7</v>
+        <v>51.52</v>
       </c>
       <c r="K57" t="n">
-        <v>-162.91</v>
+        <v>-122.18</v>
       </c>
       <c r="L57" t="n">
-        <v>176.8</v>
+        <v>132.6</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-76.88</v>
+        <v>-57.66</v>
       </c>
       <c r="K58" t="n">
-        <v>-150.34</v>
+        <v>-112.76</v>
       </c>
       <c r="L58" t="n">
-        <v>168.86</v>
+        <v>126.64</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>-12.12</v>
+        <v>-9.09</v>
       </c>
       <c r="K59" t="n">
-        <v>-38.75</v>
+        <v>-29.06</v>
       </c>
       <c r="L59" t="n">
-        <v>40.6</v>
+        <v>30.45</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>1.92</v>
+        <v>1.44</v>
       </c>
       <c r="K60" t="n">
-        <v>61.02</v>
+        <v>45.77</v>
       </c>
       <c r="L60" t="n">
-        <v>61.05</v>
+        <v>45.79</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>37.24</v>
+        <v>27.93</v>
       </c>
       <c r="K61" t="n">
-        <v>57.87</v>
+        <v>43.4</v>
       </c>
       <c r="L61" t="n">
-        <v>68.81999999999999</v>
+        <v>51.61</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>60.51</v>
+        <v>45.38</v>
       </c>
       <c r="K62" t="n">
-        <v>26.87</v>
+        <v>20.15</v>
       </c>
       <c r="L62" t="n">
-        <v>66.20999999999999</v>
+        <v>49.65</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>44.64</v>
+        <v>33.48</v>
       </c>
       <c r="K63" t="n">
-        <v>-72.19</v>
+        <v>-54.15</v>
       </c>
       <c r="L63" t="n">
-        <v>84.88</v>
+        <v>63.66</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>50.25</v>
+        <v>37.69</v>
       </c>
       <c r="K64" t="n">
-        <v>38.4</v>
+        <v>28.8</v>
       </c>
       <c r="L64" t="n">
-        <v>63.24</v>
+        <v>47.43</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>67.48999999999999</v>
+        <v>50.62</v>
       </c>
       <c r="K65" t="n">
-        <v>-125.94</v>
+        <v>-94.45</v>
       </c>
       <c r="L65" t="n">
-        <v>142.88</v>
+        <v>107.16</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-65.73</v>
+        <v>-49.3</v>
       </c>
       <c r="K66" t="n">
-        <v>122.45</v>
+        <v>91.84</v>
       </c>
       <c r="L66" t="n">
-        <v>138.98</v>
+        <v>104.23</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>52.87</v>
+        <v>39.65</v>
       </c>
       <c r="K67" t="n">
-        <v>-94.34</v>
+        <v>-70.75</v>
       </c>
       <c r="L67" t="n">
-        <v>108.14</v>
+        <v>81.11</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-74.14</v>
+        <v>-55.61</v>
       </c>
       <c r="K68" t="n">
-        <v>-145.4</v>
+        <v>-109.05</v>
       </c>
       <c r="L68" t="n">
-        <v>163.21</v>
+        <v>122.41</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>51.73</v>
+        <v>38.79</v>
       </c>
       <c r="K69" t="n">
-        <v>-79.7</v>
+        <v>-59.77</v>
       </c>
       <c r="L69" t="n">
-        <v>95.01000000000001</v>
+        <v>71.26000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-96.43000000000001</v>
+        <v>-72.31999999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>-4.45</v>
+        <v>-3.34</v>
       </c>
       <c r="L70" t="n">
-        <v>96.53</v>
+        <v>72.40000000000001</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>322.19</v>
+        <v>209.61</v>
       </c>
       <c r="K71" t="n">
-        <v>-74.36</v>
+        <v>-48.38</v>
       </c>
       <c r="L71" t="n">
-        <v>330.66</v>
+        <v>215.12</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>2.36</v>
+        <v>1.77</v>
       </c>
       <c r="K72" t="n">
-        <v>-134.22</v>
+        <v>-100.67</v>
       </c>
       <c r="L72" t="n">
-        <v>134.24</v>
+        <v>100.68</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>139.78</v>
+        <v>98.38</v>
       </c>
       <c r="K73" t="n">
-        <v>31.99</v>
+        <v>22.51</v>
       </c>
       <c r="L73" t="n">
-        <v>143.4</v>
+        <v>100.92</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>48.23</v>
+        <v>36.04</v>
       </c>
       <c r="K74" t="n">
-        <v>22.55</v>
+        <v>16.85</v>
       </c>
       <c r="L74" t="n">
-        <v>53.24</v>
+        <v>39.78</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-56.43</v>
+        <v>-39.83</v>
       </c>
       <c r="K75" t="n">
-        <v>76.78</v>
+        <v>54.19</v>
       </c>
       <c r="L75" t="n">
-        <v>95.29000000000001</v>
+        <v>67.25</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>-56.53</v>
+        <v>-42.4</v>
       </c>
       <c r="K76" t="n">
-        <v>-16.46</v>
+        <v>-12.35</v>
       </c>
       <c r="L76" t="n">
-        <v>58.88</v>
+        <v>44.16</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-63.78</v>
+        <v>-47.84</v>
       </c>
       <c r="K77" t="n">
-        <v>-23.85</v>
+        <v>-17.89</v>
       </c>
       <c r="L77" t="n">
-        <v>68.09999999999999</v>
+        <v>51.07</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-41.67</v>
+        <v>-31.25</v>
       </c>
       <c r="K78" t="n">
-        <v>-30.69</v>
+        <v>-23.02</v>
       </c>
       <c r="L78" t="n">
-        <v>51.75</v>
+        <v>38.81</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>30.19</v>
+        <v>22.64</v>
       </c>
       <c r="K79" t="n">
-        <v>49.13</v>
+        <v>36.85</v>
       </c>
       <c r="L79" t="n">
-        <v>57.67</v>
+        <v>43.25</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-96.28</v>
+        <v>-72.20999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>24.99</v>
+        <v>18.74</v>
       </c>
       <c r="L80" t="n">
-        <v>99.47</v>
+        <v>74.59999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>35.22</v>
+        <v>26.42</v>
       </c>
       <c r="K81" t="n">
-        <v>-108.53</v>
+        <v>-81.40000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>114.1</v>
+        <v>85.58</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-35.56</v>
+        <v>-26.67</v>
       </c>
       <c r="K82" t="n">
-        <v>202.15</v>
+        <v>151.61</v>
       </c>
       <c r="L82" t="n">
-        <v>205.25</v>
+        <v>153.94</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>110.93</v>
+        <v>83.2</v>
       </c>
       <c r="K83" t="n">
-        <v>-156.14</v>
+        <v>-117.11</v>
       </c>
       <c r="L83" t="n">
-        <v>191.54</v>
+        <v>143.65</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-170.49</v>
+        <v>-127.87</v>
       </c>
       <c r="K84" t="n">
-        <v>-60.4</v>
+        <v>-45.3</v>
       </c>
       <c r="L84" t="n">
-        <v>180.87</v>
+        <v>135.65</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-111.39</v>
+        <v>-83.54000000000001</v>
       </c>
       <c r="K85" t="n">
-        <v>49.96</v>
+        <v>37.47</v>
       </c>
       <c r="L85" t="n">
-        <v>122.08</v>
+        <v>91.56</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>4.73</v>
+        <v>3.55</v>
       </c>
       <c r="K86" t="n">
-        <v>-276.02</v>
+        <v>-207.02</v>
       </c>
       <c r="L86" t="n">
-        <v>276.06</v>
+        <v>207.05</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>182.74</v>
+        <v>137.06</v>
       </c>
       <c r="K87" t="n">
-        <v>-148.94</v>
+        <v>-111.7</v>
       </c>
       <c r="L87" t="n">
-        <v>235.75</v>
+        <v>176.81</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-44.73</v>
+        <v>-33.55</v>
       </c>
       <c r="K88" t="n">
-        <v>352.44</v>
+        <v>264.33</v>
       </c>
       <c r="L88" t="n">
-        <v>355.27</v>
+        <v>266.45</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-27.xlsx
+++ b/output/2024-10-27.xlsx
@@ -640,13 +640,13 @@
         <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>-13.05</v>
+        <v>-12.82</v>
       </c>
       <c r="K14" t="n">
-        <v>46.47</v>
+        <v>45.66</v>
       </c>
       <c r="L14" t="n">
-        <v>48.27</v>
+        <v>47.43</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>28.89</v>
+        <v>30.66</v>
       </c>
       <c r="K15" t="n">
-        <v>2.66</v>
+        <v>2.82</v>
       </c>
       <c r="L15" t="n">
-        <v>29.01</v>
+        <v>30.79</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="K16" t="n">
-        <v>37.77</v>
+        <v>38.35</v>
       </c>
       <c r="L16" t="n">
-        <v>37.88</v>
+        <v>38.46</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-35.76</v>
+        <v>-38.02</v>
       </c>
       <c r="K17" t="n">
-        <v>17.6</v>
+        <v>18.71</v>
       </c>
       <c r="L17" t="n">
-        <v>39.85</v>
+        <v>42.37</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-60.2</v>
+        <v>-59.41</v>
       </c>
       <c r="K18" t="n">
-        <v>28.24</v>
+        <v>27.87</v>
       </c>
       <c r="L18" t="n">
-        <v>66.48999999999999</v>
+        <v>65.63</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>48.94</v>
+        <v>50.78</v>
       </c>
       <c r="K19" t="n">
-        <v>3.43</v>
+        <v>3.56</v>
       </c>
       <c r="L19" t="n">
-        <v>49.06</v>
+        <v>50.9</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>48.55</v>
+        <v>49.21</v>
       </c>
       <c r="K20" t="n">
-        <v>71.52</v>
+        <v>72.48999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>86.44</v>
+        <v>87.61</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-66.17</v>
+        <v>-68.67</v>
       </c>
       <c r="K21" t="n">
-        <v>25.77</v>
+        <v>26.74</v>
       </c>
       <c r="L21" t="n">
-        <v>71.01000000000001</v>
+        <v>73.69</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-110.25</v>
+        <v>-108.54</v>
       </c>
       <c r="K22" t="n">
-        <v>15.39</v>
+        <v>15.15</v>
       </c>
       <c r="L22" t="n">
-        <v>111.32</v>
+        <v>109.59</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>144.59</v>
+        <v>135.96</v>
       </c>
       <c r="K23" t="n">
-        <v>190.68</v>
+        <v>179.3</v>
       </c>
       <c r="L23" t="n">
-        <v>239.3</v>
+        <v>225.02</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>43.14</v>
+        <v>44.85</v>
       </c>
       <c r="K24" t="n">
-        <v>-75.58</v>
+        <v>-78.58</v>
       </c>
       <c r="L24" t="n">
-        <v>87.02</v>
+        <v>90.48</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-92.48999999999999</v>
+        <v>-95.19</v>
       </c>
       <c r="K25" t="n">
-        <v>-35.25</v>
+        <v>-36.28</v>
       </c>
       <c r="L25" t="n">
-        <v>98.98</v>
+        <v>101.87</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>240.75</v>
+        <v>232.33</v>
       </c>
       <c r="K26" t="n">
-        <v>74.67</v>
+        <v>72.05</v>
       </c>
       <c r="L26" t="n">
-        <v>252.07</v>
+        <v>243.24</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-152.51</v>
+        <v>-151.36</v>
       </c>
       <c r="K27" t="n">
-        <v>-104.75</v>
+        <v>-103.96</v>
       </c>
       <c r="L27" t="n">
-        <v>185.02</v>
+        <v>183.62</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>114.36</v>
+        <v>121.76</v>
       </c>
       <c r="K28" t="n">
-        <v>42.39</v>
+        <v>45.13</v>
       </c>
       <c r="L28" t="n">
-        <v>121.97</v>
+        <v>129.86</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>30.04</v>
+        <v>30.25</v>
       </c>
       <c r="K29" t="n">
-        <v>39.81</v>
+        <v>40.09</v>
       </c>
       <c r="L29" t="n">
-        <v>49.88</v>
+        <v>50.22</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-17.37</v>
+        <v>-17.13</v>
       </c>
       <c r="K30" t="n">
-        <v>42.8</v>
+        <v>42.21</v>
       </c>
       <c r="L30" t="n">
-        <v>46.19</v>
+        <v>45.55</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>-27.49</v>
+        <v>-29.02</v>
       </c>
       <c r="K31" t="n">
-        <v>1.23</v>
+        <v>1.3</v>
       </c>
       <c r="L31" t="n">
-        <v>27.51</v>
+        <v>29.05</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>-27.94</v>
+        <v>-29.94</v>
       </c>
       <c r="K32" t="n">
-        <v>-28.2</v>
+        <v>-30.22</v>
       </c>
       <c r="L32" t="n">
-        <v>39.69</v>
+        <v>42.54</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>58.11</v>
+        <v>57.42</v>
       </c>
       <c r="K33" t="n">
-        <v>29.16</v>
+        <v>28.81</v>
       </c>
       <c r="L33" t="n">
-        <v>65.01000000000001</v>
+        <v>64.23999999999999</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-76.45999999999999</v>
+        <v>-75.78</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.2</v>
+        <v>-0.19</v>
       </c>
       <c r="L34" t="n">
-        <v>76.45999999999999</v>
+        <v>75.78</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-25.12</v>
+        <v>-24.51</v>
       </c>
       <c r="K35" t="n">
-        <v>104.84</v>
+        <v>102.28</v>
       </c>
       <c r="L35" t="n">
-        <v>107.81</v>
+        <v>105.17</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-76.90000000000001</v>
+        <v>-77.88</v>
       </c>
       <c r="K36" t="n">
-        <v>-16.05</v>
+        <v>-16.26</v>
       </c>
       <c r="L36" t="n">
-        <v>78.56</v>
+        <v>79.56</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>14.54</v>
+        <v>15.59</v>
       </c>
       <c r="K37" t="n">
-        <v>-50.72</v>
+        <v>-54.4</v>
       </c>
       <c r="L37" t="n">
-        <v>52.77</v>
+        <v>56.59</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-81.52</v>
+        <v>-82.77</v>
       </c>
       <c r="K38" t="n">
-        <v>-60.24</v>
+        <v>-61.17</v>
       </c>
       <c r="L38" t="n">
-        <v>101.36</v>
+        <v>102.92</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-92.25</v>
+        <v>-96.15000000000001</v>
       </c>
       <c r="K39" t="n">
         <v>0.13</v>
       </c>
       <c r="L39" t="n">
-        <v>92.25</v>
+        <v>96.15000000000001</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-49.01</v>
+        <v>-52.48</v>
       </c>
       <c r="K40" t="n">
-        <v>-59.22</v>
+        <v>-63.41</v>
       </c>
       <c r="L40" t="n">
-        <v>76.87</v>
+        <v>82.31</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>137.62</v>
+        <v>140.59</v>
       </c>
       <c r="K41" t="n">
-        <v>-28.13</v>
+        <v>-28.74</v>
       </c>
       <c r="L41" t="n">
-        <v>140.47</v>
+        <v>143.5</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-189.34</v>
+        <v>-184.97</v>
       </c>
       <c r="K42" t="n">
-        <v>-54.01</v>
+        <v>-52.77</v>
       </c>
       <c r="L42" t="n">
-        <v>196.89</v>
+        <v>192.35</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-50.99</v>
+        <v>-53.89</v>
       </c>
       <c r="K43" t="n">
-        <v>108.65</v>
+        <v>114.83</v>
       </c>
       <c r="L43" t="n">
-        <v>120.02</v>
+        <v>126.85</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>30.85</v>
+        <v>30.45</v>
       </c>
       <c r="K44" t="n">
-        <v>-39.86</v>
+        <v>-39.34</v>
       </c>
       <c r="L44" t="n">
-        <v>50.4</v>
+        <v>49.75</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>33.04</v>
+        <v>34.04</v>
       </c>
       <c r="K45" t="n">
-        <v>28.87</v>
+        <v>29.75</v>
       </c>
       <c r="L45" t="n">
-        <v>43.88</v>
+        <v>45.21</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>9.02</v>
+        <v>8.74</v>
       </c>
       <c r="K46" t="n">
-        <v>-66.31999999999999</v>
+        <v>-64.27</v>
       </c>
       <c r="L46" t="n">
-        <v>66.93000000000001</v>
+        <v>64.86</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>-6.26</v>
+        <v>-6.24</v>
       </c>
       <c r="K47" t="n">
-        <v>-58.96</v>
+        <v>-58.79</v>
       </c>
       <c r="L47" t="n">
-        <v>59.29</v>
+        <v>59.12</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>38.72</v>
+        <v>40.72</v>
       </c>
       <c r="K48" t="n">
-        <v>-20.8</v>
+        <v>-21.87</v>
       </c>
       <c r="L48" t="n">
-        <v>43.95</v>
+        <v>46.22</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-57.05</v>
+        <v>-57.32</v>
       </c>
       <c r="K49" t="n">
-        <v>-18.09</v>
+        <v>-18.18</v>
       </c>
       <c r="L49" t="n">
-        <v>59.85</v>
+        <v>60.14</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>22.3</v>
+        <v>22.48</v>
       </c>
       <c r="K50" t="n">
-        <v>-82.84</v>
+        <v>-83.52</v>
       </c>
       <c r="L50" t="n">
-        <v>85.79000000000001</v>
+        <v>86.5</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>137.78</v>
+        <v>131.78</v>
       </c>
       <c r="K51" t="n">
-        <v>-13.89</v>
+        <v>-13.28</v>
       </c>
       <c r="L51" t="n">
-        <v>138.48</v>
+        <v>132.45</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>27.48</v>
+        <v>28.61</v>
       </c>
       <c r="K52" t="n">
-        <v>-71.09999999999999</v>
+        <v>-74.02</v>
       </c>
       <c r="L52" t="n">
-        <v>76.23</v>
+        <v>79.36</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>50.35</v>
+        <v>49.69</v>
       </c>
       <c r="K53" t="n">
-        <v>-122.34</v>
+        <v>-120.73</v>
       </c>
       <c r="L53" t="n">
-        <v>132.3</v>
+        <v>130.55</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-120.4</v>
+        <v>-120.65</v>
       </c>
       <c r="K54" t="n">
-        <v>-14.13</v>
+        <v>-14.16</v>
       </c>
       <c r="L54" t="n">
-        <v>121.22</v>
+        <v>121.48</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>77.53</v>
+        <v>74.20999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>165.67</v>
+        <v>158.57</v>
       </c>
       <c r="L55" t="n">
-        <v>182.91</v>
+        <v>175.07</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>238.87</v>
+        <v>230.72</v>
       </c>
       <c r="K56" t="n">
-        <v>23.25</v>
+        <v>22.45</v>
       </c>
       <c r="L56" t="n">
-        <v>240</v>
+        <v>231.81</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>51.52</v>
+        <v>54.14</v>
       </c>
       <c r="K57" t="n">
-        <v>-122.18</v>
+        <v>-128.38</v>
       </c>
       <c r="L57" t="n">
-        <v>132.6</v>
+        <v>139.33</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-57.66</v>
+        <v>-60.27</v>
       </c>
       <c r="K58" t="n">
-        <v>-112.76</v>
+        <v>-117.87</v>
       </c>
       <c r="L58" t="n">
-        <v>126.64</v>
+        <v>132.39</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>-9.09</v>
+        <v>-9.529999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>-29.06</v>
+        <v>-30.49</v>
       </c>
       <c r="L59" t="n">
-        <v>30.45</v>
+        <v>31.94</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="K60" t="n">
-        <v>45.77</v>
+        <v>45.18</v>
       </c>
       <c r="L60" t="n">
-        <v>45.79</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>27.93</v>
+        <v>27.32</v>
       </c>
       <c r="K61" t="n">
-        <v>43.4</v>
+        <v>42.45</v>
       </c>
       <c r="L61" t="n">
-        <v>51.61</v>
+        <v>50.48</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>45.38</v>
+        <v>46.2</v>
       </c>
       <c r="K62" t="n">
-        <v>20.15</v>
+        <v>20.52</v>
       </c>
       <c r="L62" t="n">
-        <v>49.65</v>
+        <v>50.55</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>33.48</v>
+        <v>33.54</v>
       </c>
       <c r="K63" t="n">
-        <v>-54.15</v>
+        <v>-54.25</v>
       </c>
       <c r="L63" t="n">
-        <v>63.66</v>
+        <v>63.78</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>37.69</v>
+        <v>38.81</v>
       </c>
       <c r="K64" t="n">
-        <v>28.8</v>
+        <v>29.66</v>
       </c>
       <c r="L64" t="n">
-        <v>47.43</v>
+        <v>48.84</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>50.62</v>
+        <v>49.69</v>
       </c>
       <c r="K65" t="n">
-        <v>-94.45</v>
+        <v>-92.72</v>
       </c>
       <c r="L65" t="n">
-        <v>107.16</v>
+        <v>105.19</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-49.3</v>
+        <v>-48.14</v>
       </c>
       <c r="K66" t="n">
-        <v>91.84</v>
+        <v>89.68000000000001</v>
       </c>
       <c r="L66" t="n">
-        <v>104.23</v>
+        <v>101.78</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>39.65</v>
+        <v>40.19</v>
       </c>
       <c r="K67" t="n">
-        <v>-70.75</v>
+        <v>-71.72</v>
       </c>
       <c r="L67" t="n">
-        <v>81.11</v>
+        <v>82.20999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-55.61</v>
+        <v>-55.2</v>
       </c>
       <c r="K68" t="n">
-        <v>-109.05</v>
+        <v>-108.25</v>
       </c>
       <c r="L68" t="n">
-        <v>122.41</v>
+        <v>121.51</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>38.79</v>
+        <v>41.59</v>
       </c>
       <c r="K69" t="n">
-        <v>-59.77</v>
+        <v>-64.08</v>
       </c>
       <c r="L69" t="n">
-        <v>71.26000000000001</v>
+        <v>76.39</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-72.31999999999999</v>
+        <v>-78.73999999999999</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.34</v>
+        <v>-3.64</v>
       </c>
       <c r="L70" t="n">
-        <v>72.40000000000001</v>
+        <v>78.81999999999999</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>209.61</v>
+        <v>204.94</v>
       </c>
       <c r="K71" t="n">
-        <v>-48.38</v>
+        <v>-47.3</v>
       </c>
       <c r="L71" t="n">
-        <v>215.12</v>
+        <v>210.33</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>1.77</v>
+        <v>1.92</v>
       </c>
       <c r="K72" t="n">
-        <v>-100.67</v>
+        <v>-109.55</v>
       </c>
       <c r="L72" t="n">
-        <v>100.68</v>
+        <v>109.57</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>98.38</v>
+        <v>104.8</v>
       </c>
       <c r="K73" t="n">
-        <v>22.51</v>
+        <v>23.98</v>
       </c>
       <c r="L73" t="n">
-        <v>100.92</v>
+        <v>107.51</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>36.04</v>
+        <v>36.69</v>
       </c>
       <c r="K74" t="n">
-        <v>16.85</v>
+        <v>17.15</v>
       </c>
       <c r="L74" t="n">
-        <v>39.78</v>
+        <v>40.5</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-39.83</v>
+        <v>-38.56</v>
       </c>
       <c r="K75" t="n">
-        <v>54.19</v>
+        <v>52.47</v>
       </c>
       <c r="L75" t="n">
-        <v>67.25</v>
+        <v>65.12</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>-42.4</v>
+        <v>-42.75</v>
       </c>
       <c r="K76" t="n">
-        <v>-12.35</v>
+        <v>-12.45</v>
       </c>
       <c r="L76" t="n">
-        <v>44.16</v>
+        <v>44.52</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-47.84</v>
+        <v>-48.96</v>
       </c>
       <c r="K77" t="n">
-        <v>-17.89</v>
+        <v>-18.31</v>
       </c>
       <c r="L77" t="n">
-        <v>51.07</v>
+        <v>52.28</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-31.25</v>
+        <v>-33.47</v>
       </c>
       <c r="K78" t="n">
-        <v>-23.02</v>
+        <v>-24.65</v>
       </c>
       <c r="L78" t="n">
-        <v>38.81</v>
+        <v>41.57</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>22.64</v>
+        <v>24.05</v>
       </c>
       <c r="K79" t="n">
-        <v>36.85</v>
+        <v>39.14</v>
       </c>
       <c r="L79" t="n">
-        <v>43.25</v>
+        <v>45.94</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-72.20999999999999</v>
+        <v>-73.67</v>
       </c>
       <c r="K80" t="n">
-        <v>18.74</v>
+        <v>19.12</v>
       </c>
       <c r="L80" t="n">
-        <v>74.59999999999999</v>
+        <v>76.11</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>26.42</v>
+        <v>26.8</v>
       </c>
       <c r="K81" t="n">
-        <v>-81.40000000000001</v>
+        <v>-82.58</v>
       </c>
       <c r="L81" t="n">
-        <v>85.58</v>
+        <v>86.81999999999999</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-26.67</v>
+        <v>-25.26</v>
       </c>
       <c r="K82" t="n">
-        <v>151.61</v>
+        <v>143.62</v>
       </c>
       <c r="L82" t="n">
-        <v>153.94</v>
+        <v>145.83</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>83.2</v>
+        <v>81.76000000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>-117.11</v>
+        <v>-115.08</v>
       </c>
       <c r="L83" t="n">
-        <v>143.65</v>
+        <v>141.16</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-127.87</v>
+        <v>-125.27</v>
       </c>
       <c r="K84" t="n">
-        <v>-45.3</v>
+        <v>-44.38</v>
       </c>
       <c r="L84" t="n">
-        <v>135.65</v>
+        <v>132.9</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-83.54000000000001</v>
+        <v>-86.59999999999999</v>
       </c>
       <c r="K85" t="n">
-        <v>37.47</v>
+        <v>38.85</v>
       </c>
       <c r="L85" t="n">
-        <v>91.56</v>
+        <v>94.92</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>3.55</v>
+        <v>3.49</v>
       </c>
       <c r="K86" t="n">
-        <v>-207.02</v>
+        <v>-203.65</v>
       </c>
       <c r="L86" t="n">
-        <v>207.05</v>
+        <v>203.68</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>137.06</v>
+        <v>138.33</v>
       </c>
       <c r="K87" t="n">
-        <v>-111.7</v>
+        <v>-112.74</v>
       </c>
       <c r="L87" t="n">
-        <v>176.81</v>
+        <v>178.45</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-33.55</v>
+        <v>-32.44</v>
       </c>
       <c r="K88" t="n">
-        <v>264.33</v>
+        <v>255.57</v>
       </c>
       <c r="L88" t="n">
-        <v>266.45</v>
+        <v>257.62</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-27.xlsx
+++ b/output/2024-10-27.xlsx
@@ -640,13 +640,13 @@
         <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>-12.82</v>
+        <v>-12.56</v>
       </c>
       <c r="K14" t="n">
-        <v>45.66</v>
+        <v>44.73</v>
       </c>
       <c r="L14" t="n">
-        <v>47.43</v>
+        <v>46.46</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>30.66</v>
+        <v>32.69</v>
       </c>
       <c r="K15" t="n">
-        <v>2.82</v>
+        <v>3.01</v>
       </c>
       <c r="L15" t="n">
-        <v>30.79</v>
+        <v>32.83</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="K16" t="n">
-        <v>38.35</v>
+        <v>39.01</v>
       </c>
       <c r="L16" t="n">
-        <v>38.46</v>
+        <v>39.12</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-38.02</v>
+        <v>-40.6</v>
       </c>
       <c r="K17" t="n">
-        <v>18.71</v>
+        <v>19.98</v>
       </c>
       <c r="L17" t="n">
-        <v>42.37</v>
+        <v>45.25</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-59.41</v>
+        <v>-58.52</v>
       </c>
       <c r="K18" t="n">
-        <v>27.87</v>
+        <v>27.45</v>
       </c>
       <c r="L18" t="n">
-        <v>65.63</v>
+        <v>64.64</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>50.78</v>
+        <v>52.88</v>
       </c>
       <c r="K19" t="n">
-        <v>3.56</v>
+        <v>3.71</v>
       </c>
       <c r="L19" t="n">
-        <v>50.9</v>
+        <v>53.01</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>49.21</v>
+        <v>49.96</v>
       </c>
       <c r="K20" t="n">
-        <v>72.48999999999999</v>
+        <v>73.59</v>
       </c>
       <c r="L20" t="n">
-        <v>87.61</v>
+        <v>88.95</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-68.67</v>
+        <v>-71.51000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>26.74</v>
+        <v>27.84</v>
       </c>
       <c r="L21" t="n">
-        <v>73.69</v>
+        <v>76.73999999999999</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-108.54</v>
+        <v>-106.58</v>
       </c>
       <c r="K22" t="n">
-        <v>15.15</v>
+        <v>14.88</v>
       </c>
       <c r="L22" t="n">
-        <v>109.59</v>
+        <v>107.62</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>135.96</v>
+        <v>126.09</v>
       </c>
       <c r="K23" t="n">
-        <v>179.3</v>
+        <v>166.29</v>
       </c>
       <c r="L23" t="n">
-        <v>225.02</v>
+        <v>208.69</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>44.85</v>
+        <v>46.81</v>
       </c>
       <c r="K24" t="n">
-        <v>-78.58</v>
+        <v>-82.01000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>90.48</v>
+        <v>94.43000000000001</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-95.19</v>
+        <v>-98.27</v>
       </c>
       <c r="K25" t="n">
-        <v>-36.28</v>
+        <v>-37.46</v>
       </c>
       <c r="L25" t="n">
-        <v>101.87</v>
+        <v>105.17</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>232.33</v>
+        <v>222.7</v>
       </c>
       <c r="K26" t="n">
-        <v>72.05</v>
+        <v>69.06999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>243.24</v>
+        <v>233.16</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-151.36</v>
+        <v>-150.04</v>
       </c>
       <c r="K27" t="n">
-        <v>-103.96</v>
+        <v>-103.05</v>
       </c>
       <c r="L27" t="n">
-        <v>183.62</v>
+        <v>182.02</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>121.76</v>
+        <v>130.22</v>
       </c>
       <c r="K28" t="n">
-        <v>45.13</v>
+        <v>48.26</v>
       </c>
       <c r="L28" t="n">
-        <v>129.86</v>
+        <v>138.87</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>30.25</v>
+        <v>30.49</v>
       </c>
       <c r="K29" t="n">
-        <v>40.09</v>
+        <v>40.41</v>
       </c>
       <c r="L29" t="n">
-        <v>50.22</v>
+        <v>50.62</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-17.13</v>
+        <v>-16.86</v>
       </c>
       <c r="K30" t="n">
-        <v>42.21</v>
+        <v>41.54</v>
       </c>
       <c r="L30" t="n">
-        <v>45.55</v>
+        <v>44.83</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>-29.02</v>
+        <v>-30.78</v>
       </c>
       <c r="K31" t="n">
-        <v>1.3</v>
+        <v>1.38</v>
       </c>
       <c r="L31" t="n">
-        <v>29.05</v>
+        <v>30.81</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>-29.94</v>
+        <v>-32.23</v>
       </c>
       <c r="K32" t="n">
-        <v>-30.22</v>
+        <v>-32.53</v>
       </c>
       <c r="L32" t="n">
-        <v>42.54</v>
+        <v>45.79</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>57.42</v>
+        <v>56.63</v>
       </c>
       <c r="K33" t="n">
-        <v>28.81</v>
+        <v>28.41</v>
       </c>
       <c r="L33" t="n">
-        <v>64.23999999999999</v>
+        <v>63.36</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-75.78</v>
+        <v>-75.01000000000001</v>
       </c>
       <c r="K34" t="n">
         <v>-0.19</v>
       </c>
       <c r="L34" t="n">
-        <v>75.78</v>
+        <v>75.01000000000001</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-24.51</v>
+        <v>-23.8</v>
       </c>
       <c r="K35" t="n">
-        <v>102.28</v>
+        <v>99.34999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>105.17</v>
+        <v>102.16</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-77.88</v>
+        <v>-79</v>
       </c>
       <c r="K36" t="n">
-        <v>-16.26</v>
+        <v>-16.49</v>
       </c>
       <c r="L36" t="n">
-        <v>79.56</v>
+        <v>80.7</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>15.59</v>
+        <v>16.8</v>
       </c>
       <c r="K37" t="n">
-        <v>-54.4</v>
+        <v>-58.61</v>
       </c>
       <c r="L37" t="n">
-        <v>56.59</v>
+        <v>60.97</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-82.77</v>
+        <v>-84.20999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>-61.17</v>
+        <v>-62.23</v>
       </c>
       <c r="L38" t="n">
-        <v>102.92</v>
+        <v>104.71</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-96.15000000000001</v>
+        <v>-100.59</v>
       </c>
       <c r="K39" t="n">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="L39" t="n">
-        <v>96.15000000000001</v>
+        <v>100.59</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-52.48</v>
+        <v>-56.45</v>
       </c>
       <c r="K40" t="n">
-        <v>-63.41</v>
+        <v>-68.2</v>
       </c>
       <c r="L40" t="n">
-        <v>82.31</v>
+        <v>88.53</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>140.59</v>
+        <v>143.99</v>
       </c>
       <c r="K41" t="n">
-        <v>-28.74</v>
+        <v>-29.43</v>
       </c>
       <c r="L41" t="n">
-        <v>143.5</v>
+        <v>146.97</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-184.97</v>
+        <v>-179.98</v>
       </c>
       <c r="K42" t="n">
-        <v>-52.77</v>
+        <v>-51.34</v>
       </c>
       <c r="L42" t="n">
-        <v>192.35</v>
+        <v>187.16</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-53.89</v>
+        <v>-57.2</v>
       </c>
       <c r="K43" t="n">
-        <v>114.83</v>
+        <v>121.89</v>
       </c>
       <c r="L43" t="n">
-        <v>126.85</v>
+        <v>134.64</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>30.45</v>
+        <v>29.99</v>
       </c>
       <c r="K44" t="n">
-        <v>-39.34</v>
+        <v>-38.75</v>
       </c>
       <c r="L44" t="n">
-        <v>49.75</v>
+        <v>49</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>34.04</v>
+        <v>35.19</v>
       </c>
       <c r="K45" t="n">
-        <v>29.75</v>
+        <v>30.74</v>
       </c>
       <c r="L45" t="n">
-        <v>45.21</v>
+        <v>46.73</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>8.74</v>
+        <v>8.42</v>
       </c>
       <c r="K46" t="n">
-        <v>-64.27</v>
+        <v>-61.92</v>
       </c>
       <c r="L46" t="n">
-        <v>64.86</v>
+        <v>62.49</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>-6.24</v>
+        <v>-6.22</v>
       </c>
       <c r="K47" t="n">
-        <v>-58.79</v>
+        <v>-58.6</v>
       </c>
       <c r="L47" t="n">
-        <v>59.12</v>
+        <v>58.93</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>40.72</v>
+        <v>43</v>
       </c>
       <c r="K48" t="n">
-        <v>-21.87</v>
+        <v>-23.1</v>
       </c>
       <c r="L48" t="n">
-        <v>46.22</v>
+        <v>48.81</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-57.32</v>
+        <v>-57.64</v>
       </c>
       <c r="K49" t="n">
-        <v>-18.18</v>
+        <v>-18.28</v>
       </c>
       <c r="L49" t="n">
-        <v>60.14</v>
+        <v>60.47</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>22.48</v>
+        <v>22.69</v>
       </c>
       <c r="K50" t="n">
-        <v>-83.52</v>
+        <v>-84.31</v>
       </c>
       <c r="L50" t="n">
-        <v>86.5</v>
+        <v>87.31</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>131.78</v>
+        <v>124.93</v>
       </c>
       <c r="K51" t="n">
-        <v>-13.28</v>
+        <v>-12.59</v>
       </c>
       <c r="L51" t="n">
-        <v>132.45</v>
+        <v>125.56</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>28.61</v>
+        <v>29.9</v>
       </c>
       <c r="K52" t="n">
-        <v>-74.02</v>
+        <v>-77.36</v>
       </c>
       <c r="L52" t="n">
-        <v>79.36</v>
+        <v>82.94</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>49.69</v>
+        <v>48.93</v>
       </c>
       <c r="K53" t="n">
-        <v>-120.73</v>
+        <v>-118.88</v>
       </c>
       <c r="L53" t="n">
-        <v>130.55</v>
+        <v>128.56</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-120.65</v>
+        <v>-120.94</v>
       </c>
       <c r="K54" t="n">
-        <v>-14.16</v>
+        <v>-14.2</v>
       </c>
       <c r="L54" t="n">
-        <v>121.48</v>
+        <v>121.77</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>74.20999999999999</v>
+        <v>70.41</v>
       </c>
       <c r="K55" t="n">
-        <v>158.57</v>
+        <v>150.45</v>
       </c>
       <c r="L55" t="n">
-        <v>175.07</v>
+        <v>166.11</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>230.72</v>
+        <v>221.4</v>
       </c>
       <c r="K56" t="n">
-        <v>22.45</v>
+        <v>21.55</v>
       </c>
       <c r="L56" t="n">
-        <v>231.81</v>
+        <v>222.45</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>54.14</v>
+        <v>57.12</v>
       </c>
       <c r="K57" t="n">
-        <v>-128.38</v>
+        <v>-135.46</v>
       </c>
       <c r="L57" t="n">
-        <v>139.33</v>
+        <v>147.01</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-60.27</v>
+        <v>-63.26</v>
       </c>
       <c r="K58" t="n">
-        <v>-117.87</v>
+        <v>-123.72</v>
       </c>
       <c r="L58" t="n">
-        <v>132.39</v>
+        <v>138.95</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>-9.529999999999999</v>
+        <v>-10.04</v>
       </c>
       <c r="K59" t="n">
-        <v>-30.49</v>
+        <v>-32.11</v>
       </c>
       <c r="L59" t="n">
-        <v>31.94</v>
+        <v>33.65</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="K60" t="n">
-        <v>45.18</v>
+        <v>44.5</v>
       </c>
       <c r="L60" t="n">
-        <v>45.2</v>
+        <v>44.53</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>27.32</v>
+        <v>26.62</v>
       </c>
       <c r="K61" t="n">
-        <v>42.45</v>
+        <v>41.37</v>
       </c>
       <c r="L61" t="n">
-        <v>50.48</v>
+        <v>49.19</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>46.2</v>
+        <v>47.14</v>
       </c>
       <c r="K62" t="n">
-        <v>20.52</v>
+        <v>20.93</v>
       </c>
       <c r="L62" t="n">
-        <v>50.55</v>
+        <v>51.58</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>33.54</v>
+        <v>33.61</v>
       </c>
       <c r="K63" t="n">
-        <v>-54.25</v>
+        <v>-54.36</v>
       </c>
       <c r="L63" t="n">
-        <v>63.78</v>
+        <v>63.91</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>38.81</v>
+        <v>40.09</v>
       </c>
       <c r="K64" t="n">
-        <v>29.66</v>
+        <v>30.64</v>
       </c>
       <c r="L64" t="n">
-        <v>48.84</v>
+        <v>50.46</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>49.69</v>
+        <v>48.63</v>
       </c>
       <c r="K65" t="n">
-        <v>-92.72</v>
+        <v>-90.73999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>105.19</v>
+        <v>102.95</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-48.14</v>
+        <v>-46.82</v>
       </c>
       <c r="K66" t="n">
-        <v>89.68000000000001</v>
+        <v>87.22</v>
       </c>
       <c r="L66" t="n">
-        <v>101.78</v>
+        <v>98.98999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>40.19</v>
+        <v>40.81</v>
       </c>
       <c r="K67" t="n">
-        <v>-71.72</v>
+        <v>-72.81999999999999</v>
       </c>
       <c r="L67" t="n">
-        <v>82.20999999999999</v>
+        <v>83.48</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-55.2</v>
+        <v>-54.73</v>
       </c>
       <c r="K68" t="n">
-        <v>-108.25</v>
+        <v>-107.33</v>
       </c>
       <c r="L68" t="n">
-        <v>121.51</v>
+        <v>120.48</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>41.59</v>
+        <v>44.79</v>
       </c>
       <c r="K69" t="n">
-        <v>-64.08</v>
+        <v>-69</v>
       </c>
       <c r="L69" t="n">
-        <v>76.39</v>
+        <v>82.26000000000001</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-78.73999999999999</v>
+        <v>-86.08</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.64</v>
+        <v>-3.97</v>
       </c>
       <c r="L70" t="n">
-        <v>78.81999999999999</v>
+        <v>86.17</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>204.94</v>
+        <v>199.6</v>
       </c>
       <c r="K71" t="n">
-        <v>-47.3</v>
+        <v>-46.07</v>
       </c>
       <c r="L71" t="n">
-        <v>210.33</v>
+        <v>204.84</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>1.92</v>
+        <v>2.1</v>
       </c>
       <c r="K72" t="n">
-        <v>-109.55</v>
+        <v>-119.71</v>
       </c>
       <c r="L72" t="n">
-        <v>109.57</v>
+        <v>119.73</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>104.8</v>
+        <v>115.45</v>
       </c>
       <c r="K73" t="n">
-        <v>23.98</v>
+        <v>26.42</v>
       </c>
       <c r="L73" t="n">
-        <v>107.51</v>
+        <v>118.44</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>36.69</v>
+        <v>37.43</v>
       </c>
       <c r="K74" t="n">
-        <v>17.15</v>
+        <v>17.5</v>
       </c>
       <c r="L74" t="n">
-        <v>40.5</v>
+        <v>41.32</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-38.56</v>
+        <v>-37.12</v>
       </c>
       <c r="K75" t="n">
-        <v>52.47</v>
+        <v>50.5</v>
       </c>
       <c r="L75" t="n">
-        <v>65.12</v>
+        <v>62.68</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>-42.75</v>
+        <v>-43.15</v>
       </c>
       <c r="K76" t="n">
-        <v>-12.45</v>
+        <v>-12.57</v>
       </c>
       <c r="L76" t="n">
-        <v>44.52</v>
+        <v>44.94</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-48.96</v>
+        <v>-50.25</v>
       </c>
       <c r="K77" t="n">
-        <v>-18.31</v>
+        <v>-18.79</v>
       </c>
       <c r="L77" t="n">
-        <v>52.28</v>
+        <v>53.65</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-33.47</v>
+        <v>-36.01</v>
       </c>
       <c r="K78" t="n">
-        <v>-24.65</v>
+        <v>-26.52</v>
       </c>
       <c r="L78" t="n">
-        <v>41.57</v>
+        <v>44.72</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>24.05</v>
+        <v>25.66</v>
       </c>
       <c r="K79" t="n">
-        <v>39.14</v>
+        <v>41.76</v>
       </c>
       <c r="L79" t="n">
-        <v>45.94</v>
+        <v>49.02</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-73.67</v>
+        <v>-75.34</v>
       </c>
       <c r="K80" t="n">
-        <v>19.12</v>
+        <v>19.56</v>
       </c>
       <c r="L80" t="n">
-        <v>76.11</v>
+        <v>77.84</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>26.8</v>
+        <v>27.24</v>
       </c>
       <c r="K81" t="n">
-        <v>-82.58</v>
+        <v>-83.92</v>
       </c>
       <c r="L81" t="n">
-        <v>86.81999999999999</v>
+        <v>88.23</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-25.26</v>
+        <v>-23.66</v>
       </c>
       <c r="K82" t="n">
-        <v>143.62</v>
+        <v>134.49</v>
       </c>
       <c r="L82" t="n">
-        <v>145.83</v>
+        <v>136.55</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>81.76000000000001</v>
+        <v>80.11</v>
       </c>
       <c r="K83" t="n">
-        <v>-115.08</v>
+        <v>-112.76</v>
       </c>
       <c r="L83" t="n">
-        <v>141.16</v>
+        <v>138.32</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-125.27</v>
+        <v>-122.31</v>
       </c>
       <c r="K84" t="n">
-        <v>-44.38</v>
+        <v>-43.33</v>
       </c>
       <c r="L84" t="n">
-        <v>132.9</v>
+        <v>129.76</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-86.59999999999999</v>
+        <v>-90.09999999999999</v>
       </c>
       <c r="K85" t="n">
-        <v>38.85</v>
+        <v>40.42</v>
       </c>
       <c r="L85" t="n">
-        <v>94.92</v>
+        <v>98.75</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>3.49</v>
+        <v>3.43</v>
       </c>
       <c r="K86" t="n">
-        <v>-203.65</v>
+        <v>-199.81</v>
       </c>
       <c r="L86" t="n">
-        <v>203.68</v>
+        <v>199.84</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>138.33</v>
+        <v>139.78</v>
       </c>
       <c r="K87" t="n">
-        <v>-112.74</v>
+        <v>-113.92</v>
       </c>
       <c r="L87" t="n">
-        <v>178.45</v>
+        <v>180.32</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-32.44</v>
+        <v>-31.17</v>
       </c>
       <c r="K88" t="n">
-        <v>255.57</v>
+        <v>245.56</v>
       </c>
       <c r="L88" t="n">
-        <v>257.62</v>
+        <v>247.53</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-27.xlsx
+++ b/output/2024-10-27.xlsx
@@ -628,25 +628,25 @@
         <v>1.42</v>
       </c>
       <c r="F14" t="n">
-        <v>4.33</v>
+        <v>3.58</v>
       </c>
       <c r="G14" t="n">
-        <v>217.8</v>
+        <v>208.1</v>
       </c>
       <c r="H14" t="n">
-        <v>72.90000000000001</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>-12.56</v>
+        <v>-13.88</v>
       </c>
       <c r="K14" t="n">
-        <v>44.73</v>
+        <v>48.93</v>
       </c>
       <c r="L14" t="n">
-        <v>46.46</v>
+        <v>50.86</v>
       </c>
     </row>
     <row r="15">
@@ -670,25 +670,25 @@
         <v>1.29</v>
       </c>
       <c r="F15" t="n">
-        <v>4.2</v>
+        <v>4.38</v>
       </c>
       <c r="G15" t="n">
-        <v>201.6</v>
+        <v>205.4</v>
       </c>
       <c r="H15" t="n">
-        <v>75.8</v>
+        <v>70.8</v>
       </c>
       <c r="I15" t="n">
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>32.69</v>
+        <v>40.09</v>
       </c>
       <c r="K15" t="n">
-        <v>3.01</v>
+        <v>3.24</v>
       </c>
       <c r="L15" t="n">
-        <v>32.83</v>
+        <v>40.22</v>
       </c>
     </row>
     <row r="16">
@@ -712,25 +712,25 @@
         <v>1.19</v>
       </c>
       <c r="F16" t="n">
-        <v>4.66</v>
+        <v>2.03</v>
       </c>
       <c r="G16" t="n">
-        <v>219.1</v>
+        <v>214.5</v>
       </c>
       <c r="H16" t="n">
-        <v>70.8</v>
+        <v>79.5</v>
       </c>
       <c r="I16" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>2.93</v>
+        <v>3.12</v>
       </c>
       <c r="K16" t="n">
-        <v>39.01</v>
+        <v>43.13</v>
       </c>
       <c r="L16" t="n">
-        <v>39.12</v>
+        <v>43.24</v>
       </c>
     </row>
     <row r="17">
@@ -754,25 +754,25 @@
         <v>1.33</v>
       </c>
       <c r="F17" t="n">
-        <v>4.84</v>
+        <v>4.94</v>
       </c>
       <c r="G17" t="n">
-        <v>220.6</v>
+        <v>218.2</v>
       </c>
       <c r="H17" t="n">
-        <v>71.7</v>
+        <v>80.3</v>
       </c>
       <c r="I17" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>-40.6</v>
+        <v>-51.95</v>
       </c>
       <c r="K17" t="n">
-        <v>19.98</v>
+        <v>23.49</v>
       </c>
       <c r="L17" t="n">
-        <v>45.25</v>
+        <v>57.01</v>
       </c>
     </row>
     <row r="18">
@@ -796,25 +796,25 @@
         <v>1.33</v>
       </c>
       <c r="F18" t="n">
-        <v>4.16</v>
+        <v>4.68</v>
       </c>
       <c r="G18" t="n">
-        <v>199.2</v>
+        <v>204.7</v>
       </c>
       <c r="H18" t="n">
-        <v>75.8</v>
+        <v>69.59999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J18" t="n">
-        <v>-58.52</v>
+        <v>-72.36</v>
       </c>
       <c r="K18" t="n">
-        <v>27.45</v>
+        <v>32.96</v>
       </c>
       <c r="L18" t="n">
-        <v>64.64</v>
+        <v>79.51000000000001</v>
       </c>
     </row>
     <row r="19">
@@ -838,25 +838,25 @@
         <v>1.33</v>
       </c>
       <c r="F19" t="n">
-        <v>4.32</v>
+        <v>3.32</v>
       </c>
       <c r="G19" t="n">
-        <v>200.2</v>
+        <v>207.7</v>
       </c>
       <c r="H19" t="n">
-        <v>72.09999999999999</v>
+        <v>70.09999999999999</v>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>52.88</v>
+        <v>55.86</v>
       </c>
       <c r="K19" t="n">
-        <v>3.71</v>
+        <v>2.89</v>
       </c>
       <c r="L19" t="n">
-        <v>53.01</v>
+        <v>55.93</v>
       </c>
     </row>
     <row r="20">
@@ -880,25 +880,25 @@
         <v>1.67</v>
       </c>
       <c r="F20" t="n">
-        <v>4.51</v>
+        <v>2.99</v>
       </c>
       <c r="G20" t="n">
-        <v>198.8</v>
+        <v>211.7</v>
       </c>
       <c r="H20" t="n">
-        <v>69.8</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J20" t="n">
-        <v>49.96</v>
+        <v>49.35</v>
       </c>
       <c r="K20" t="n">
-        <v>73.59</v>
+        <v>73.73999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>88.95</v>
+        <v>88.73</v>
       </c>
     </row>
     <row r="21">
@@ -922,25 +922,25 @@
         <v>1.51</v>
       </c>
       <c r="F21" t="n">
-        <v>4.24</v>
+        <v>4.94</v>
       </c>
       <c r="G21" t="n">
-        <v>202.5</v>
+        <v>206.1</v>
       </c>
       <c r="H21" t="n">
-        <v>75</v>
+        <v>71.3</v>
       </c>
       <c r="I21" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-71.51000000000001</v>
+        <v>-91.91</v>
       </c>
       <c r="K21" t="n">
-        <v>27.84</v>
+        <v>28.12</v>
       </c>
       <c r="L21" t="n">
-        <v>76.73999999999999</v>
+        <v>96.11</v>
       </c>
     </row>
     <row r="22">
@@ -964,25 +964,25 @@
         <v>1.58</v>
       </c>
       <c r="F22" t="n">
-        <v>4.08</v>
+        <v>4.64</v>
       </c>
       <c r="G22" t="n">
-        <v>209.3</v>
+        <v>203.1</v>
       </c>
       <c r="H22" t="n">
-        <v>74</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-106.58</v>
+        <v>-107.51</v>
       </c>
       <c r="K22" t="n">
-        <v>14.88</v>
+        <v>11.03</v>
       </c>
       <c r="L22" t="n">
-        <v>107.62</v>
+        <v>108.07</v>
       </c>
     </row>
     <row r="23">
@@ -1006,25 +1006,25 @@
         <v>1.49</v>
       </c>
       <c r="F23" t="n">
-        <v>4.66</v>
+        <v>2.71</v>
       </c>
       <c r="G23" t="n">
-        <v>218.1</v>
+        <v>214.6</v>
       </c>
       <c r="H23" t="n">
-        <v>74</v>
+        <v>79.09999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>126.09</v>
+        <v>112.9</v>
       </c>
       <c r="K23" t="n">
-        <v>166.29</v>
+        <v>148.14</v>
       </c>
       <c r="L23" t="n">
-        <v>208.69</v>
+        <v>186.26</v>
       </c>
     </row>
     <row r="24">
@@ -1048,25 +1048,25 @@
         <v>1.33</v>
       </c>
       <c r="F24" t="n">
-        <v>4.64</v>
+        <v>4.94</v>
       </c>
       <c r="G24" t="n">
-        <v>200.1</v>
+        <v>214.2</v>
       </c>
       <c r="H24" t="n">
-        <v>76.5</v>
+        <v>70</v>
       </c>
       <c r="I24" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>46.81</v>
+        <v>45.51</v>
       </c>
       <c r="K24" t="n">
-        <v>-82.01000000000001</v>
+        <v>-106.93</v>
       </c>
       <c r="L24" t="n">
-        <v>94.43000000000001</v>
+        <v>116.21</v>
       </c>
     </row>
     <row r="25">
@@ -1090,25 +1090,25 @@
         <v>1.29</v>
       </c>
       <c r="F25" t="n">
-        <v>4.44</v>
+        <v>4.94</v>
       </c>
       <c r="G25" t="n">
-        <v>212.8</v>
+        <v>210.2</v>
       </c>
       <c r="H25" t="n">
-        <v>77.5</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I25" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>-98.27</v>
+        <v>-115.55</v>
       </c>
       <c r="K25" t="n">
-        <v>-37.46</v>
+        <v>-52.54</v>
       </c>
       <c r="L25" t="n">
-        <v>105.17</v>
+        <v>126.93</v>
       </c>
     </row>
     <row r="26">
@@ -1132,25 +1132,25 @@
         <v>1.26</v>
       </c>
       <c r="F26" t="n">
-        <v>4.32</v>
+        <v>1.9</v>
       </c>
       <c r="G26" t="n">
         <v>207.8</v>
       </c>
       <c r="H26" t="n">
-        <v>69.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="I26" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>222.7</v>
+        <v>203.27</v>
       </c>
       <c r="K26" t="n">
-        <v>69.06999999999999</v>
+        <v>53.22</v>
       </c>
       <c r="L26" t="n">
-        <v>233.16</v>
+        <v>210.12</v>
       </c>
     </row>
     <row r="27">
@@ -1174,25 +1174,25 @@
         <v>1.39</v>
       </c>
       <c r="F27" t="n">
-        <v>4.62</v>
+        <v>1.69</v>
       </c>
       <c r="G27" t="n">
-        <v>200.3</v>
+        <v>213.9</v>
       </c>
       <c r="H27" t="n">
-        <v>65.40000000000001</v>
+        <v>70.2</v>
       </c>
       <c r="I27" t="n">
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-150.04</v>
+        <v>-153.46</v>
       </c>
       <c r="K27" t="n">
-        <v>-103.05</v>
+        <v>-111.1</v>
       </c>
       <c r="L27" t="n">
-        <v>182.02</v>
+        <v>189.45</v>
       </c>
     </row>
     <row r="28">
@@ -1216,25 +1216,25 @@
         <v>1.25</v>
       </c>
       <c r="F28" t="n">
-        <v>5.01</v>
+        <v>4.94</v>
       </c>
       <c r="G28" t="n">
-        <v>206.3</v>
+        <v>221.6</v>
       </c>
       <c r="H28" t="n">
-        <v>79.90000000000001</v>
+        <v>73.09999999999999</v>
       </c>
       <c r="I28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>130.22</v>
+        <v>168.98</v>
       </c>
       <c r="K28" t="n">
-        <v>48.26</v>
+        <v>39.52</v>
       </c>
       <c r="L28" t="n">
-        <v>138.87</v>
+        <v>173.54</v>
       </c>
     </row>
     <row r="29">
@@ -1258,25 +1258,25 @@
         <v>2.48</v>
       </c>
       <c r="F29" t="n">
-        <v>4.26</v>
+        <v>4.94</v>
       </c>
       <c r="G29" t="n">
-        <v>213.3</v>
+        <v>206.6</v>
       </c>
       <c r="H29" t="n">
-        <v>69.3</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I29" t="n">
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>30.49</v>
+        <v>32.51</v>
       </c>
       <c r="K29" t="n">
-        <v>40.41</v>
+        <v>42.72</v>
       </c>
       <c r="L29" t="n">
-        <v>50.62</v>
+        <v>53.68</v>
       </c>
     </row>
     <row r="30">
@@ -1300,25 +1300,25 @@
         <v>1.38</v>
       </c>
       <c r="F30" t="n">
-        <v>4.2</v>
+        <v>1.68</v>
       </c>
       <c r="G30" t="n">
-        <v>193</v>
+        <v>205.5</v>
       </c>
       <c r="H30" t="n">
-        <v>68.2</v>
+        <v>66.5</v>
       </c>
       <c r="I30" t="n">
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-16.86</v>
+        <v>-16.83</v>
       </c>
       <c r="K30" t="n">
-        <v>41.54</v>
+        <v>40.9</v>
       </c>
       <c r="L30" t="n">
-        <v>44.83</v>
+        <v>44.23</v>
       </c>
     </row>
     <row r="31">
@@ -1342,25 +1342,25 @@
         <v>1.42</v>
       </c>
       <c r="F31" t="n">
-        <v>4.25</v>
+        <v>3.65</v>
       </c>
       <c r="G31" t="n">
-        <v>199.7</v>
+        <v>206.4</v>
       </c>
       <c r="H31" t="n">
-        <v>77.59999999999999</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I31" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-30.78</v>
+        <v>-39.56</v>
       </c>
       <c r="K31" t="n">
-        <v>1.38</v>
+        <v>1.3</v>
       </c>
       <c r="L31" t="n">
-        <v>30.81</v>
+        <v>39.58</v>
       </c>
     </row>
     <row r="32">
@@ -1384,25 +1384,25 @@
         <v>1.44</v>
       </c>
       <c r="F32" t="n">
-        <v>4.37</v>
+        <v>4.22</v>
       </c>
       <c r="G32" t="n">
-        <v>211.8</v>
+        <v>208.8</v>
       </c>
       <c r="H32" t="n">
-        <v>73.7</v>
+        <v>75.90000000000001</v>
       </c>
       <c r="I32" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>-32.23</v>
+        <v>-33.92</v>
       </c>
       <c r="K32" t="n">
-        <v>-32.53</v>
+        <v>-35.12</v>
       </c>
       <c r="L32" t="n">
-        <v>45.79</v>
+        <v>48.83</v>
       </c>
     </row>
     <row r="33">
@@ -1426,25 +1426,25 @@
         <v>1.56</v>
       </c>
       <c r="F33" t="n">
-        <v>4.91</v>
+        <v>4.94</v>
       </c>
       <c r="G33" t="n">
-        <v>199.6</v>
+        <v>219.7</v>
       </c>
       <c r="H33" t="n">
-        <v>83.09999999999999</v>
+        <v>69.8</v>
       </c>
       <c r="I33" t="n">
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>56.63</v>
+        <v>63.99</v>
       </c>
       <c r="K33" t="n">
-        <v>28.41</v>
+        <v>31.98</v>
       </c>
       <c r="L33" t="n">
-        <v>63.36</v>
+        <v>71.54000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1468,25 +1468,25 @@
         <v>2.41</v>
       </c>
       <c r="F34" t="n">
-        <v>4.23</v>
+        <v>4.94</v>
       </c>
       <c r="G34" t="n">
-        <v>207.5</v>
+        <v>205.9</v>
       </c>
       <c r="H34" t="n">
-        <v>70.8</v>
+        <v>73.7</v>
       </c>
       <c r="I34" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-75.01000000000001</v>
+        <v>-74.54000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.19</v>
+        <v>-1.64</v>
       </c>
       <c r="L34" t="n">
-        <v>75.01000000000001</v>
+        <v>74.56</v>
       </c>
     </row>
     <row r="35">
@@ -1510,25 +1510,25 @@
         <v>1.65</v>
       </c>
       <c r="F35" t="n">
-        <v>4.27</v>
+        <v>4.93</v>
       </c>
       <c r="G35" t="n">
-        <v>202.8</v>
+        <v>206.7</v>
       </c>
       <c r="H35" t="n">
-        <v>83.90000000000001</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="J35" t="n">
-        <v>-23.8</v>
+        <v>-30.49</v>
       </c>
       <c r="K35" t="n">
-        <v>99.34999999999999</v>
+        <v>115.18</v>
       </c>
       <c r="L35" t="n">
-        <v>102.16</v>
+        <v>119.15</v>
       </c>
     </row>
     <row r="36">
@@ -1552,25 +1552,25 @@
         <v>1.43</v>
       </c>
       <c r="F36" t="n">
-        <v>4.63</v>
+        <v>4.94</v>
       </c>
       <c r="G36" t="n">
-        <v>210.5</v>
+        <v>214</v>
       </c>
       <c r="H36" t="n">
-        <v>77.2</v>
+        <v>75.3</v>
       </c>
       <c r="I36" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>-79</v>
+        <v>-89.67</v>
       </c>
       <c r="K36" t="n">
-        <v>-16.49</v>
+        <v>-21.78</v>
       </c>
       <c r="L36" t="n">
-        <v>80.7</v>
+        <v>92.28</v>
       </c>
     </row>
     <row r="37">
@@ -1594,25 +1594,25 @@
         <v>1.56</v>
       </c>
       <c r="F37" t="n">
-        <v>4.3</v>
+        <v>4.94</v>
       </c>
       <c r="G37" t="n">
-        <v>210.8</v>
+        <v>207.4</v>
       </c>
       <c r="H37" t="n">
-        <v>71.59999999999999</v>
+        <v>75.40000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J37" t="n">
-        <v>16.8</v>
+        <v>14.8</v>
       </c>
       <c r="K37" t="n">
-        <v>-58.61</v>
+        <v>-72.91</v>
       </c>
       <c r="L37" t="n">
-        <v>60.97</v>
+        <v>74.40000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1636,25 +1636,25 @@
         <v>1.57</v>
       </c>
       <c r="F38" t="n">
-        <v>3.91</v>
+        <v>4.94</v>
       </c>
       <c r="G38" t="n">
-        <v>194.3</v>
+        <v>199.7</v>
       </c>
       <c r="H38" t="n">
-        <v>75.7</v>
+        <v>67.2</v>
       </c>
       <c r="I38" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>-84.20999999999999</v>
+        <v>-93.01000000000001</v>
       </c>
       <c r="K38" t="n">
-        <v>-62.23</v>
+        <v>-76.13</v>
       </c>
       <c r="L38" t="n">
-        <v>104.71</v>
+        <v>120.2</v>
       </c>
     </row>
     <row r="39">
@@ -1678,25 +1678,25 @@
         <v>1.62</v>
       </c>
       <c r="F39" t="n">
-        <v>4.29</v>
+        <v>4.09</v>
       </c>
       <c r="G39" t="n">
-        <v>210</v>
+        <v>207.1</v>
       </c>
       <c r="H39" t="n">
-        <v>76.09999999999999</v>
+        <v>75</v>
       </c>
       <c r="I39" t="n">
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-100.59</v>
+        <v>-114.95</v>
       </c>
       <c r="K39" t="n">
-        <v>0.14</v>
+        <v>-15.19</v>
       </c>
       <c r="L39" t="n">
-        <v>100.59</v>
+        <v>115.95</v>
       </c>
     </row>
     <row r="40">
@@ -1720,25 +1720,25 @@
         <v>1.35</v>
       </c>
       <c r="F40" t="n">
-        <v>4.33</v>
+        <v>1.65</v>
       </c>
       <c r="G40" t="n">
-        <v>199.5</v>
+        <v>208.1</v>
       </c>
       <c r="H40" t="n">
-        <v>68.3</v>
+        <v>69.8</v>
       </c>
       <c r="I40" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>-56.45</v>
+        <v>-58.47</v>
       </c>
       <c r="K40" t="n">
-        <v>-68.2</v>
+        <v>-73.63</v>
       </c>
       <c r="L40" t="n">
-        <v>88.53</v>
+        <v>94.03</v>
       </c>
     </row>
     <row r="41">
@@ -1762,25 +1762,25 @@
         <v>1.75</v>
       </c>
       <c r="F41" t="n">
-        <v>4.51</v>
+        <v>3.06</v>
       </c>
       <c r="G41" t="n">
-        <v>206.8</v>
+        <v>211.5</v>
       </c>
       <c r="H41" t="n">
-        <v>70.3</v>
+        <v>73.40000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>143.99</v>
+        <v>154.52</v>
       </c>
       <c r="K41" t="n">
-        <v>-29.43</v>
+        <v>-64.09</v>
       </c>
       <c r="L41" t="n">
-        <v>146.97</v>
+        <v>167.28</v>
       </c>
     </row>
     <row r="42">
@@ -1804,25 +1804,25 @@
         <v>1.45</v>
       </c>
       <c r="F42" t="n">
-        <v>4.47</v>
+        <v>1.75</v>
       </c>
       <c r="G42" t="n">
-        <v>207.9</v>
+        <v>210.8</v>
       </c>
       <c r="H42" t="n">
-        <v>62.6</v>
+        <v>74</v>
       </c>
       <c r="I42" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-179.98</v>
+        <v>-201.56</v>
       </c>
       <c r="K42" t="n">
-        <v>-51.34</v>
+        <v>-69.20999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>187.16</v>
+        <v>213.11</v>
       </c>
     </row>
     <row r="43">
@@ -1846,25 +1846,25 @@
         <v>1.32</v>
       </c>
       <c r="F43" t="n">
-        <v>4.09</v>
+        <v>3.62</v>
       </c>
       <c r="G43" t="n">
-        <v>217</v>
+        <v>203.1</v>
       </c>
       <c r="H43" t="n">
-        <v>77</v>
+        <v>78.5</v>
       </c>
       <c r="I43" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>-57.2</v>
+        <v>-84.92</v>
       </c>
       <c r="K43" t="n">
-        <v>121.89</v>
+        <v>114.56</v>
       </c>
       <c r="L43" t="n">
-        <v>134.64</v>
+        <v>142.6</v>
       </c>
     </row>
     <row r="44">
@@ -1888,25 +1888,25 @@
         <v>1.69</v>
       </c>
       <c r="F44" t="n">
-        <v>4.56</v>
+        <v>4.94</v>
       </c>
       <c r="G44" t="n">
-        <v>197.7</v>
+        <v>212.7</v>
       </c>
       <c r="H44" t="n">
-        <v>78</v>
+        <v>68.8</v>
       </c>
       <c r="I44" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J44" t="n">
-        <v>29.99</v>
+        <v>33.9</v>
       </c>
       <c r="K44" t="n">
-        <v>-38.75</v>
+        <v>-44.42</v>
       </c>
       <c r="L44" t="n">
-        <v>49</v>
+        <v>55.88</v>
       </c>
     </row>
     <row r="45">
@@ -1930,25 +1930,25 @@
         <v>2.28</v>
       </c>
       <c r="F45" t="n">
-        <v>4.2</v>
+        <v>4.94</v>
       </c>
       <c r="G45" t="n">
-        <v>197</v>
+        <v>205.5</v>
       </c>
       <c r="H45" t="n">
-        <v>79.40000000000001</v>
+        <v>68.5</v>
       </c>
       <c r="I45" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>35.19</v>
+        <v>38.42</v>
       </c>
       <c r="K45" t="n">
-        <v>30.74</v>
+        <v>33.34</v>
       </c>
       <c r="L45" t="n">
-        <v>46.73</v>
+        <v>50.87</v>
       </c>
     </row>
     <row r="46">
@@ -1972,25 +1972,25 @@
         <v>2</v>
       </c>
       <c r="F46" t="n">
-        <v>4.17</v>
+        <v>4.94</v>
       </c>
       <c r="G46" t="n">
-        <v>209.4</v>
+        <v>204.9</v>
       </c>
       <c r="H46" t="n">
-        <v>75</v>
+        <v>74.7</v>
       </c>
       <c r="I46" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>8.42</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>-61.92</v>
+        <v>-67.77</v>
       </c>
       <c r="L46" t="n">
-        <v>62.49</v>
+        <v>68.37</v>
       </c>
     </row>
     <row r="47">
@@ -2014,25 +2014,25 @@
         <v>1.58</v>
       </c>
       <c r="F47" t="n">
-        <v>4.41</v>
+        <v>4.94</v>
       </c>
       <c r="G47" t="n">
-        <v>201.3</v>
+        <v>209.5</v>
       </c>
       <c r="H47" t="n">
-        <v>73.2</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I47" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-6.22</v>
+        <v>-8.619999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-58.6</v>
+        <v>-75.44</v>
       </c>
       <c r="L47" t="n">
-        <v>58.93</v>
+        <v>75.93000000000001</v>
       </c>
     </row>
     <row r="48">
@@ -2056,25 +2056,25 @@
         <v>1.53</v>
       </c>
       <c r="F48" t="n">
-        <v>4.03</v>
+        <v>4.32</v>
       </c>
       <c r="G48" t="n">
-        <v>213.3</v>
+        <v>202</v>
       </c>
       <c r="H48" t="n">
-        <v>72.8</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I48" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J48" t="n">
-        <v>43</v>
+        <v>45.81</v>
       </c>
       <c r="K48" t="n">
-        <v>-23.1</v>
+        <v>-26.51</v>
       </c>
       <c r="L48" t="n">
-        <v>48.81</v>
+        <v>52.93</v>
       </c>
     </row>
     <row r="49">
@@ -2098,25 +2098,25 @@
         <v>1.92</v>
       </c>
       <c r="F49" t="n">
-        <v>3.97</v>
+        <v>3.71</v>
       </c>
       <c r="G49" t="n">
-        <v>199.9</v>
+        <v>200.8</v>
       </c>
       <c r="H49" t="n">
-        <v>70.3</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-57.64</v>
+        <v>-61.56</v>
       </c>
       <c r="K49" t="n">
-        <v>-18.28</v>
+        <v>-20.61</v>
       </c>
       <c r="L49" t="n">
-        <v>60.47</v>
+        <v>64.92</v>
       </c>
     </row>
     <row r="50">
@@ -2140,25 +2140,25 @@
         <v>1.72</v>
       </c>
       <c r="F50" t="n">
-        <v>4.15</v>
+        <v>4.94</v>
       </c>
       <c r="G50" t="n">
-        <v>193.9</v>
+        <v>204.4</v>
       </c>
       <c r="H50" t="n">
-        <v>76.40000000000001</v>
+        <v>67</v>
       </c>
       <c r="I50" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J50" t="n">
-        <v>22.69</v>
+        <v>22.53</v>
       </c>
       <c r="K50" t="n">
-        <v>-84.31</v>
+        <v>-99.51000000000001</v>
       </c>
       <c r="L50" t="n">
-        <v>87.31</v>
+        <v>102.03</v>
       </c>
     </row>
     <row r="51">
@@ -2182,25 +2182,25 @@
         <v>1.85</v>
       </c>
       <c r="F51" t="n">
-        <v>4.32</v>
+        <v>4.94</v>
       </c>
       <c r="G51" t="n">
-        <v>209.9</v>
+        <v>207.8</v>
       </c>
       <c r="H51" t="n">
-        <v>77.2</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>124.93</v>
+        <v>138.94</v>
       </c>
       <c r="K51" t="n">
-        <v>-12.59</v>
+        <v>-17.7</v>
       </c>
       <c r="L51" t="n">
-        <v>125.56</v>
+        <v>140.06</v>
       </c>
     </row>
     <row r="52">
@@ -2224,25 +2224,25 @@
         <v>2.49</v>
       </c>
       <c r="F52" t="n">
-        <v>3.66</v>
+        <v>4.94</v>
       </c>
       <c r="G52" t="n">
-        <v>209.4</v>
+        <v>194.5</v>
       </c>
       <c r="H52" t="n">
-        <v>75.59999999999999</v>
+        <v>74.7</v>
       </c>
       <c r="I52" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>29.9</v>
+        <v>29.1</v>
       </c>
       <c r="K52" t="n">
-        <v>-77.36</v>
+        <v>-89.13</v>
       </c>
       <c r="L52" t="n">
-        <v>82.94</v>
+        <v>93.76000000000001</v>
       </c>
     </row>
     <row r="53">
@@ -2266,25 +2266,25 @@
         <v>1.48</v>
       </c>
       <c r="F53" t="n">
-        <v>3.97</v>
+        <v>4.94</v>
       </c>
       <c r="G53" t="n">
-        <v>213.6</v>
+        <v>200.7</v>
       </c>
       <c r="H53" t="n">
-        <v>75.3</v>
+        <v>76.8</v>
       </c>
       <c r="I53" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>48.93</v>
+        <v>52.29</v>
       </c>
       <c r="K53" t="n">
-        <v>-118.88</v>
+        <v>-141.98</v>
       </c>
       <c r="L53" t="n">
-        <v>128.56</v>
+        <v>151.3</v>
       </c>
     </row>
     <row r="54">
@@ -2308,25 +2308,25 @@
         <v>1.61</v>
       </c>
       <c r="F54" t="n">
-        <v>4.32</v>
+        <v>4.93</v>
       </c>
       <c r="G54" t="n">
-        <v>210</v>
+        <v>207.9</v>
       </c>
       <c r="H54" t="n">
-        <v>73.5</v>
+        <v>75</v>
       </c>
       <c r="I54" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-120.94</v>
+        <v>-135.88</v>
       </c>
       <c r="K54" t="n">
-        <v>-14.2</v>
+        <v>-25.8</v>
       </c>
       <c r="L54" t="n">
-        <v>121.77</v>
+        <v>138.3</v>
       </c>
     </row>
     <row r="55">
@@ -2350,25 +2350,25 @@
         <v>1.76</v>
       </c>
       <c r="F55" t="n">
-        <v>4.12</v>
+        <v>4.86</v>
       </c>
       <c r="G55" t="n">
         <v>203.9</v>
       </c>
       <c r="H55" t="n">
-        <v>72.2</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I55" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>70.41</v>
+        <v>77.81999999999999</v>
       </c>
       <c r="K55" t="n">
-        <v>150.45</v>
+        <v>165.82</v>
       </c>
       <c r="L55" t="n">
-        <v>166.11</v>
+        <v>183.17</v>
       </c>
     </row>
     <row r="56">
@@ -2392,25 +2392,25 @@
         <v>1.47</v>
       </c>
       <c r="F56" t="n">
-        <v>3.89</v>
+        <v>4.94</v>
       </c>
       <c r="G56" t="n">
-        <v>204.8</v>
+        <v>199.2</v>
       </c>
       <c r="H56" t="n">
-        <v>75.90000000000001</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I56" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>221.4</v>
+        <v>273.48</v>
       </c>
       <c r="K56" t="n">
-        <v>21.55</v>
+        <v>7.84</v>
       </c>
       <c r="L56" t="n">
-        <v>222.45</v>
+        <v>273.6</v>
       </c>
     </row>
     <row r="57">
@@ -2434,25 +2434,25 @@
         <v>1.48</v>
       </c>
       <c r="F57" t="n">
-        <v>4.02</v>
+        <v>2.6</v>
       </c>
       <c r="G57" t="n">
-        <v>212.9</v>
+        <v>201.9</v>
       </c>
       <c r="H57" t="n">
-        <v>73.8</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>57.12</v>
+        <v>38.79</v>
       </c>
       <c r="K57" t="n">
-        <v>-135.46</v>
+        <v>-142.47</v>
       </c>
       <c r="L57" t="n">
-        <v>147.01</v>
+        <v>147.65</v>
       </c>
     </row>
     <row r="58">
@@ -2476,25 +2476,25 @@
         <v>1.49</v>
       </c>
       <c r="F58" t="n">
-        <v>4.67</v>
+        <v>4.94</v>
       </c>
       <c r="G58" t="n">
-        <v>204.1</v>
+        <v>214.8</v>
       </c>
       <c r="H58" t="n">
-        <v>75.3</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I58" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-63.26</v>
+        <v>-92.8</v>
       </c>
       <c r="K58" t="n">
-        <v>-123.72</v>
+        <v>-164.07</v>
       </c>
       <c r="L58" t="n">
-        <v>138.95</v>
+        <v>188.49</v>
       </c>
     </row>
     <row r="59">
@@ -2518,25 +2518,25 @@
         <v>1.63</v>
       </c>
       <c r="F59" t="n">
-        <v>4.11</v>
+        <v>2.03</v>
       </c>
       <c r="G59" t="n">
-        <v>213.1</v>
+        <v>203.7</v>
       </c>
       <c r="H59" t="n">
-        <v>81.40000000000001</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I59" t="n">
         <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>-10.04</v>
+        <v>-10.28</v>
       </c>
       <c r="K59" t="n">
-        <v>-32.11</v>
+        <v>-33.04</v>
       </c>
       <c r="L59" t="n">
-        <v>33.65</v>
+        <v>34.6</v>
       </c>
     </row>
     <row r="60">
@@ -2560,25 +2560,25 @@
         <v>1.6</v>
       </c>
       <c r="F60" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="G60" t="n">
-        <v>204.1</v>
+        <v>205.9</v>
       </c>
       <c r="H60" t="n">
-        <v>71.8</v>
+        <v>72.09999999999999</v>
       </c>
       <c r="I60" t="n">
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="K60" t="n">
-        <v>44.5</v>
+        <v>48.96</v>
       </c>
       <c r="L60" t="n">
-        <v>44.53</v>
+        <v>48.98</v>
       </c>
     </row>
     <row r="61">
@@ -2602,25 +2602,25 @@
         <v>1.54</v>
       </c>
       <c r="F61" t="n">
-        <v>4.68</v>
+        <v>1.84</v>
       </c>
       <c r="G61" t="n">
-        <v>196.2</v>
+        <v>215.1</v>
       </c>
       <c r="H61" t="n">
-        <v>71.7</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I61" t="n">
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>26.62</v>
+        <v>25.9</v>
       </c>
       <c r="K61" t="n">
-        <v>41.37</v>
+        <v>40.46</v>
       </c>
       <c r="L61" t="n">
-        <v>49.19</v>
+        <v>48.04</v>
       </c>
     </row>
     <row r="62">
@@ -2644,25 +2644,25 @@
         <v>1.5</v>
       </c>
       <c r="F62" t="n">
-        <v>4.51</v>
+        <v>4.94</v>
       </c>
       <c r="G62" t="n">
-        <v>208.9</v>
+        <v>211.6</v>
       </c>
       <c r="H62" t="n">
-        <v>79</v>
+        <v>74.5</v>
       </c>
       <c r="I62" t="n">
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>47.14</v>
+        <v>55.91</v>
       </c>
       <c r="K62" t="n">
-        <v>20.93</v>
+        <v>24.13</v>
       </c>
       <c r="L62" t="n">
-        <v>51.58</v>
+        <v>60.89</v>
       </c>
     </row>
     <row r="63">
@@ -2686,25 +2686,25 @@
         <v>1.81</v>
       </c>
       <c r="F63" t="n">
-        <v>4.02</v>
+        <v>4.94</v>
       </c>
       <c r="G63" t="n">
-        <v>215.6</v>
+        <v>201.8</v>
       </c>
       <c r="H63" t="n">
-        <v>73</v>
+        <v>77.8</v>
       </c>
       <c r="I63" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>33.61</v>
+        <v>38.95</v>
       </c>
       <c r="K63" t="n">
-        <v>-54.36</v>
+        <v>-64.83</v>
       </c>
       <c r="L63" t="n">
-        <v>63.91</v>
+        <v>75.63</v>
       </c>
     </row>
     <row r="64">
@@ -2728,25 +2728,25 @@
         <v>1.46</v>
       </c>
       <c r="F64" t="n">
-        <v>3.08</v>
+        <v>4.94</v>
       </c>
       <c r="G64" t="n">
-        <v>204.7</v>
+        <v>183</v>
       </c>
       <c r="H64" t="n">
-        <v>77.59999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="I64" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>40.09</v>
+        <v>51.03</v>
       </c>
       <c r="K64" t="n">
-        <v>30.64</v>
+        <v>37.11</v>
       </c>
       <c r="L64" t="n">
-        <v>50.46</v>
+        <v>63.09</v>
       </c>
     </row>
     <row r="65">
@@ -2770,25 +2770,25 @@
         <v>1.69</v>
       </c>
       <c r="F65" t="n">
-        <v>4.43</v>
+        <v>4.63</v>
       </c>
       <c r="G65" t="n">
-        <v>201.8</v>
+        <v>210</v>
       </c>
       <c r="H65" t="n">
-        <v>69.3</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I65" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>48.63</v>
+        <v>53.01</v>
       </c>
       <c r="K65" t="n">
-        <v>-90.73999999999999</v>
+        <v>-107.51</v>
       </c>
       <c r="L65" t="n">
-        <v>102.95</v>
+        <v>119.87</v>
       </c>
     </row>
     <row r="66">
@@ -2812,25 +2812,25 @@
         <v>1.4</v>
       </c>
       <c r="F66" t="n">
-        <v>3.78</v>
+        <v>2.64</v>
       </c>
       <c r="G66" t="n">
-        <v>208.9</v>
+        <v>196.9</v>
       </c>
       <c r="H66" t="n">
-        <v>69.59999999999999</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I66" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>-46.82</v>
+        <v>-47.14</v>
       </c>
       <c r="K66" t="n">
-        <v>87.22</v>
+        <v>84.05</v>
       </c>
       <c r="L66" t="n">
-        <v>98.98999999999999</v>
+        <v>96.37</v>
       </c>
     </row>
     <row r="67">
@@ -2854,25 +2854,25 @@
         <v>1.7</v>
       </c>
       <c r="F67" t="n">
-        <v>4.27</v>
+        <v>4.94</v>
       </c>
       <c r="G67" t="n">
-        <v>208.7</v>
+        <v>206.9</v>
       </c>
       <c r="H67" t="n">
-        <v>74.8</v>
+        <v>74.40000000000001</v>
       </c>
       <c r="I67" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>40.81</v>
+        <v>44.28</v>
       </c>
       <c r="K67" t="n">
-        <v>-72.81999999999999</v>
+        <v>-88.75</v>
       </c>
       <c r="L67" t="n">
-        <v>83.48</v>
+        <v>99.18000000000001</v>
       </c>
     </row>
     <row r="68">
@@ -2896,25 +2896,25 @@
         <v>1.6</v>
       </c>
       <c r="F68" t="n">
-        <v>4.37</v>
+        <v>4.94</v>
       </c>
       <c r="G68" t="n">
-        <v>212.2</v>
+        <v>208.7</v>
       </c>
       <c r="H68" t="n">
-        <v>76</v>
+        <v>76.09999999999999</v>
       </c>
       <c r="I68" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>-54.73</v>
+        <v>-62.27</v>
       </c>
       <c r="K68" t="n">
-        <v>-107.33</v>
+        <v>-122.21</v>
       </c>
       <c r="L68" t="n">
-        <v>120.48</v>
+        <v>137.16</v>
       </c>
     </row>
     <row r="69">
@@ -2938,25 +2938,25 @@
         <v>1.72</v>
       </c>
       <c r="F69" t="n">
-        <v>4.3</v>
+        <v>4.94</v>
       </c>
       <c r="G69" t="n">
         <v>207.4</v>
       </c>
       <c r="H69" t="n">
-        <v>74.7</v>
+        <v>73.7</v>
       </c>
       <c r="I69" t="n">
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>44.79</v>
+        <v>36.77</v>
       </c>
       <c r="K69" t="n">
-        <v>-69</v>
+        <v>-93.14</v>
       </c>
       <c r="L69" t="n">
-        <v>82.26000000000001</v>
+        <v>100.14</v>
       </c>
     </row>
     <row r="70">
@@ -2980,25 +2980,25 @@
         <v>1.62</v>
       </c>
       <c r="F70" t="n">
-        <v>4.24</v>
+        <v>4.94</v>
       </c>
       <c r="G70" t="n">
-        <v>202.8</v>
+        <v>206.2</v>
       </c>
       <c r="H70" t="n">
-        <v>75.7</v>
+        <v>71.40000000000001</v>
       </c>
       <c r="I70" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>-86.08</v>
+        <v>-92.87</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.97</v>
+        <v>-27.15</v>
       </c>
       <c r="L70" t="n">
-        <v>86.17</v>
+        <v>96.75</v>
       </c>
     </row>
     <row r="71">
@@ -3022,25 +3022,25 @@
         <v>2.49</v>
       </c>
       <c r="F71" t="n">
-        <v>4.83</v>
+        <v>4.94</v>
       </c>
       <c r="G71" t="n">
-        <v>212.7</v>
+        <v>218</v>
       </c>
       <c r="H71" t="n">
-        <v>73.7</v>
+        <v>76.3</v>
       </c>
       <c r="I71" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>199.6</v>
+        <v>205.24</v>
       </c>
       <c r="K71" t="n">
-        <v>-46.07</v>
+        <v>-78.55</v>
       </c>
       <c r="L71" t="n">
-        <v>204.84</v>
+        <v>219.76</v>
       </c>
     </row>
     <row r="72">
@@ -3064,25 +3064,25 @@
         <v>1.77</v>
       </c>
       <c r="F72" t="n">
-        <v>4.17</v>
+        <v>2.8</v>
       </c>
       <c r="G72" t="n">
-        <v>196.9</v>
+        <v>204.8</v>
       </c>
       <c r="H72" t="n">
-        <v>67.3</v>
+        <v>68.40000000000001</v>
       </c>
       <c r="I72" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>2.1</v>
+        <v>-21.62</v>
       </c>
       <c r="K72" t="n">
-        <v>-119.71</v>
+        <v>-131.3</v>
       </c>
       <c r="L72" t="n">
-        <v>119.73</v>
+        <v>133.07</v>
       </c>
     </row>
     <row r="73">
@@ -3106,25 +3106,25 @@
         <v>2.12</v>
       </c>
       <c r="F73" t="n">
-        <v>4.49</v>
+        <v>4.94</v>
       </c>
       <c r="G73" t="n">
-        <v>201.8</v>
+        <v>211.2</v>
       </c>
       <c r="H73" t="n">
-        <v>73.7</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I73" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J73" t="n">
-        <v>115.45</v>
+        <v>56</v>
       </c>
       <c r="K73" t="n">
-        <v>26.42</v>
+        <v>-49.05</v>
       </c>
       <c r="L73" t="n">
-        <v>118.44</v>
+        <v>74.44</v>
       </c>
     </row>
     <row r="74">
@@ -3148,25 +3148,25 @@
         <v>1.86</v>
       </c>
       <c r="F74" t="n">
-        <v>4.47</v>
+        <v>4.94</v>
       </c>
       <c r="G74" t="n">
-        <v>202.3</v>
+        <v>210.8</v>
       </c>
       <c r="H74" t="n">
-        <v>73.2</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I74" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>37.43</v>
+        <v>40.35</v>
       </c>
       <c r="K74" t="n">
-        <v>17.5</v>
+        <v>18.65</v>
       </c>
       <c r="L74" t="n">
-        <v>41.32</v>
+        <v>44.46</v>
       </c>
     </row>
     <row r="75">
@@ -3190,25 +3190,25 @@
         <v>2.02</v>
       </c>
       <c r="F75" t="n">
-        <v>3.44</v>
+        <v>4.57</v>
       </c>
       <c r="G75" t="n">
-        <v>192.1</v>
+        <v>190.3</v>
       </c>
       <c r="H75" t="n">
-        <v>71.59999999999999</v>
+        <v>66</v>
       </c>
       <c r="I75" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>-37.12</v>
+        <v>-37.26</v>
       </c>
       <c r="K75" t="n">
-        <v>50.5</v>
+        <v>50.29</v>
       </c>
       <c r="L75" t="n">
-        <v>62.68</v>
+        <v>62.59</v>
       </c>
     </row>
     <row r="76">
@@ -3232,25 +3232,25 @@
         <v>1.82</v>
       </c>
       <c r="F76" t="n">
-        <v>4.99</v>
+        <v>4.94</v>
       </c>
       <c r="G76" t="n">
-        <v>219.3</v>
+        <v>221.1</v>
       </c>
       <c r="H76" t="n">
-        <v>72.40000000000001</v>
+        <v>79.59999999999999</v>
       </c>
       <c r="I76" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>-43.15</v>
+        <v>-47.24</v>
       </c>
       <c r="K76" t="n">
-        <v>-12.57</v>
+        <v>-13.99</v>
       </c>
       <c r="L76" t="n">
-        <v>44.94</v>
+        <v>49.27</v>
       </c>
     </row>
     <row r="77">
@@ -3274,25 +3274,25 @@
         <v>1.72</v>
       </c>
       <c r="F77" t="n">
-        <v>4.12</v>
+        <v>4.94</v>
       </c>
       <c r="G77" t="n">
-        <v>196.2</v>
+        <v>203.8</v>
       </c>
       <c r="H77" t="n">
-        <v>81.5</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="I77" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-50.25</v>
+        <v>-58.26</v>
       </c>
       <c r="K77" t="n">
-        <v>-18.79</v>
+        <v>-22.79</v>
       </c>
       <c r="L77" t="n">
-        <v>53.65</v>
+        <v>62.56</v>
       </c>
     </row>
     <row r="78">
@@ -3316,25 +3316,25 @@
         <v>1.56</v>
       </c>
       <c r="F78" t="n">
-        <v>4.18</v>
+        <v>4.94</v>
       </c>
       <c r="G78" t="n">
-        <v>209.8</v>
+        <v>204.9</v>
       </c>
       <c r="H78" t="n">
-        <v>74.3</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="I78" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-36.01</v>
+        <v>-44.31</v>
       </c>
       <c r="K78" t="n">
-        <v>-26.52</v>
+        <v>-34.28</v>
       </c>
       <c r="L78" t="n">
-        <v>44.72</v>
+        <v>56.02</v>
       </c>
     </row>
     <row r="79">
@@ -3358,25 +3358,25 @@
         <v>1.72</v>
       </c>
       <c r="F79" t="n">
-        <v>3.68</v>
+        <v>4.94</v>
       </c>
       <c r="G79" t="n">
-        <v>204.7</v>
+        <v>194.9</v>
       </c>
       <c r="H79" t="n">
-        <v>70.2</v>
+        <v>72.3</v>
       </c>
       <c r="I79" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>25.66</v>
+        <v>31.77</v>
       </c>
       <c r="K79" t="n">
-        <v>41.76</v>
+        <v>49.48</v>
       </c>
       <c r="L79" t="n">
-        <v>49.02</v>
+        <v>58.8</v>
       </c>
     </row>
     <row r="80">
@@ -3400,25 +3400,25 @@
         <v>1.5</v>
       </c>
       <c r="F80" t="n">
-        <v>4.3</v>
+        <v>4.94</v>
       </c>
       <c r="G80" t="n">
-        <v>203.5</v>
+        <v>207.4</v>
       </c>
       <c r="H80" t="n">
-        <v>78.3</v>
+        <v>71.7</v>
       </c>
       <c r="I80" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-75.34</v>
+        <v>-92.86</v>
       </c>
       <c r="K80" t="n">
-        <v>19.56</v>
+        <v>18.64</v>
       </c>
       <c r="L80" t="n">
-        <v>77.84</v>
+        <v>94.70999999999999</v>
       </c>
     </row>
     <row r="81">
@@ -3442,25 +3442,25 @@
         <v>1.8</v>
       </c>
       <c r="F81" t="n">
-        <v>4.81</v>
+        <v>4.94</v>
       </c>
       <c r="G81" t="n">
-        <v>197.2</v>
+        <v>217.7</v>
       </c>
       <c r="H81" t="n">
-        <v>75</v>
+        <v>68.59999999999999</v>
       </c>
       <c r="I81" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>27.24</v>
+        <v>25.89</v>
       </c>
       <c r="K81" t="n">
-        <v>-83.92</v>
+        <v>-100.98</v>
       </c>
       <c r="L81" t="n">
-        <v>88.23</v>
+        <v>104.24</v>
       </c>
     </row>
     <row r="82">
@@ -3484,25 +3484,25 @@
         <v>1.48</v>
       </c>
       <c r="F82" t="n">
-        <v>3.89</v>
+        <v>4.31</v>
       </c>
       <c r="G82" t="n">
-        <v>221.2</v>
+        <v>199.3</v>
       </c>
       <c r="H82" t="n">
-        <v>72.7</v>
+        <v>80.59999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-23.66</v>
+        <v>-25.56</v>
       </c>
       <c r="K82" t="n">
-        <v>134.49</v>
+        <v>140.6</v>
       </c>
       <c r="L82" t="n">
-        <v>136.55</v>
+        <v>142.91</v>
       </c>
     </row>
     <row r="83">
@@ -3526,25 +3526,25 @@
         <v>1.78</v>
       </c>
       <c r="F83" t="n">
-        <v>4.48</v>
+        <v>4.94</v>
       </c>
       <c r="G83" t="n">
-        <v>229.2</v>
+        <v>211.1</v>
       </c>
       <c r="H83" t="n">
-        <v>71.8</v>
+        <v>84.59999999999999</v>
       </c>
       <c r="I83" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>80.11</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>-112.76</v>
+        <v>-141.02</v>
       </c>
       <c r="L83" t="n">
-        <v>138.32</v>
+        <v>165.98</v>
       </c>
     </row>
     <row r="84">
@@ -3568,25 +3568,25 @@
         <v>1.55</v>
       </c>
       <c r="F84" t="n">
-        <v>4.27</v>
+        <v>4.94</v>
       </c>
       <c r="G84" t="n">
-        <v>197</v>
+        <v>206.9</v>
       </c>
       <c r="H84" t="n">
-        <v>77.7</v>
+        <v>68.5</v>
       </c>
       <c r="I84" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-122.31</v>
+        <v>-155.39</v>
       </c>
       <c r="K84" t="n">
-        <v>-43.33</v>
+        <v>-61.59</v>
       </c>
       <c r="L84" t="n">
-        <v>129.76</v>
+        <v>167.15</v>
       </c>
     </row>
     <row r="85">
@@ -3610,25 +3610,25 @@
         <v>1.75</v>
       </c>
       <c r="F85" t="n">
-        <v>4.3</v>
+        <v>4.94</v>
       </c>
       <c r="G85" t="n">
-        <v>210.2</v>
+        <v>207.5</v>
       </c>
       <c r="H85" t="n">
-        <v>75.59999999999999</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="I85" t="n">
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-90.09999999999999</v>
+        <v>-110.93</v>
       </c>
       <c r="K85" t="n">
-        <v>40.42</v>
+        <v>30.23</v>
       </c>
       <c r="L85" t="n">
-        <v>98.75</v>
+        <v>114.97</v>
       </c>
     </row>
     <row r="86">
@@ -3652,25 +3652,25 @@
         <v>1.58</v>
       </c>
       <c r="F86" t="n">
-        <v>4.51</v>
+        <v>3.52</v>
       </c>
       <c r="G86" t="n">
-        <v>211</v>
+        <v>211.6</v>
       </c>
       <c r="H86" t="n">
-        <v>70.09999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="I86" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>3.43</v>
+        <v>-7.75</v>
       </c>
       <c r="K86" t="n">
-        <v>-199.81</v>
+        <v>-230.17</v>
       </c>
       <c r="L86" t="n">
-        <v>199.84</v>
+        <v>230.3</v>
       </c>
     </row>
     <row r="87">
@@ -3694,25 +3694,25 @@
         <v>1.42</v>
       </c>
       <c r="F87" t="n">
-        <v>4.54</v>
+        <v>4.94</v>
       </c>
       <c r="G87" t="n">
-        <v>218.5</v>
+        <v>212.3</v>
       </c>
       <c r="H87" t="n">
-        <v>76.8</v>
+        <v>79.3</v>
       </c>
       <c r="I87" t="n">
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>139.78</v>
+        <v>151.83</v>
       </c>
       <c r="K87" t="n">
-        <v>-113.92</v>
+        <v>-159.82</v>
       </c>
       <c r="L87" t="n">
-        <v>180.32</v>
+        <v>220.44</v>
       </c>
     </row>
     <row r="88">
@@ -3736,25 +3736,25 @@
         <v>1.74</v>
       </c>
       <c r="F88" t="n">
-        <v>4.37</v>
+        <v>4.94</v>
       </c>
       <c r="G88" t="n">
-        <v>217.3</v>
+        <v>208.9</v>
       </c>
       <c r="H88" t="n">
-        <v>76.5</v>
+        <v>78.7</v>
       </c>
       <c r="I88" t="n">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>-31.17</v>
+        <v>-41.88</v>
       </c>
       <c r="K88" t="n">
-        <v>245.56</v>
+        <v>235.43</v>
       </c>
       <c r="L88" t="n">
-        <v>247.53</v>
+        <v>239.13</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-27.xlsx
+++ b/output/2024-10-27.xlsx
@@ -640,13 +640,13 @@
         <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>-13.88</v>
+        <v>-12.67</v>
       </c>
       <c r="K14" t="n">
-        <v>48.93</v>
+        <v>44.68</v>
       </c>
       <c r="L14" t="n">
-        <v>50.86</v>
+        <v>46.44</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>40.09</v>
+        <v>39.27</v>
       </c>
       <c r="K15" t="n">
-        <v>3.24</v>
+        <v>3.17</v>
       </c>
       <c r="L15" t="n">
-        <v>40.22</v>
+        <v>39.4</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>22</v>
       </c>
       <c r="J16" t="n">
-        <v>3.12</v>
+        <v>3.24</v>
       </c>
       <c r="K16" t="n">
-        <v>43.13</v>
+        <v>44.79</v>
       </c>
       <c r="L16" t="n">
-        <v>43.24</v>
+        <v>44.91</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>26</v>
       </c>
       <c r="J17" t="n">
-        <v>-51.95</v>
+        <v>-49.78</v>
       </c>
       <c r="K17" t="n">
-        <v>23.49</v>
+        <v>22.51</v>
       </c>
       <c r="L17" t="n">
-        <v>57.01</v>
+        <v>54.64</v>
       </c>
     </row>
     <row r="18">
@@ -850,13 +850,13 @@
         <v>25</v>
       </c>
       <c r="J19" t="n">
-        <v>55.86</v>
+        <v>54.72</v>
       </c>
       <c r="K19" t="n">
-        <v>2.89</v>
+        <v>2.83</v>
       </c>
       <c r="L19" t="n">
-        <v>55.93</v>
+        <v>54.79</v>
       </c>
     </row>
     <row r="20">
@@ -934,13 +934,13 @@
         <v>22</v>
       </c>
       <c r="J21" t="n">
-        <v>-91.91</v>
+        <v>-95.44</v>
       </c>
       <c r="K21" t="n">
-        <v>28.12</v>
+        <v>29.21</v>
       </c>
       <c r="L21" t="n">
-        <v>96.11</v>
+        <v>99.81</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>28</v>
       </c>
       <c r="J22" t="n">
-        <v>-107.51</v>
+        <v>-98.16</v>
       </c>
       <c r="K22" t="n">
-        <v>11.03</v>
+        <v>10.07</v>
       </c>
       <c r="L22" t="n">
-        <v>108.07</v>
+        <v>98.68000000000001</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>28</v>
       </c>
       <c r="J23" t="n">
-        <v>112.9</v>
+        <v>103.08</v>
       </c>
       <c r="K23" t="n">
-        <v>148.14</v>
+        <v>135.26</v>
       </c>
       <c r="L23" t="n">
-        <v>186.26</v>
+        <v>170.06</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>45.51</v>
+        <v>41.55</v>
       </c>
       <c r="K24" t="n">
-        <v>-106.93</v>
+        <v>-97.63</v>
       </c>
       <c r="L24" t="n">
-        <v>116.21</v>
+        <v>106.11</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>-115.55</v>
+        <v>-108.17</v>
       </c>
       <c r="K25" t="n">
-        <v>-52.54</v>
+        <v>-49.19</v>
       </c>
       <c r="L25" t="n">
-        <v>126.93</v>
+        <v>118.83</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>203.27</v>
+        <v>190.29</v>
       </c>
       <c r="K26" t="n">
-        <v>53.22</v>
+        <v>49.82</v>
       </c>
       <c r="L26" t="n">
-        <v>210.12</v>
+        <v>196.71</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-153.46</v>
+        <v>-147.06</v>
       </c>
       <c r="K27" t="n">
-        <v>-111.1</v>
+        <v>-106.47</v>
       </c>
       <c r="L27" t="n">
-        <v>189.45</v>
+        <v>181.56</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>22</v>
       </c>
       <c r="J28" t="n">
-        <v>168.98</v>
+        <v>175.48</v>
       </c>
       <c r="K28" t="n">
-        <v>39.52</v>
+        <v>41.04</v>
       </c>
       <c r="L28" t="n">
-        <v>173.54</v>
+        <v>180.21</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>32.51</v>
+        <v>31.16</v>
       </c>
       <c r="K29" t="n">
-        <v>42.72</v>
+        <v>40.94</v>
       </c>
       <c r="L29" t="n">
-        <v>53.68</v>
+        <v>51.45</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-16.83</v>
+        <v>-16.13</v>
       </c>
       <c r="K30" t="n">
-        <v>40.9</v>
+        <v>39.2</v>
       </c>
       <c r="L30" t="n">
-        <v>44.23</v>
+        <v>42.39</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>22</v>
       </c>
       <c r="J31" t="n">
-        <v>-39.56</v>
+        <v>-41.08</v>
       </c>
       <c r="K31" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="L31" t="n">
-        <v>39.58</v>
+        <v>41.1</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>28</v>
       </c>
       <c r="J32" t="n">
-        <v>-33.92</v>
+        <v>-30.97</v>
       </c>
       <c r="K32" t="n">
-        <v>-35.12</v>
+        <v>-32.07</v>
       </c>
       <c r="L32" t="n">
-        <v>48.83</v>
+        <v>44.58</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>63.99</v>
+        <v>59.91</v>
       </c>
       <c r="K33" t="n">
-        <v>31.98</v>
+        <v>29.94</v>
       </c>
       <c r="L33" t="n">
-        <v>71.54000000000001</v>
+        <v>66.97</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>26</v>
       </c>
       <c r="J34" t="n">
-        <v>-74.54000000000001</v>
+        <v>-71.43000000000001</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.64</v>
+        <v>-1.57</v>
       </c>
       <c r="L34" t="n">
-        <v>74.56</v>
+        <v>71.45</v>
       </c>
     </row>
     <row r="35">
@@ -1564,13 +1564,13 @@
         <v>28</v>
       </c>
       <c r="J36" t="n">
-        <v>-89.67</v>
+        <v>-81.88</v>
       </c>
       <c r="K36" t="n">
-        <v>-21.78</v>
+        <v>-19.89</v>
       </c>
       <c r="L36" t="n">
-        <v>92.28</v>
+        <v>84.26000000000001</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>28</v>
       </c>
       <c r="J37" t="n">
-        <v>14.8</v>
+        <v>13.51</v>
       </c>
       <c r="K37" t="n">
-        <v>-72.91</v>
+        <v>-66.56999999999999</v>
       </c>
       <c r="L37" t="n">
-        <v>74.40000000000001</v>
+        <v>67.93000000000001</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>28</v>
       </c>
       <c r="J38" t="n">
-        <v>-93.01000000000001</v>
+        <v>-84.92</v>
       </c>
       <c r="K38" t="n">
-        <v>-76.13</v>
+        <v>-69.51000000000001</v>
       </c>
       <c r="L38" t="n">
-        <v>120.2</v>
+        <v>109.74</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-114.95</v>
+        <v>-119.37</v>
       </c>
       <c r="K39" t="n">
-        <v>-15.19</v>
+        <v>-15.78</v>
       </c>
       <c r="L39" t="n">
-        <v>115.95</v>
+        <v>120.41</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>23</v>
       </c>
       <c r="J40" t="n">
-        <v>-58.47</v>
+        <v>-59.62</v>
       </c>
       <c r="K40" t="n">
-        <v>-73.63</v>
+        <v>-75.08</v>
       </c>
       <c r="L40" t="n">
-        <v>94.03</v>
+        <v>95.87</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>23</v>
       </c>
       <c r="J41" t="n">
-        <v>154.52</v>
+        <v>157.55</v>
       </c>
       <c r="K41" t="n">
-        <v>-64.09</v>
+        <v>-65.34</v>
       </c>
       <c r="L41" t="n">
-        <v>167.28</v>
+        <v>170.56</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>23</v>
       </c>
       <c r="J42" t="n">
-        <v>-201.56</v>
+        <v>-205.51</v>
       </c>
       <c r="K42" t="n">
-        <v>-69.20999999999999</v>
+        <v>-70.56999999999999</v>
       </c>
       <c r="L42" t="n">
-        <v>213.11</v>
+        <v>217.29</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>27</v>
       </c>
       <c r="J43" t="n">
-        <v>-84.92</v>
+        <v>-79.5</v>
       </c>
       <c r="K43" t="n">
-        <v>114.56</v>
+        <v>107.24</v>
       </c>
       <c r="L43" t="n">
-        <v>142.6</v>
+        <v>133.49</v>
       </c>
     </row>
     <row r="44">
@@ -1942,13 +1942,13 @@
         <v>22</v>
       </c>
       <c r="J45" t="n">
-        <v>38.42</v>
+        <v>39.9</v>
       </c>
       <c r="K45" t="n">
-        <v>33.34</v>
+        <v>34.63</v>
       </c>
       <c r="L45" t="n">
-        <v>50.87</v>
+        <v>52.83</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>22</v>
       </c>
       <c r="J46" t="n">
-        <v>9.050000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="K46" t="n">
-        <v>-67.77</v>
+        <v>-70.38</v>
       </c>
       <c r="L46" t="n">
-        <v>68.37</v>
+        <v>71</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-8.619999999999999</v>
+        <v>-8.789999999999999</v>
       </c>
       <c r="K47" t="n">
-        <v>-75.44</v>
+        <v>-76.92</v>
       </c>
       <c r="L47" t="n">
-        <v>75.93000000000001</v>
+        <v>77.42</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>28</v>
       </c>
       <c r="J48" t="n">
-        <v>45.81</v>
+        <v>41.83</v>
       </c>
       <c r="K48" t="n">
-        <v>-26.51</v>
+        <v>-24.2</v>
       </c>
       <c r="L48" t="n">
-        <v>52.93</v>
+        <v>48.32</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>26</v>
       </c>
       <c r="J49" t="n">
-        <v>-61.56</v>
+        <v>-59</v>
       </c>
       <c r="K49" t="n">
-        <v>-20.61</v>
+        <v>-19.75</v>
       </c>
       <c r="L49" t="n">
-        <v>64.92</v>
+        <v>62.21</v>
       </c>
     </row>
     <row r="50">
@@ -2194,13 +2194,13 @@
         <v>25</v>
       </c>
       <c r="J51" t="n">
-        <v>138.94</v>
+        <v>136.1</v>
       </c>
       <c r="K51" t="n">
-        <v>-17.7</v>
+        <v>-17.34</v>
       </c>
       <c r="L51" t="n">
-        <v>140.06</v>
+        <v>137.2</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>23</v>
       </c>
       <c r="J52" t="n">
-        <v>29.1</v>
+        <v>29.67</v>
       </c>
       <c r="K52" t="n">
-        <v>-89.13</v>
+        <v>-90.88</v>
       </c>
       <c r="L52" t="n">
-        <v>93.76000000000001</v>
+        <v>95.59999999999999</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>26</v>
       </c>
       <c r="J53" t="n">
-        <v>52.29</v>
+        <v>50.12</v>
       </c>
       <c r="K53" t="n">
-        <v>-141.98</v>
+        <v>-136.06</v>
       </c>
       <c r="L53" t="n">
-        <v>151.3</v>
+        <v>145</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>25</v>
       </c>
       <c r="J54" t="n">
-        <v>-135.88</v>
+        <v>-133.1</v>
       </c>
       <c r="K54" t="n">
-        <v>-25.8</v>
+        <v>-25.28</v>
       </c>
       <c r="L54" t="n">
-        <v>138.3</v>
+        <v>135.48</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>23</v>
       </c>
       <c r="J55" t="n">
-        <v>77.81999999999999</v>
+        <v>79.34</v>
       </c>
       <c r="K55" t="n">
-        <v>165.82</v>
+        <v>169.08</v>
       </c>
       <c r="L55" t="n">
-        <v>183.17</v>
+        <v>186.77</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>22</v>
       </c>
       <c r="J56" t="n">
-        <v>273.48</v>
+        <v>284</v>
       </c>
       <c r="K56" t="n">
-        <v>7.84</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="L56" t="n">
-        <v>273.6</v>
+        <v>284.12</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>27</v>
       </c>
       <c r="J57" t="n">
-        <v>38.79</v>
+        <v>36.32</v>
       </c>
       <c r="K57" t="n">
-        <v>-142.47</v>
+        <v>-133.37</v>
       </c>
       <c r="L57" t="n">
-        <v>147.65</v>
+        <v>138.23</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-92.8</v>
+        <v>-94.62</v>
       </c>
       <c r="K58" t="n">
-        <v>-164.07</v>
+        <v>-167.28</v>
       </c>
       <c r="L58" t="n">
-        <v>188.49</v>
+        <v>192.19</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>-10.28</v>
+        <v>-9.619999999999999</v>
       </c>
       <c r="K59" t="n">
-        <v>-33.04</v>
+        <v>-30.93</v>
       </c>
       <c r="L59" t="n">
-        <v>34.6</v>
+        <v>32.4</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>1.41</v>
+        <v>1.29</v>
       </c>
       <c r="K60" t="n">
-        <v>48.96</v>
+        <v>44.7</v>
       </c>
       <c r="L60" t="n">
-        <v>48.98</v>
+        <v>44.72</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>25.9</v>
+        <v>24.82</v>
       </c>
       <c r="K61" t="n">
-        <v>40.46</v>
+        <v>38.77</v>
       </c>
       <c r="L61" t="n">
-        <v>48.04</v>
+        <v>46.04</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>55.91</v>
+        <v>51.05</v>
       </c>
       <c r="K62" t="n">
-        <v>24.13</v>
+        <v>22.03</v>
       </c>
       <c r="L62" t="n">
-        <v>60.89</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>22</v>
       </c>
       <c r="J63" t="n">
-        <v>38.95</v>
+        <v>40.45</v>
       </c>
       <c r="K63" t="n">
-        <v>-64.83</v>
+        <v>-67.33</v>
       </c>
       <c r="L63" t="n">
-        <v>75.63</v>
+        <v>78.54000000000001</v>
       </c>
     </row>
     <row r="64">
@@ -2782,13 +2782,13 @@
         <v>22</v>
       </c>
       <c r="J65" t="n">
-        <v>53.01</v>
+        <v>55.05</v>
       </c>
       <c r="K65" t="n">
-        <v>-107.51</v>
+        <v>-111.65</v>
       </c>
       <c r="L65" t="n">
-        <v>119.87</v>
+        <v>124.48</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>28</v>
       </c>
       <c r="J66" t="n">
-        <v>-47.14</v>
+        <v>-43.04</v>
       </c>
       <c r="K66" t="n">
-        <v>84.05</v>
+        <v>76.73999999999999</v>
       </c>
       <c r="L66" t="n">
-        <v>96.37</v>
+        <v>87.98999999999999</v>
       </c>
     </row>
     <row r="67">
@@ -2908,13 +2908,13 @@
         <v>28</v>
       </c>
       <c r="J68" t="n">
-        <v>-62.27</v>
+        <v>-56.86</v>
       </c>
       <c r="K68" t="n">
-        <v>-122.21</v>
+        <v>-111.58</v>
       </c>
       <c r="L68" t="n">
-        <v>137.16</v>
+        <v>125.23</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>36.77</v>
+        <v>34.42</v>
       </c>
       <c r="K69" t="n">
-        <v>-93.14</v>
+        <v>-87.2</v>
       </c>
       <c r="L69" t="n">
-        <v>100.14</v>
+        <v>93.75</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>27</v>
       </c>
       <c r="J70" t="n">
-        <v>-92.87</v>
+        <v>-86.94</v>
       </c>
       <c r="K70" t="n">
-        <v>-27.15</v>
+        <v>-25.41</v>
       </c>
       <c r="L70" t="n">
-        <v>96.75</v>
+        <v>90.58</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>25</v>
       </c>
       <c r="J71" t="n">
-        <v>205.24</v>
+        <v>201.05</v>
       </c>
       <c r="K71" t="n">
-        <v>-78.55</v>
+        <v>-76.94</v>
       </c>
       <c r="L71" t="n">
-        <v>219.76</v>
+        <v>215.28</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>27</v>
       </c>
       <c r="J72" t="n">
-        <v>-21.62</v>
+        <v>-20.24</v>
       </c>
       <c r="K72" t="n">
-        <v>-131.3</v>
+        <v>-122.92</v>
       </c>
       <c r="L72" t="n">
-        <v>133.07</v>
+        <v>124.58</v>
       </c>
     </row>
     <row r="73">
@@ -3160,13 +3160,13 @@
         <v>28</v>
       </c>
       <c r="J74" t="n">
-        <v>40.35</v>
+        <v>36.84</v>
       </c>
       <c r="K74" t="n">
-        <v>18.65</v>
+        <v>17.03</v>
       </c>
       <c r="L74" t="n">
-        <v>44.46</v>
+        <v>40.59</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>26</v>
       </c>
       <c r="J75" t="n">
-        <v>-37.26</v>
+        <v>-35.71</v>
       </c>
       <c r="K75" t="n">
-        <v>50.29</v>
+        <v>48.19</v>
       </c>
       <c r="L75" t="n">
-        <v>62.59</v>
+        <v>59.98</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>26</v>
       </c>
       <c r="J76" t="n">
-        <v>-47.24</v>
+        <v>-45.28</v>
       </c>
       <c r="K76" t="n">
-        <v>-13.99</v>
+        <v>-13.4</v>
       </c>
       <c r="L76" t="n">
-        <v>49.27</v>
+        <v>47.22</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>27</v>
       </c>
       <c r="J77" t="n">
-        <v>-58.26</v>
+        <v>-54.54</v>
       </c>
       <c r="K77" t="n">
-        <v>-22.79</v>
+        <v>-21.33</v>
       </c>
       <c r="L77" t="n">
-        <v>62.56</v>
+        <v>58.57</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>25</v>
       </c>
       <c r="J78" t="n">
-        <v>-44.31</v>
+        <v>-43.4</v>
       </c>
       <c r="K78" t="n">
-        <v>-34.28</v>
+        <v>-33.58</v>
       </c>
       <c r="L78" t="n">
-        <v>56.02</v>
+        <v>54.87</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>23</v>
       </c>
       <c r="J79" t="n">
-        <v>31.77</v>
+        <v>32.4</v>
       </c>
       <c r="K79" t="n">
-        <v>49.48</v>
+        <v>50.45</v>
       </c>
       <c r="L79" t="n">
-        <v>58.8</v>
+        <v>59.96</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>26</v>
       </c>
       <c r="J80" t="n">
-        <v>-92.86</v>
+        <v>-88.98999999999999</v>
       </c>
       <c r="K80" t="n">
-        <v>18.64</v>
+        <v>17.86</v>
       </c>
       <c r="L80" t="n">
-        <v>94.70999999999999</v>
+        <v>90.76000000000001</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>22</v>
       </c>
       <c r="J81" t="n">
-        <v>25.89</v>
+        <v>26.88</v>
       </c>
       <c r="K81" t="n">
-        <v>-100.98</v>
+        <v>-104.86</v>
       </c>
       <c r="L81" t="n">
-        <v>104.24</v>
+        <v>108.25</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>28</v>
       </c>
       <c r="J82" t="n">
-        <v>-25.56</v>
+        <v>-23.33</v>
       </c>
       <c r="K82" t="n">
-        <v>140.6</v>
+        <v>128.38</v>
       </c>
       <c r="L82" t="n">
-        <v>142.91</v>
+        <v>130.48</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>22</v>
       </c>
       <c r="J83" t="n">
-        <v>87.54000000000001</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="K83" t="n">
-        <v>-141.02</v>
+        <v>-146.44</v>
       </c>
       <c r="L83" t="n">
-        <v>165.98</v>
+        <v>172.36</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>23</v>
       </c>
       <c r="J84" t="n">
-        <v>-155.39</v>
+        <v>-158.43</v>
       </c>
       <c r="K84" t="n">
-        <v>-61.59</v>
+        <v>-62.8</v>
       </c>
       <c r="L84" t="n">
-        <v>167.15</v>
+        <v>170.42</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-110.93</v>
+        <v>-106.3</v>
       </c>
       <c r="K85" t="n">
-        <v>30.23</v>
+        <v>28.97</v>
       </c>
       <c r="L85" t="n">
-        <v>114.97</v>
+        <v>110.18</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>23</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.75</v>
+        <v>-7.91</v>
       </c>
       <c r="K86" t="n">
-        <v>-230.17</v>
+        <v>-234.68</v>
       </c>
       <c r="L86" t="n">
-        <v>230.3</v>
+        <v>234.81</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>151.83</v>
+        <v>157.67</v>
       </c>
       <c r="K87" t="n">
-        <v>-159.82</v>
+        <v>-165.96</v>
       </c>
       <c r="L87" t="n">
-        <v>220.44</v>
+        <v>228.92</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>27</v>
       </c>
       <c r="J88" t="n">
-        <v>-41.88</v>
+        <v>-39.21</v>
       </c>
       <c r="K88" t="n">
-        <v>235.43</v>
+        <v>220.4</v>
       </c>
       <c r="L88" t="n">
-        <v>239.13</v>
+        <v>223.86</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-27.xlsx
+++ b/output/2024-10-27.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.42</v>
+        <v>1.17</v>
       </c>
       <c r="F14" t="n">
-        <v>3.58</v>
+        <v>1.47</v>
       </c>
       <c r="G14" t="n">
-        <v>208.1</v>
+        <v>218.1</v>
       </c>
       <c r="H14" t="n">
-        <v>78.90000000000001</v>
+        <v>60.5</v>
       </c>
       <c r="I14" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="J14" t="n">
-        <v>-12.67</v>
+        <v>-24.73</v>
       </c>
       <c r="K14" t="n">
-        <v>44.68</v>
+        <v>12.78</v>
       </c>
       <c r="L14" t="n">
-        <v>46.44</v>
+        <v>27.84</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08:13:27</t>
+          <t>08:13:52</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.29</v>
+        <v>1.2</v>
       </c>
       <c r="F15" t="n">
-        <v>4.38</v>
+        <v>1.5</v>
       </c>
       <c r="G15" t="n">
-        <v>205.4</v>
+        <v>203.4</v>
       </c>
       <c r="H15" t="n">
-        <v>70.8</v>
+        <v>34.6</v>
       </c>
       <c r="I15" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="J15" t="n">
-        <v>39.27</v>
+        <v>-10.61</v>
       </c>
       <c r="K15" t="n">
-        <v>3.17</v>
+        <v>-25.01</v>
       </c>
       <c r="L15" t="n">
-        <v>39.4</v>
+        <v>27.16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08:15:57</t>
+          <t>08:16:06</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="F16" t="n">
-        <v>2.03</v>
+        <v>2.17</v>
       </c>
       <c r="G16" t="n">
-        <v>214.5</v>
+        <v>211.5</v>
       </c>
       <c r="H16" t="n">
-        <v>79.5</v>
+        <v>66</v>
       </c>
       <c r="I16" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J16" t="n">
-        <v>3.24</v>
+        <v>-15.14</v>
       </c>
       <c r="K16" t="n">
-        <v>44.79</v>
+        <v>-14.9</v>
       </c>
       <c r="L16" t="n">
-        <v>44.91</v>
+        <v>21.24</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08:20:57</t>
+          <t>08:21:33</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.33</v>
+        <v>1.64</v>
       </c>
       <c r="F17" t="n">
-        <v>4.94</v>
+        <v>3.87</v>
       </c>
       <c r="G17" t="n">
-        <v>218.2</v>
+        <v>203.9</v>
       </c>
       <c r="H17" t="n">
-        <v>80.3</v>
+        <v>55</v>
       </c>
       <c r="I17" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="J17" t="n">
-        <v>-49.78</v>
+        <v>-34.67</v>
       </c>
       <c r="K17" t="n">
-        <v>22.51</v>
+        <v>-16.91</v>
       </c>
       <c r="L17" t="n">
-        <v>54.64</v>
+        <v>38.57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08:22:03</t>
+          <t>08:23:06</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.33</v>
+        <v>1.63</v>
       </c>
       <c r="F18" t="n">
-        <v>4.68</v>
+        <v>4.94</v>
       </c>
       <c r="G18" t="n">
-        <v>204.7</v>
+        <v>219.6</v>
       </c>
       <c r="H18" t="n">
-        <v>69.59999999999999</v>
+        <v>75.5</v>
       </c>
       <c r="I18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J18" t="n">
-        <v>-72.36</v>
+        <v>-26.97</v>
       </c>
       <c r="K18" t="n">
-        <v>32.96</v>
+        <v>-34.77</v>
       </c>
       <c r="L18" t="n">
-        <v>79.51000000000001</v>
+        <v>44</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08:24:39</t>
+          <t>08:25:13</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="F19" t="n">
-        <v>3.32</v>
+        <v>3.81</v>
       </c>
       <c r="G19" t="n">
-        <v>207.7</v>
+        <v>204.8</v>
       </c>
       <c r="H19" t="n">
-        <v>70.09999999999999</v>
+        <v>46.1</v>
       </c>
       <c r="I19" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>54.72</v>
+        <v>27.07</v>
       </c>
       <c r="K19" t="n">
-        <v>2.83</v>
+        <v>27.65</v>
       </c>
       <c r="L19" t="n">
-        <v>54.79</v>
+        <v>38.69</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08:30:04</t>
+          <t>08:30:13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.67</v>
+        <v>1.37</v>
       </c>
       <c r="F20" t="n">
-        <v>2.99</v>
+        <v>1.8</v>
       </c>
       <c r="G20" t="n">
-        <v>211.7</v>
+        <v>203.9</v>
       </c>
       <c r="H20" t="n">
-        <v>69.40000000000001</v>
+        <v>81.3</v>
       </c>
       <c r="I20" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J20" t="n">
-        <v>49.35</v>
+        <v>-64.06</v>
       </c>
       <c r="K20" t="n">
-        <v>73.73999999999999</v>
+        <v>-18.55</v>
       </c>
       <c r="L20" t="n">
-        <v>88.73</v>
+        <v>66.69</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08:31:52</t>
+          <t>08:31:32</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.51</v>
+        <v>1.42</v>
       </c>
       <c r="F21" t="n">
-        <v>4.94</v>
+        <v>3.77</v>
       </c>
       <c r="G21" t="n">
-        <v>206.1</v>
+        <v>211.1</v>
       </c>
       <c r="H21" t="n">
-        <v>71.3</v>
+        <v>27.7</v>
       </c>
       <c r="I21" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="J21" t="n">
-        <v>-95.44</v>
+        <v>75.43000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>29.21</v>
+        <v>-7.19</v>
       </c>
       <c r="L21" t="n">
-        <v>99.81</v>
+        <v>75.78</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08:33:26</t>
+          <t>08:33:08</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="F22" t="n">
-        <v>4.64</v>
+        <v>4.24</v>
       </c>
       <c r="G22" t="n">
-        <v>203.1</v>
+        <v>203.2</v>
       </c>
       <c r="H22" t="n">
-        <v>74.59999999999999</v>
+        <v>38.4</v>
       </c>
       <c r="I22" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="J22" t="n">
-        <v>-98.16</v>
+        <v>-22.06</v>
       </c>
       <c r="K22" t="n">
-        <v>10.07</v>
+        <v>-33.96</v>
       </c>
       <c r="L22" t="n">
-        <v>98.68000000000001</v>
+        <v>40.49</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08:37:25</t>
+          <t>08:38:22</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,28 +1003,28 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.49</v>
+        <v>1.61</v>
       </c>
       <c r="F23" t="n">
-        <v>2.71</v>
+        <v>1.91</v>
       </c>
       <c r="G23" t="n">
-        <v>214.6</v>
+        <v>207.2</v>
       </c>
       <c r="H23" t="n">
-        <v>79.09999999999999</v>
+        <v>42.2</v>
       </c>
       <c r="I23" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J23" t="n">
-        <v>103.08</v>
+        <v>-79.34</v>
       </c>
       <c r="K23" t="n">
-        <v>135.26</v>
+        <v>-62.63</v>
       </c>
       <c r="L23" t="n">
-        <v>170.06</v>
+        <v>101.08</v>
       </c>
     </row>
     <row r="24">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="F24" t="n">
         <v>4.94</v>
       </c>
       <c r="G24" t="n">
-        <v>214.2</v>
+        <v>197.8</v>
       </c>
       <c r="H24" t="n">
-        <v>70</v>
+        <v>56.4</v>
       </c>
       <c r="I24" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J24" t="n">
-        <v>41.55</v>
+        <v>-13.61</v>
       </c>
       <c r="K24" t="n">
-        <v>-97.63</v>
+        <v>-85.68000000000001</v>
       </c>
       <c r="L24" t="n">
-        <v>106.11</v>
+        <v>86.76000000000001</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08:40:32</t>
+          <t>08:41:27</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="F25" t="n">
-        <v>4.94</v>
+        <v>1.58</v>
       </c>
       <c r="G25" t="n">
-        <v>210.2</v>
+        <v>198.5</v>
       </c>
       <c r="H25" t="n">
-        <v>76.40000000000001</v>
+        <v>46.2</v>
       </c>
       <c r="I25" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J25" t="n">
-        <v>-108.17</v>
+        <v>-46.48</v>
       </c>
       <c r="K25" t="n">
-        <v>-49.19</v>
+        <v>-87.72</v>
       </c>
       <c r="L25" t="n">
-        <v>118.83</v>
+        <v>99.27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08:45:28</t>
+          <t>08:45:31</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="F26" t="n">
-        <v>1.9</v>
+        <v>4.94</v>
       </c>
       <c r="G26" t="n">
-        <v>207.8</v>
+        <v>203.5</v>
       </c>
       <c r="H26" t="n">
-        <v>73.90000000000001</v>
+        <v>43.6</v>
       </c>
       <c r="I26" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="J26" t="n">
-        <v>190.29</v>
+        <v>-35.17</v>
       </c>
       <c r="K26" t="n">
-        <v>49.82</v>
+        <v>139.88</v>
       </c>
       <c r="L26" t="n">
-        <v>196.71</v>
+        <v>144.24</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08:46:56</t>
+          <t>08:47:14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.39</v>
+        <v>1.61</v>
       </c>
       <c r="F27" t="n">
-        <v>1.69</v>
+        <v>4.94</v>
       </c>
       <c r="G27" t="n">
-        <v>213.9</v>
+        <v>210.7</v>
       </c>
       <c r="H27" t="n">
-        <v>70.2</v>
+        <v>29.6</v>
       </c>
       <c r="I27" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J27" t="n">
-        <v>-147.06</v>
+        <v>11.02</v>
       </c>
       <c r="K27" t="n">
-        <v>-106.47</v>
+        <v>-133.97</v>
       </c>
       <c r="L27" t="n">
-        <v>181.56</v>
+        <v>134.42</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08:48:53</t>
+          <t>08:47:59</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.25</v>
+        <v>1.49</v>
       </c>
       <c r="F28" t="n">
         <v>4.94</v>
       </c>
       <c r="G28" t="n">
-        <v>221.6</v>
+        <v>217.8</v>
       </c>
       <c r="H28" t="n">
-        <v>73.09999999999999</v>
+        <v>52.5</v>
       </c>
       <c r="I28" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="J28" t="n">
-        <v>175.48</v>
+        <v>-167.46</v>
       </c>
       <c r="K28" t="n">
-        <v>41.04</v>
+        <v>-48.07</v>
       </c>
       <c r="L28" t="n">
-        <v>180.21</v>
+        <v>174.22</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>08:58:58</t>
+          <t>09:00:19</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1255,34 +1255,34 @@
         <v>1</v>
       </c>
       <c r="E29" t="n">
-        <v>2.48</v>
+        <v>1.43</v>
       </c>
       <c r="F29" t="n">
         <v>4.94</v>
       </c>
       <c r="G29" t="n">
-        <v>206.6</v>
+        <v>208</v>
       </c>
       <c r="H29" t="n">
-        <v>76.59999999999999</v>
+        <v>31.8</v>
       </c>
       <c r="I29" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="J29" t="n">
-        <v>31.16</v>
+        <v>0.12</v>
       </c>
       <c r="K29" t="n">
-        <v>40.94</v>
+        <v>28.62</v>
       </c>
       <c r="L29" t="n">
-        <v>51.45</v>
+        <v>28.62</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09:00:07</t>
+          <t>09:01:31</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="F30" t="n">
-        <v>1.68</v>
+        <v>4.13</v>
       </c>
       <c r="G30" t="n">
-        <v>205.5</v>
+        <v>198.6</v>
       </c>
       <c r="H30" t="n">
-        <v>66.5</v>
+        <v>50.2</v>
       </c>
       <c r="I30" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J30" t="n">
-        <v>-16.13</v>
+        <v>26.42</v>
       </c>
       <c r="K30" t="n">
-        <v>39.2</v>
+        <v>4.69</v>
       </c>
       <c r="L30" t="n">
-        <v>42.39</v>
+        <v>26.84</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09:01:56</t>
+          <t>09:02:31</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="F31" t="n">
-        <v>3.65</v>
+        <v>4.32</v>
       </c>
       <c r="G31" t="n">
-        <v>206.4</v>
+        <v>212.5</v>
       </c>
       <c r="H31" t="n">
-        <v>69.90000000000001</v>
+        <v>45.2</v>
       </c>
       <c r="I31" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>-41.08</v>
+        <v>17.99</v>
       </c>
       <c r="K31" t="n">
-        <v>1.36</v>
+        <v>-24.06</v>
       </c>
       <c r="L31" t="n">
-        <v>41.1</v>
+        <v>30.04</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09:05:49</t>
+          <t>09:07:32</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="F32" t="n">
-        <v>4.22</v>
+        <v>4.94</v>
       </c>
       <c r="G32" t="n">
-        <v>208.8</v>
+        <v>214.2</v>
       </c>
       <c r="H32" t="n">
-        <v>75.90000000000001</v>
+        <v>42.2</v>
       </c>
       <c r="I32" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J32" t="n">
-        <v>-30.97</v>
+        <v>-29.34</v>
       </c>
       <c r="K32" t="n">
-        <v>-32.07</v>
+        <v>-30.18</v>
       </c>
       <c r="L32" t="n">
-        <v>44.58</v>
+        <v>42.09</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09:08:02</t>
+          <t>09:10:04</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1423,34 +1423,34 @@
         <v>2</v>
       </c>
       <c r="E33" t="n">
-        <v>1.56</v>
+        <v>1.49</v>
       </c>
       <c r="F33" t="n">
-        <v>4.94</v>
+        <v>3.57</v>
       </c>
       <c r="G33" t="n">
-        <v>219.7</v>
+        <v>212.2</v>
       </c>
       <c r="H33" t="n">
-        <v>69.8</v>
+        <v>39.1</v>
       </c>
       <c r="I33" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J33" t="n">
-        <v>59.91</v>
+        <v>20</v>
       </c>
       <c r="K33" t="n">
-        <v>29.94</v>
+        <v>-35.64</v>
       </c>
       <c r="L33" t="n">
-        <v>66.97</v>
+        <v>40.87</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09:09:13</t>
+          <t>09:10:54</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>2.41</v>
+        <v>1.39</v>
       </c>
       <c r="F34" t="n">
         <v>4.94</v>
       </c>
       <c r="G34" t="n">
-        <v>205.9</v>
+        <v>196.1</v>
       </c>
       <c r="H34" t="n">
-        <v>73.7</v>
+        <v>40.4</v>
       </c>
       <c r="I34" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J34" t="n">
-        <v>-71.43000000000001</v>
+        <v>1.75</v>
       </c>
       <c r="K34" t="n">
-        <v>-1.57</v>
+        <v>-35.03</v>
       </c>
       <c r="L34" t="n">
-        <v>71.45</v>
+        <v>35.08</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09:13:17</t>
+          <t>09:13:48</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.65</v>
+        <v>1.44</v>
       </c>
       <c r="F35" t="n">
-        <v>4.93</v>
+        <v>4.94</v>
       </c>
       <c r="G35" t="n">
-        <v>206.7</v>
+        <v>216.2</v>
       </c>
       <c r="H35" t="n">
-        <v>71.40000000000001</v>
+        <v>91.8</v>
       </c>
       <c r="I35" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-30.49</v>
+        <v>-39.03</v>
       </c>
       <c r="K35" t="n">
-        <v>115.18</v>
+        <v>-77.8</v>
       </c>
       <c r="L35" t="n">
-        <v>119.15</v>
+        <v>87.04000000000001</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09:15:19</t>
+          <t>09:15:00</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="F36" t="n">
         <v>4.94</v>
       </c>
       <c r="G36" t="n">
-        <v>214</v>
+        <v>215.8</v>
       </c>
       <c r="H36" t="n">
-        <v>75.3</v>
+        <v>61.3</v>
       </c>
       <c r="I36" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>-81.88</v>
+        <v>49.81</v>
       </c>
       <c r="K36" t="n">
-        <v>-19.89</v>
+        <v>25.47</v>
       </c>
       <c r="L36" t="n">
-        <v>84.26000000000001</v>
+        <v>55.94</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09:16:41</t>
+          <t>09:17:01</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.56</v>
+        <v>1.52</v>
       </c>
       <c r="F37" t="n">
-        <v>4.94</v>
+        <v>4.52</v>
       </c>
       <c r="G37" t="n">
-        <v>207.4</v>
+        <v>210.9</v>
       </c>
       <c r="H37" t="n">
-        <v>75.40000000000001</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="J37" t="n">
-        <v>13.51</v>
+        <v>29.31</v>
       </c>
       <c r="K37" t="n">
-        <v>-66.56999999999999</v>
+        <v>-66.14</v>
       </c>
       <c r="L37" t="n">
-        <v>67.93000000000001</v>
+        <v>72.34</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09:21:53</t>
+          <t>09:22:26</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.57</v>
+        <v>1.63</v>
       </c>
       <c r="F38" t="n">
-        <v>4.94</v>
+        <v>4.49</v>
       </c>
       <c r="G38" t="n">
-        <v>199.7</v>
+        <v>200.9</v>
       </c>
       <c r="H38" t="n">
-        <v>67.2</v>
+        <v>75.3</v>
       </c>
       <c r="I38" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="J38" t="n">
-        <v>-84.92</v>
+        <v>-93.23999999999999</v>
       </c>
       <c r="K38" t="n">
-        <v>-69.51000000000001</v>
+        <v>-35.26</v>
       </c>
       <c r="L38" t="n">
-        <v>109.74</v>
+        <v>99.68000000000001</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09:23:52</t>
+          <t>09:24:41</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="F39" t="n">
-        <v>4.09</v>
+        <v>3.43</v>
       </c>
       <c r="G39" t="n">
-        <v>207.1</v>
+        <v>208.2</v>
       </c>
       <c r="H39" t="n">
-        <v>75</v>
+        <v>11.1</v>
       </c>
       <c r="I39" t="n">
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-119.37</v>
+        <v>60.97</v>
       </c>
       <c r="K39" t="n">
-        <v>-15.78</v>
+        <v>-52.55</v>
       </c>
       <c r="L39" t="n">
-        <v>120.41</v>
+        <v>80.48999999999999</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09:26:13</t>
+          <t>09:26:01</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1720,31 +1720,31 @@
         <v>1.35</v>
       </c>
       <c r="F40" t="n">
-        <v>1.65</v>
+        <v>2.6</v>
       </c>
       <c r="G40" t="n">
-        <v>208.1</v>
+        <v>212.9</v>
       </c>
       <c r="H40" t="n">
-        <v>69.8</v>
+        <v>18.5</v>
       </c>
       <c r="I40" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J40" t="n">
-        <v>-59.62</v>
+        <v>81.65000000000001</v>
       </c>
       <c r="K40" t="n">
-        <v>-75.08</v>
+        <v>31.94</v>
       </c>
       <c r="L40" t="n">
-        <v>95.87</v>
+        <v>87.68000000000001</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09:30:10</t>
+          <t>09:30:02</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="F41" t="n">
-        <v>3.06</v>
+        <v>2.43</v>
       </c>
       <c r="G41" t="n">
-        <v>211.5</v>
+        <v>200.8</v>
       </c>
       <c r="H41" t="n">
-        <v>73.40000000000001</v>
+        <v>27.5</v>
       </c>
       <c r="I41" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J41" t="n">
-        <v>157.55</v>
+        <v>-43.75</v>
       </c>
       <c r="K41" t="n">
-        <v>-65.34</v>
+        <v>-74.31</v>
       </c>
       <c r="L41" t="n">
-        <v>170.56</v>
+        <v>86.23</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09:32:19</t>
+          <t>09:32:28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.45</v>
+        <v>1.35</v>
       </c>
       <c r="F42" t="n">
-        <v>1.75</v>
+        <v>4.94</v>
       </c>
       <c r="G42" t="n">
-        <v>210.8</v>
+        <v>206</v>
       </c>
       <c r="H42" t="n">
-        <v>74</v>
+        <v>29.5</v>
       </c>
       <c r="I42" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="J42" t="n">
-        <v>-205.51</v>
+        <v>-94.56999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>-70.56999999999999</v>
+        <v>-95.91</v>
       </c>
       <c r="L42" t="n">
-        <v>217.29</v>
+        <v>134.7</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09:32:57</t>
+          <t>09:33:17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.32</v>
+        <v>1.88</v>
       </c>
       <c r="F43" t="n">
-        <v>3.62</v>
+        <v>4.94</v>
       </c>
       <c r="G43" t="n">
-        <v>203.1</v>
+        <v>194.7</v>
       </c>
       <c r="H43" t="n">
-        <v>78.5</v>
+        <v>51.3</v>
       </c>
       <c r="I43" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J43" t="n">
-        <v>-79.5</v>
+        <v>-66.7</v>
       </c>
       <c r="K43" t="n">
-        <v>107.24</v>
+        <v>-85.91</v>
       </c>
       <c r="L43" t="n">
-        <v>133.49</v>
+        <v>108.76</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09:46:02</t>
+          <t>09:44:31</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="F44" t="n">
         <v>4.94</v>
       </c>
       <c r="G44" t="n">
-        <v>212.7</v>
+        <v>205</v>
       </c>
       <c r="H44" t="n">
-        <v>68.8</v>
+        <v>56</v>
       </c>
       <c r="I44" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="J44" t="n">
-        <v>33.9</v>
+        <v>1.72</v>
       </c>
       <c r="K44" t="n">
-        <v>-44.42</v>
+        <v>-44.45</v>
       </c>
       <c r="L44" t="n">
-        <v>55.88</v>
+        <v>44.48</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09:48:03</t>
+          <t>09:46:35</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>2.28</v>
+        <v>1.57</v>
       </c>
       <c r="F45" t="n">
-        <v>4.94</v>
+        <v>4.46</v>
       </c>
       <c r="G45" t="n">
-        <v>205.5</v>
+        <v>194</v>
       </c>
       <c r="H45" t="n">
-        <v>68.5</v>
+        <v>31.5</v>
       </c>
       <c r="I45" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J45" t="n">
-        <v>39.9</v>
+        <v>18.89</v>
       </c>
       <c r="K45" t="n">
-        <v>34.63</v>
+        <v>-25.93</v>
       </c>
       <c r="L45" t="n">
-        <v>52.83</v>
+        <v>32.09</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09:50:42</t>
+          <t>09:48:19</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>1.39</v>
       </c>
       <c r="F46" t="n">
-        <v>4.94</v>
+        <v>3.72</v>
       </c>
       <c r="G46" t="n">
-        <v>204.9</v>
+        <v>207.7</v>
       </c>
       <c r="H46" t="n">
-        <v>74.7</v>
+        <v>73</v>
       </c>
       <c r="I46" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J46" t="n">
-        <v>9.4</v>
+        <v>-5.48</v>
       </c>
       <c r="K46" t="n">
-        <v>-70.38</v>
+        <v>-29.52</v>
       </c>
       <c r="L46" t="n">
-        <v>71</v>
+        <v>30.02</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:54:47</t>
+          <t>09:52:25</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="F47" t="n">
-        <v>4.94</v>
+        <v>1.9</v>
       </c>
       <c r="G47" t="n">
-        <v>209.5</v>
+        <v>207.2</v>
       </c>
       <c r="H47" t="n">
-        <v>70.59999999999999</v>
+        <v>25.2</v>
       </c>
       <c r="I47" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J47" t="n">
-        <v>-8.789999999999999</v>
+        <v>-10.82</v>
       </c>
       <c r="K47" t="n">
-        <v>-76.92</v>
+        <v>-44.31</v>
       </c>
       <c r="L47" t="n">
-        <v>77.42</v>
+        <v>45.61</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:56:45</t>
+          <t>09:54:31</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.53</v>
+        <v>1.7</v>
       </c>
       <c r="F48" t="n">
-        <v>4.32</v>
+        <v>4.35</v>
       </c>
       <c r="G48" t="n">
-        <v>202</v>
+        <v>217.9</v>
       </c>
       <c r="H48" t="n">
-        <v>76.59999999999999</v>
+        <v>31.8</v>
       </c>
       <c r="I48" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="J48" t="n">
-        <v>41.83</v>
+        <v>-10.79</v>
       </c>
       <c r="K48" t="n">
-        <v>-24.2</v>
+        <v>48.57</v>
       </c>
       <c r="L48" t="n">
-        <v>48.32</v>
+        <v>49.76</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:58:28</t>
+          <t>09:55:16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.92</v>
+        <v>1.5</v>
       </c>
       <c r="F49" t="n">
-        <v>3.71</v>
+        <v>4.94</v>
       </c>
       <c r="G49" t="n">
-        <v>200.8</v>
+        <v>216.4</v>
       </c>
       <c r="H49" t="n">
-        <v>69.90000000000001</v>
+        <v>60.8</v>
       </c>
       <c r="I49" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J49" t="n">
-        <v>-59</v>
+        <v>-41.82</v>
       </c>
       <c r="K49" t="n">
-        <v>-19.75</v>
+        <v>19.11</v>
       </c>
       <c r="L49" t="n">
-        <v>62.21</v>
+        <v>45.98</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10:03:11</t>
+          <t>10:00:32</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="F50" t="n">
-        <v>4.94</v>
+        <v>3.31</v>
       </c>
       <c r="G50" t="n">
-        <v>204.4</v>
+        <v>211.1</v>
       </c>
       <c r="H50" t="n">
-        <v>67</v>
+        <v>5.3</v>
       </c>
       <c r="I50" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="J50" t="n">
-        <v>22.53</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="K50" t="n">
-        <v>-99.51000000000001</v>
+        <v>55.78</v>
       </c>
       <c r="L50" t="n">
-        <v>102.03</v>
+        <v>56.39</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10:04:20</t>
+          <t>10:02:39</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.85</v>
+        <v>1.47</v>
       </c>
       <c r="F51" t="n">
-        <v>4.94</v>
+        <v>1.79</v>
       </c>
       <c r="G51" t="n">
-        <v>207.8</v>
+        <v>208.8</v>
       </c>
       <c r="H51" t="n">
-        <v>74.90000000000001</v>
+        <v>56</v>
       </c>
       <c r="I51" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J51" t="n">
-        <v>136.1</v>
+        <v>47.51</v>
       </c>
       <c r="K51" t="n">
-        <v>-17.34</v>
+        <v>-48.06</v>
       </c>
       <c r="L51" t="n">
-        <v>137.2</v>
+        <v>67.58</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10:06:20</t>
+          <t>10:03:33</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.49</v>
+        <v>2.4</v>
       </c>
       <c r="F52" t="n">
         <v>4.94</v>
       </c>
       <c r="G52" t="n">
-        <v>194.5</v>
+        <v>215.8</v>
       </c>
       <c r="H52" t="n">
-        <v>74.7</v>
+        <v>46.4</v>
       </c>
       <c r="I52" t="n">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="J52" t="n">
-        <v>29.67</v>
+        <v>-88.76000000000001</v>
       </c>
       <c r="K52" t="n">
-        <v>-90.88</v>
+        <v>-4.97</v>
       </c>
       <c r="L52" t="n">
-        <v>95.59999999999999</v>
+        <v>88.90000000000001</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10:10:06</t>
+          <t>10:07:14</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="F53" t="n">
         <v>4.94</v>
       </c>
       <c r="G53" t="n">
-        <v>200.7</v>
+        <v>217.2</v>
       </c>
       <c r="H53" t="n">
-        <v>76.8</v>
+        <v>67.90000000000001</v>
       </c>
       <c r="I53" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J53" t="n">
-        <v>50.12</v>
+        <v>33.47</v>
       </c>
       <c r="K53" t="n">
-        <v>-136.06</v>
+        <v>-96.23</v>
       </c>
       <c r="L53" t="n">
-        <v>145</v>
+        <v>101.89</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10:12:48</t>
+          <t>10:09:03</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.61</v>
+        <v>1.35</v>
       </c>
       <c r="F54" t="n">
-        <v>4.93</v>
+        <v>4.3</v>
       </c>
       <c r="G54" t="n">
-        <v>207.9</v>
+        <v>213.7</v>
       </c>
       <c r="H54" t="n">
-        <v>75</v>
+        <v>27.4</v>
       </c>
       <c r="I54" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J54" t="n">
-        <v>-133.1</v>
+        <v>-18.24</v>
       </c>
       <c r="K54" t="n">
-        <v>-25.28</v>
+        <v>-93.12</v>
       </c>
       <c r="L54" t="n">
-        <v>135.48</v>
+        <v>94.89</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10:14:02</t>
+          <t>10:10:14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="F55" t="n">
-        <v>4.86</v>
+        <v>2.48</v>
       </c>
       <c r="G55" t="n">
-        <v>203.9</v>
+        <v>215.3</v>
       </c>
       <c r="H55" t="n">
-        <v>71.90000000000001</v>
+        <v>58.4</v>
       </c>
       <c r="I55" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J55" t="n">
-        <v>79.34</v>
+        <v>3.61</v>
       </c>
       <c r="K55" t="n">
-        <v>169.08</v>
+        <v>99.90000000000001</v>
       </c>
       <c r="L55" t="n">
-        <v>186.77</v>
+        <v>99.97</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10:18:34</t>
+          <t>10:14:36</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.47</v>
+        <v>1.32</v>
       </c>
       <c r="F56" t="n">
-        <v>4.94</v>
+        <v>1.62</v>
       </c>
       <c r="G56" t="n">
-        <v>199.2</v>
+        <v>201.9</v>
       </c>
       <c r="H56" t="n">
-        <v>72.40000000000001</v>
+        <v>38.9</v>
       </c>
       <c r="I56" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J56" t="n">
-        <v>284</v>
+        <v>10.89</v>
       </c>
       <c r="K56" t="n">
-        <v>8.140000000000001</v>
+        <v>141.26</v>
       </c>
       <c r="L56" t="n">
-        <v>284.12</v>
+        <v>141.68</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10:20:22</t>
+          <t>10:15:59</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.48</v>
+        <v>1.59</v>
       </c>
       <c r="F57" t="n">
-        <v>2.6</v>
+        <v>4.94</v>
       </c>
       <c r="G57" t="n">
-        <v>201.9</v>
+        <v>205.4</v>
       </c>
       <c r="H57" t="n">
-        <v>76.40000000000001</v>
+        <v>42.2</v>
       </c>
       <c r="I57" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J57" t="n">
-        <v>36.32</v>
+        <v>41.2</v>
       </c>
       <c r="K57" t="n">
-        <v>-133.37</v>
+        <v>95.26000000000001</v>
       </c>
       <c r="L57" t="n">
-        <v>138.23</v>
+        <v>103.78</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10:22:05</t>
+          <t>10:17:57</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.49</v>
+        <v>1.66</v>
       </c>
       <c r="F58" t="n">
-        <v>4.94</v>
+        <v>4.57</v>
       </c>
       <c r="G58" t="n">
-        <v>214.8</v>
+        <v>205.9</v>
       </c>
       <c r="H58" t="n">
-        <v>72.09999999999999</v>
+        <v>65</v>
       </c>
       <c r="I58" t="n">
         <v>23</v>
       </c>
       <c r="J58" t="n">
-        <v>-94.62</v>
+        <v>147.21</v>
       </c>
       <c r="K58" t="n">
-        <v>-167.28</v>
+        <v>21.38</v>
       </c>
       <c r="L58" t="n">
-        <v>192.19</v>
+        <v>148.75</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10:33:16</t>
+          <t>10:27:29</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.63</v>
+        <v>1.49</v>
       </c>
       <c r="F59" t="n">
-        <v>2.03</v>
+        <v>2.71</v>
       </c>
       <c r="G59" t="n">
-        <v>203.7</v>
+        <v>216.1</v>
       </c>
       <c r="H59" t="n">
-        <v>76.59999999999999</v>
+        <v>46.2</v>
       </c>
       <c r="I59" t="n">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="J59" t="n">
-        <v>-9.619999999999999</v>
+        <v>28.92</v>
       </c>
       <c r="K59" t="n">
-        <v>-30.93</v>
+        <v>17.52</v>
       </c>
       <c r="L59" t="n">
-        <v>32.4</v>
+        <v>33.81</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10:35:12</t>
+          <t>10:29:55</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.6</v>
+        <v>1.66</v>
       </c>
       <c r="F60" t="n">
-        <v>4.2</v>
+        <v>4.94</v>
       </c>
       <c r="G60" t="n">
-        <v>205.9</v>
+        <v>214.4</v>
       </c>
       <c r="H60" t="n">
-        <v>72.09999999999999</v>
+        <v>54.9</v>
       </c>
       <c r="I60" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J60" t="n">
-        <v>1.29</v>
+        <v>-20.38</v>
       </c>
       <c r="K60" t="n">
-        <v>44.7</v>
+        <v>10.3</v>
       </c>
       <c r="L60" t="n">
-        <v>44.72</v>
+        <v>22.84</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10:36:29</t>
+          <t>10:31:28</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="F61" t="n">
-        <v>1.84</v>
+        <v>3.81</v>
       </c>
       <c r="G61" t="n">
-        <v>215.1</v>
+        <v>206.2</v>
       </c>
       <c r="H61" t="n">
-        <v>68.09999999999999</v>
+        <v>43.2</v>
       </c>
       <c r="I61" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="J61" t="n">
-        <v>24.82</v>
+        <v>-21.74</v>
       </c>
       <c r="K61" t="n">
-        <v>38.77</v>
+        <v>2.34</v>
       </c>
       <c r="L61" t="n">
-        <v>46.04</v>
+        <v>21.86</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10:39:46</t>
+          <t>10:36:50</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="F62" t="n">
-        <v>4.94</v>
+        <v>4.7</v>
       </c>
       <c r="G62" t="n">
-        <v>211.6</v>
+        <v>201.3</v>
       </c>
       <c r="H62" t="n">
-        <v>74.5</v>
+        <v>56.5</v>
       </c>
       <c r="I62" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="J62" t="n">
-        <v>51.05</v>
+        <v>-17.09</v>
       </c>
       <c r="K62" t="n">
-        <v>22.03</v>
+        <v>-37.88</v>
       </c>
       <c r="L62" t="n">
-        <v>55.6</v>
+        <v>41.56</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10:40:28</t>
+          <t>10:38:20</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.81</v>
+        <v>1.69</v>
       </c>
       <c r="F63" t="n">
         <v>4.94</v>
       </c>
       <c r="G63" t="n">
-        <v>201.8</v>
+        <v>210.2</v>
       </c>
       <c r="H63" t="n">
-        <v>77.8</v>
+        <v>78.7</v>
       </c>
       <c r="I63" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J63" t="n">
-        <v>40.45</v>
+        <v>-13.28</v>
       </c>
       <c r="K63" t="n">
-        <v>-67.33</v>
+        <v>-29.57</v>
       </c>
       <c r="L63" t="n">
-        <v>78.54000000000001</v>
+        <v>32.41</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10:41:36</t>
+          <t>10:40:09</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.46</v>
+        <v>1.7</v>
       </c>
       <c r="F64" t="n">
         <v>4.94</v>
       </c>
       <c r="G64" t="n">
-        <v>183</v>
+        <v>189.6</v>
       </c>
       <c r="H64" t="n">
-        <v>72.3</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="I64" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="J64" t="n">
-        <v>51.03</v>
+        <v>28.87</v>
       </c>
       <c r="K64" t="n">
-        <v>37.11</v>
+        <v>31.4</v>
       </c>
       <c r="L64" t="n">
-        <v>63.09</v>
+        <v>42.66</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10:47:40</t>
+          <t>10:44:33</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.69</v>
+        <v>1.53</v>
       </c>
       <c r="F65" t="n">
-        <v>4.63</v>
+        <v>4.94</v>
       </c>
       <c r="G65" t="n">
-        <v>210</v>
+        <v>217.2</v>
       </c>
       <c r="H65" t="n">
-        <v>70.90000000000001</v>
+        <v>62.8</v>
       </c>
       <c r="I65" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J65" t="n">
-        <v>55.05</v>
+        <v>79.78</v>
       </c>
       <c r="K65" t="n">
-        <v>-111.65</v>
+        <v>-31.83</v>
       </c>
       <c r="L65" t="n">
-        <v>124.48</v>
+        <v>85.90000000000001</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10:49:14</t>
+          <t>10:45:51</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="F66" t="n">
-        <v>2.64</v>
+        <v>4.94</v>
       </c>
       <c r="G66" t="n">
-        <v>196.9</v>
+        <v>214.7</v>
       </c>
       <c r="H66" t="n">
-        <v>74.40000000000001</v>
+        <v>24.8</v>
       </c>
       <c r="I66" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J66" t="n">
-        <v>-43.04</v>
+        <v>0.23</v>
       </c>
       <c r="K66" t="n">
-        <v>76.73999999999999</v>
+        <v>76.72</v>
       </c>
       <c r="L66" t="n">
-        <v>87.98999999999999</v>
+        <v>76.72</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10:50:18</t>
+          <t>10:47:42</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.7</v>
+        <v>1.51</v>
       </c>
       <c r="F67" t="n">
-        <v>4.94</v>
+        <v>3.89</v>
       </c>
       <c r="G67" t="n">
-        <v>206.9</v>
+        <v>213.8</v>
       </c>
       <c r="H67" t="n">
-        <v>74.40000000000001</v>
+        <v>32.2</v>
       </c>
       <c r="I67" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="J67" t="n">
-        <v>44.28</v>
+        <v>27.78</v>
       </c>
       <c r="K67" t="n">
-        <v>-88.75</v>
+        <v>-53.95</v>
       </c>
       <c r="L67" t="n">
-        <v>99.18000000000001</v>
+        <v>60.68</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:54:20</t>
+          <t>10:52:58</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="F68" t="n">
         <v>4.94</v>
       </c>
       <c r="G68" t="n">
-        <v>208.7</v>
+        <v>195.4</v>
       </c>
       <c r="H68" t="n">
-        <v>76.09999999999999</v>
+        <v>44.7</v>
       </c>
       <c r="I68" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J68" t="n">
-        <v>-56.86</v>
+        <v>67.83</v>
       </c>
       <c r="K68" t="n">
-        <v>-111.58</v>
+        <v>77.27</v>
       </c>
       <c r="L68" t="n">
-        <v>125.23</v>
+        <v>102.81</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:56:33</t>
+          <t>10:54:56</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.72</v>
+        <v>1.49</v>
       </c>
       <c r="F69" t="n">
-        <v>4.94</v>
+        <v>4.39</v>
       </c>
       <c r="G69" t="n">
-        <v>207.4</v>
+        <v>209.9</v>
       </c>
       <c r="H69" t="n">
-        <v>73.7</v>
+        <v>42.8</v>
       </c>
       <c r="I69" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J69" t="n">
-        <v>34.42</v>
+        <v>-71.18000000000001</v>
       </c>
       <c r="K69" t="n">
-        <v>-87.2</v>
+        <v>-44.04</v>
       </c>
       <c r="L69" t="n">
-        <v>93.75</v>
+        <v>83.7</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:57:37</t>
+          <t>10:57:07</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.62</v>
+        <v>1.49</v>
       </c>
       <c r="F70" t="n">
         <v>4.94</v>
       </c>
       <c r="G70" t="n">
-        <v>206.2</v>
+        <v>206.6</v>
       </c>
       <c r="H70" t="n">
-        <v>71.40000000000001</v>
+        <v>52.9</v>
       </c>
       <c r="I70" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="J70" t="n">
-        <v>-86.94</v>
+        <v>-99.97</v>
       </c>
       <c r="K70" t="n">
-        <v>-25.41</v>
+        <v>-68.58</v>
       </c>
       <c r="L70" t="n">
-        <v>90.58</v>
+        <v>121.23</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>11:03:20</t>
+          <t>11:01:11</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>2.49</v>
+        <v>1.74</v>
       </c>
       <c r="F71" t="n">
-        <v>4.94</v>
+        <v>4</v>
       </c>
       <c r="G71" t="n">
-        <v>218</v>
+        <v>213.2</v>
       </c>
       <c r="H71" t="n">
-        <v>76.3</v>
+        <v>86.8</v>
       </c>
       <c r="I71" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="J71" t="n">
-        <v>201.05</v>
+        <v>-163.28</v>
       </c>
       <c r="K71" t="n">
-        <v>-76.94</v>
+        <v>65.91</v>
       </c>
       <c r="L71" t="n">
-        <v>215.28</v>
+        <v>176.08</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>11:04:28</t>
+          <t>11:02:25</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.77</v>
+        <v>1.58</v>
       </c>
       <c r="F72" t="n">
-        <v>2.8</v>
+        <v>3.88</v>
       </c>
       <c r="G72" t="n">
-        <v>204.8</v>
+        <v>198.4</v>
       </c>
       <c r="H72" t="n">
-        <v>68.40000000000001</v>
+        <v>42.7</v>
       </c>
       <c r="I72" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="J72" t="n">
-        <v>-20.24</v>
+        <v>-107.87</v>
       </c>
       <c r="K72" t="n">
-        <v>-122.92</v>
+        <v>-108.69</v>
       </c>
       <c r="L72" t="n">
-        <v>124.58</v>
+        <v>153.13</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>11:05:49</t>
+          <t>11:04:21</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>2.12</v>
+        <v>1.6</v>
       </c>
       <c r="F73" t="n">
         <v>4.94</v>
       </c>
       <c r="G73" t="n">
-        <v>211.2</v>
+        <v>215.4</v>
       </c>
       <c r="H73" t="n">
-        <v>70.90000000000001</v>
+        <v>56.2</v>
       </c>
       <c r="I73" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J73" t="n">
-        <v>56</v>
+        <v>29.7</v>
       </c>
       <c r="K73" t="n">
-        <v>-49.05</v>
+        <v>-133.27</v>
       </c>
       <c r="L73" t="n">
-        <v>74.44</v>
+        <v>136.54</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>11:16:18</t>
+          <t>11:13:57</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="F74" t="n">
         <v>4.94</v>
       </c>
       <c r="G74" t="n">
-        <v>210.8</v>
+        <v>219.9</v>
       </c>
       <c r="H74" t="n">
-        <v>71.09999999999999</v>
+        <v>44.2</v>
       </c>
       <c r="I74" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="J74" t="n">
-        <v>36.84</v>
+        <v>-17.84</v>
       </c>
       <c r="K74" t="n">
-        <v>17.03</v>
+        <v>-12.72</v>
       </c>
       <c r="L74" t="n">
-        <v>40.59</v>
+        <v>21.92</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>11:17:31</t>
+          <t>11:15:59</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>2.02</v>
+        <v>1.55</v>
       </c>
       <c r="F75" t="n">
-        <v>4.57</v>
+        <v>2.79</v>
       </c>
       <c r="G75" t="n">
-        <v>190.3</v>
+        <v>198.7</v>
       </c>
       <c r="H75" t="n">
-        <v>66</v>
+        <v>48.3</v>
       </c>
       <c r="I75" t="n">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J75" t="n">
-        <v>-35.71</v>
+        <v>6.06</v>
       </c>
       <c r="K75" t="n">
-        <v>48.19</v>
+        <v>19.74</v>
       </c>
       <c r="L75" t="n">
-        <v>59.98</v>
+        <v>20.65</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>11:19:03</t>
+          <t>11:18:10</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="F76" t="n">
         <v>4.94</v>
       </c>
       <c r="G76" t="n">
-        <v>221.1</v>
+        <v>193.3</v>
       </c>
       <c r="H76" t="n">
-        <v>79.59999999999999</v>
+        <v>44.6</v>
       </c>
       <c r="I76" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J76" t="n">
-        <v>-45.28</v>
+        <v>-31.87</v>
       </c>
       <c r="K76" t="n">
-        <v>-13.4</v>
+        <v>-10.79</v>
       </c>
       <c r="L76" t="n">
-        <v>47.22</v>
+        <v>33.65</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>11:24:03</t>
+          <t>11:22:35</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.72</v>
+        <v>1.57</v>
       </c>
       <c r="F77" t="n">
         <v>4.94</v>
       </c>
       <c r="G77" t="n">
-        <v>203.8</v>
+        <v>213.7</v>
       </c>
       <c r="H77" t="n">
-        <v>68.09999999999999</v>
+        <v>54</v>
       </c>
       <c r="I77" t="n">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="J77" t="n">
-        <v>-54.54</v>
+        <v>-33.91</v>
       </c>
       <c r="K77" t="n">
-        <v>-21.33</v>
+        <v>-18.14</v>
       </c>
       <c r="L77" t="n">
-        <v>58.57</v>
+        <v>38.46</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>11:25:39</t>
+          <t>11:24:26</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="F78" t="n">
-        <v>4.94</v>
+        <v>4.46</v>
       </c>
       <c r="G78" t="n">
-        <v>204.9</v>
+        <v>222.1</v>
       </c>
       <c r="H78" t="n">
-        <v>74.90000000000001</v>
+        <v>81.8</v>
       </c>
       <c r="I78" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J78" t="n">
-        <v>-43.4</v>
+        <v>-23.92</v>
       </c>
       <c r="K78" t="n">
-        <v>-33.58</v>
+        <v>12.66</v>
       </c>
       <c r="L78" t="n">
-        <v>54.87</v>
+        <v>27.07</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>11:27:15</t>
+          <t>11:26:54</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.72</v>
+        <v>1.6</v>
       </c>
       <c r="F79" t="n">
-        <v>4.94</v>
+        <v>2.8</v>
       </c>
       <c r="G79" t="n">
-        <v>194.9</v>
+        <v>217.6</v>
       </c>
       <c r="H79" t="n">
-        <v>72.3</v>
+        <v>10.4</v>
       </c>
       <c r="I79" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J79" t="n">
-        <v>32.4</v>
+        <v>31.9</v>
       </c>
       <c r="K79" t="n">
-        <v>50.45</v>
+        <v>-7.4</v>
       </c>
       <c r="L79" t="n">
-        <v>59.96</v>
+        <v>32.75</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>11:31:31</t>
+          <t>11:31:26</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3400,31 +3400,31 @@
         <v>1.5</v>
       </c>
       <c r="F80" t="n">
-        <v>4.94</v>
+        <v>2.83</v>
       </c>
       <c r="G80" t="n">
-        <v>207.4</v>
+        <v>186.3</v>
       </c>
       <c r="H80" t="n">
-        <v>71.7</v>
+        <v>48.6</v>
       </c>
       <c r="I80" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J80" t="n">
-        <v>-88.98999999999999</v>
+        <v>-61.06</v>
       </c>
       <c r="K80" t="n">
-        <v>17.86</v>
+        <v>-37.86</v>
       </c>
       <c r="L80" t="n">
-        <v>90.76000000000001</v>
+        <v>71.84999999999999</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>11:32:39</t>
+          <t>11:33:22</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="F81" t="n">
         <v>4.94</v>
       </c>
       <c r="G81" t="n">
-        <v>217.7</v>
+        <v>211.5</v>
       </c>
       <c r="H81" t="n">
-        <v>68.59999999999999</v>
+        <v>39.7</v>
       </c>
       <c r="I81" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J81" t="n">
-        <v>26.88</v>
+        <v>-40.62</v>
       </c>
       <c r="K81" t="n">
-        <v>-104.86</v>
+        <v>51.26</v>
       </c>
       <c r="L81" t="n">
-        <v>108.25</v>
+        <v>65.41</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>11:34:18</t>
+          <t>11:35:10</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.48</v>
+        <v>1.64</v>
       </c>
       <c r="F82" t="n">
-        <v>4.31</v>
+        <v>4.94</v>
       </c>
       <c r="G82" t="n">
-        <v>199.3</v>
+        <v>208.9</v>
       </c>
       <c r="H82" t="n">
-        <v>80.59999999999999</v>
+        <v>54.4</v>
       </c>
       <c r="I82" t="n">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="J82" t="n">
-        <v>-23.33</v>
+        <v>-45.08</v>
       </c>
       <c r="K82" t="n">
-        <v>128.38</v>
+        <v>-42.7</v>
       </c>
       <c r="L82" t="n">
-        <v>130.48</v>
+        <v>62.09</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>11:38:50</t>
+          <t>11:39:43</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="F83" t="n">
         <v>4.94</v>
       </c>
       <c r="G83" t="n">
-        <v>211.1</v>
+        <v>207.7</v>
       </c>
       <c r="H83" t="n">
-        <v>84.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="I83" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J83" t="n">
-        <v>90.90000000000001</v>
+        <v>-103.33</v>
       </c>
       <c r="K83" t="n">
-        <v>-146.44</v>
+        <v>-41.39</v>
       </c>
       <c r="L83" t="n">
-        <v>172.36</v>
+        <v>111.31</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>11:41:26</t>
+          <t>11:40:35</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.55</v>
+        <v>1.66</v>
       </c>
       <c r="F84" t="n">
-        <v>4.94</v>
+        <v>1.96</v>
       </c>
       <c r="G84" t="n">
-        <v>206.9</v>
+        <v>201.9</v>
       </c>
       <c r="H84" t="n">
-        <v>68.5</v>
+        <v>48.2</v>
       </c>
       <c r="I84" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="J84" t="n">
-        <v>-158.43</v>
+        <v>-93.06</v>
       </c>
       <c r="K84" t="n">
-        <v>-62.8</v>
+        <v>-63.66</v>
       </c>
       <c r="L84" t="n">
-        <v>170.42</v>
+        <v>112.75</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>11:43:56</t>
+          <t>11:42:51</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="F85" t="n">
-        <v>4.94</v>
+        <v>4.6</v>
       </c>
       <c r="G85" t="n">
-        <v>207.5</v>
+        <v>219.5</v>
       </c>
       <c r="H85" t="n">
-        <v>75.09999999999999</v>
+        <v>72.3</v>
       </c>
       <c r="I85" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="J85" t="n">
-        <v>-106.3</v>
+        <v>63.59</v>
       </c>
       <c r="K85" t="n">
-        <v>28.97</v>
+        <v>-93.70999999999999</v>
       </c>
       <c r="L85" t="n">
-        <v>110.18</v>
+        <v>113.25</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>11:47:08</t>
+          <t>11:47:31</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.58</v>
+        <v>1.53</v>
       </c>
       <c r="F86" t="n">
-        <v>3.52</v>
+        <v>3.38</v>
       </c>
       <c r="G86" t="n">
-        <v>211.6</v>
+        <v>230.7</v>
       </c>
       <c r="H86" t="n">
-        <v>75.5</v>
+        <v>49.8</v>
       </c>
       <c r="I86" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J86" t="n">
-        <v>-7.91</v>
+        <v>33.82</v>
       </c>
       <c r="K86" t="n">
-        <v>-234.68</v>
+        <v>-112.33</v>
       </c>
       <c r="L86" t="n">
-        <v>234.81</v>
+        <v>117.31</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11:48:21</t>
+          <t>11:49:04</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>1.42</v>
+        <v>2.13</v>
       </c>
       <c r="F87" t="n">
-        <v>4.94</v>
+        <v>4.43</v>
       </c>
       <c r="G87" t="n">
-        <v>212.3</v>
+        <v>211.8</v>
       </c>
       <c r="H87" t="n">
-        <v>79.3</v>
+        <v>32.4</v>
       </c>
       <c r="I87" t="n">
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>157.67</v>
+        <v>64.17</v>
       </c>
       <c r="K87" t="n">
-        <v>-165.96</v>
+        <v>-85.94</v>
       </c>
       <c r="L87" t="n">
-        <v>228.92</v>
+        <v>107.25</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11:50:34</t>
+          <t>11:50:49</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.74</v>
+        <v>1.56</v>
       </c>
       <c r="F88" t="n">
-        <v>4.94</v>
+        <v>4.07</v>
       </c>
       <c r="G88" t="n">
-        <v>208.9</v>
+        <v>205.4</v>
       </c>
       <c r="H88" t="n">
-        <v>78.7</v>
+        <v>47.2</v>
       </c>
       <c r="I88" t="n">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>-39.21</v>
+        <v>104.5</v>
       </c>
       <c r="K88" t="n">
-        <v>220.4</v>
+        <v>-23.99</v>
       </c>
       <c r="L88" t="n">
-        <v>223.86</v>
+        <v>107.21</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-27.xlsx
+++ b/output/2024-10-27.xlsx
@@ -625,34 +625,34 @@
         <v>1</v>
       </c>
       <c r="E14" t="n">
-        <v>1.17</v>
+        <v>1.41</v>
       </c>
       <c r="F14" t="n">
-        <v>1.47</v>
+        <v>3.16</v>
       </c>
       <c r="G14" t="n">
-        <v>218.1</v>
+        <v>211.5</v>
       </c>
       <c r="H14" t="n">
-        <v>60.5</v>
+        <v>39.7</v>
       </c>
       <c r="I14" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J14" t="n">
-        <v>-24.73</v>
+        <v>20.79</v>
       </c>
       <c r="K14" t="n">
-        <v>12.78</v>
+        <v>-20.94</v>
       </c>
       <c r="L14" t="n">
-        <v>27.84</v>
+        <v>29.5</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>08:13:52</t>
+          <t>08:13:43</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -667,34 +667,34 @@
         <v>2</v>
       </c>
       <c r="E15" t="n">
-        <v>1.2</v>
+        <v>1.13</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="G15" t="n">
-        <v>203.4</v>
+        <v>211.8</v>
       </c>
       <c r="H15" t="n">
-        <v>34.6</v>
+        <v>49.8</v>
       </c>
       <c r="I15" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J15" t="n">
-        <v>-10.61</v>
+        <v>-3.24</v>
       </c>
       <c r="K15" t="n">
-        <v>-25.01</v>
+        <v>-30.73</v>
       </c>
       <c r="L15" t="n">
-        <v>27.16</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>08:16:06</t>
+          <t>08:14:58</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -709,34 +709,34 @@
         <v>3</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1</v>
+        <v>1.54</v>
       </c>
       <c r="F16" t="n">
-        <v>2.17</v>
+        <v>1.84</v>
       </c>
       <c r="G16" t="n">
-        <v>211.5</v>
+        <v>195.5</v>
       </c>
       <c r="H16" t="n">
-        <v>66</v>
+        <v>58.5</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J16" t="n">
-        <v>-15.14</v>
+        <v>-2.49</v>
       </c>
       <c r="K16" t="n">
-        <v>-14.9</v>
+        <v>-31.08</v>
       </c>
       <c r="L16" t="n">
-        <v>21.24</v>
+        <v>31.17</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>08:21:33</t>
+          <t>08:19:59</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -751,34 +751,34 @@
         <v>1</v>
       </c>
       <c r="E17" t="n">
-        <v>1.64</v>
+        <v>1.24</v>
       </c>
       <c r="F17" t="n">
-        <v>3.87</v>
+        <v>2.54</v>
       </c>
       <c r="G17" t="n">
-        <v>203.9</v>
+        <v>208.7</v>
       </c>
       <c r="H17" t="n">
-        <v>55</v>
+        <v>50.9</v>
       </c>
       <c r="I17" t="n">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-34.67</v>
+        <v>-14.55</v>
       </c>
       <c r="K17" t="n">
-        <v>-16.91</v>
+        <v>-32.89</v>
       </c>
       <c r="L17" t="n">
-        <v>38.57</v>
+        <v>35.96</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>08:23:06</t>
+          <t>08:22:14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -793,34 +793,34 @@
         <v>2</v>
       </c>
       <c r="E18" t="n">
-        <v>1.63</v>
+        <v>1.43</v>
       </c>
       <c r="F18" t="n">
-        <v>4.94</v>
+        <v>4.35</v>
       </c>
       <c r="G18" t="n">
-        <v>219.6</v>
+        <v>202.4</v>
       </c>
       <c r="H18" t="n">
-        <v>75.5</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J18" t="n">
-        <v>-26.97</v>
+        <v>-26.83</v>
       </c>
       <c r="K18" t="n">
-        <v>-34.77</v>
+        <v>44.25</v>
       </c>
       <c r="L18" t="n">
-        <v>44</v>
+        <v>51.74</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>08:25:13</t>
+          <t>08:23:46</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -835,34 +835,34 @@
         <v>3</v>
       </c>
       <c r="E19" t="n">
-        <v>1.29</v>
+        <v>1.58</v>
       </c>
       <c r="F19" t="n">
-        <v>3.81</v>
+        <v>2.54</v>
       </c>
       <c r="G19" t="n">
-        <v>204.8</v>
+        <v>200.6</v>
       </c>
       <c r="H19" t="n">
-        <v>46.1</v>
+        <v>55.9</v>
       </c>
       <c r="I19" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J19" t="n">
-        <v>27.07</v>
+        <v>29.17</v>
       </c>
       <c r="K19" t="n">
-        <v>27.65</v>
+        <v>-17.07</v>
       </c>
       <c r="L19" t="n">
-        <v>38.69</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>08:30:13</t>
+          <t>08:27:52</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -877,34 +877,34 @@
         <v>1</v>
       </c>
       <c r="E20" t="n">
-        <v>1.37</v>
+        <v>1.31</v>
       </c>
       <c r="F20" t="n">
-        <v>1.8</v>
+        <v>4.94</v>
       </c>
       <c r="G20" t="n">
-        <v>203.9</v>
+        <v>197.8</v>
       </c>
       <c r="H20" t="n">
-        <v>81.3</v>
+        <v>28.3</v>
       </c>
       <c r="I20" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J20" t="n">
-        <v>-64.06</v>
+        <v>36.78</v>
       </c>
       <c r="K20" t="n">
-        <v>-18.55</v>
+        <v>58.39</v>
       </c>
       <c r="L20" t="n">
-        <v>66.69</v>
+        <v>69.01000000000001</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>08:31:32</t>
+          <t>08:29:58</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -919,34 +919,34 @@
         <v>2</v>
       </c>
       <c r="E21" t="n">
-        <v>1.42</v>
+        <v>1.24</v>
       </c>
       <c r="F21" t="n">
-        <v>3.77</v>
+        <v>2.15</v>
       </c>
       <c r="G21" t="n">
-        <v>211.1</v>
+        <v>199.4</v>
       </c>
       <c r="H21" t="n">
-        <v>27.7</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I21" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="J21" t="n">
-        <v>75.43000000000001</v>
+        <v>30.48</v>
       </c>
       <c r="K21" t="n">
-        <v>-7.19</v>
+        <v>-42.99</v>
       </c>
       <c r="L21" t="n">
-        <v>75.78</v>
+        <v>52.69</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>08:33:08</t>
+          <t>08:30:49</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -961,34 +961,34 @@
         <v>3</v>
       </c>
       <c r="E22" t="n">
-        <v>1.5</v>
+        <v>1.18</v>
       </c>
       <c r="F22" t="n">
-        <v>4.24</v>
+        <v>4.94</v>
       </c>
       <c r="G22" t="n">
-        <v>203.2</v>
+        <v>196.4</v>
       </c>
       <c r="H22" t="n">
-        <v>38.4</v>
+        <v>50.8</v>
       </c>
       <c r="I22" t="n">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="J22" t="n">
-        <v>-22.06</v>
+        <v>18.28</v>
       </c>
       <c r="K22" t="n">
-        <v>-33.96</v>
+        <v>65.91</v>
       </c>
       <c r="L22" t="n">
-        <v>40.49</v>
+        <v>68.40000000000001</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>08:38:22</t>
+          <t>08:35:30</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1003,34 +1003,34 @@
         <v>1</v>
       </c>
       <c r="E23" t="n">
-        <v>1.61</v>
+        <v>1.3</v>
       </c>
       <c r="F23" t="n">
-        <v>1.91</v>
+        <v>1.6</v>
       </c>
       <c r="G23" t="n">
-        <v>207.2</v>
+        <v>198.2</v>
       </c>
       <c r="H23" t="n">
-        <v>42.2</v>
+        <v>88.8</v>
       </c>
       <c r="I23" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J23" t="n">
-        <v>-79.34</v>
+        <v>-68.14</v>
       </c>
       <c r="K23" t="n">
-        <v>-62.63</v>
+        <v>-74.48</v>
       </c>
       <c r="L23" t="n">
-        <v>101.08</v>
+        <v>100.95</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>08:39:34</t>
+          <t>08:37:36</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1045,34 +1045,34 @@
         <v>2</v>
       </c>
       <c r="E24" t="n">
-        <v>1.49</v>
+        <v>1.38</v>
       </c>
       <c r="F24" t="n">
         <v>4.94</v>
       </c>
       <c r="G24" t="n">
-        <v>197.8</v>
+        <v>196.1</v>
       </c>
       <c r="H24" t="n">
-        <v>56.4</v>
+        <v>37.7</v>
       </c>
       <c r="I24" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="J24" t="n">
-        <v>-13.61</v>
+        <v>-22.22</v>
       </c>
       <c r="K24" t="n">
-        <v>-85.68000000000001</v>
+        <v>-104.41</v>
       </c>
       <c r="L24" t="n">
-        <v>86.76000000000001</v>
+        <v>106.75</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>08:41:27</t>
+          <t>08:39:11</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1087,34 +1087,34 @@
         <v>3</v>
       </c>
       <c r="E25" t="n">
-        <v>1.28</v>
+        <v>1.46</v>
       </c>
       <c r="F25" t="n">
-        <v>1.58</v>
+        <v>4.37</v>
       </c>
       <c r="G25" t="n">
-        <v>198.5</v>
+        <v>209.2</v>
       </c>
       <c r="H25" t="n">
-        <v>46.2</v>
+        <v>37.7</v>
       </c>
       <c r="I25" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="J25" t="n">
-        <v>-46.48</v>
+        <v>64.52</v>
       </c>
       <c r="K25" t="n">
-        <v>-87.72</v>
+        <v>-37.06</v>
       </c>
       <c r="L25" t="n">
-        <v>99.27</v>
+        <v>74.41</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>08:45:31</t>
+          <t>08:42:29</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1129,34 +1129,34 @@
         <v>1</v>
       </c>
       <c r="E26" t="n">
-        <v>1.32</v>
+        <v>1.52</v>
       </c>
       <c r="F26" t="n">
-        <v>4.94</v>
+        <v>2.03</v>
       </c>
       <c r="G26" t="n">
-        <v>203.5</v>
+        <v>224.7</v>
       </c>
       <c r="H26" t="n">
-        <v>43.6</v>
+        <v>87.2</v>
       </c>
       <c r="I26" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J26" t="n">
-        <v>-35.17</v>
+        <v>137.61</v>
       </c>
       <c r="K26" t="n">
-        <v>139.88</v>
+        <v>-5.81</v>
       </c>
       <c r="L26" t="n">
-        <v>144.24</v>
+        <v>137.73</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>08:47:14</t>
+          <t>08:44:17</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1171,34 +1171,34 @@
         <v>2</v>
       </c>
       <c r="E27" t="n">
-        <v>1.61</v>
+        <v>1.64</v>
       </c>
       <c r="F27" t="n">
         <v>4.94</v>
       </c>
       <c r="G27" t="n">
-        <v>210.7</v>
+        <v>226.6</v>
       </c>
       <c r="H27" t="n">
-        <v>29.6</v>
+        <v>76.40000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="J27" t="n">
-        <v>11.02</v>
+        <v>99.15000000000001</v>
       </c>
       <c r="K27" t="n">
-        <v>-133.97</v>
+        <v>124.91</v>
       </c>
       <c r="L27" t="n">
-        <v>134.42</v>
+        <v>159.48</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>08:47:59</t>
+          <t>08:46:07</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1213,34 +1213,34 @@
         <v>3</v>
       </c>
       <c r="E28" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="F28" t="n">
         <v>4.94</v>
       </c>
       <c r="G28" t="n">
-        <v>217.8</v>
+        <v>203</v>
       </c>
       <c r="H28" t="n">
-        <v>52.5</v>
+        <v>66.90000000000001</v>
       </c>
       <c r="I28" t="n">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="J28" t="n">
-        <v>-167.46</v>
+        <v>132.3</v>
       </c>
       <c r="K28" t="n">
-        <v>-48.07</v>
+        <v>45.43</v>
       </c>
       <c r="L28" t="n">
-        <v>174.22</v>
+        <v>139.88</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>09:00:19</t>
+          <t>08:57:14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1261,28 +1261,28 @@
         <v>4.94</v>
       </c>
       <c r="G29" t="n">
-        <v>208</v>
+        <v>208.8</v>
       </c>
       <c r="H29" t="n">
-        <v>31.8</v>
+        <v>21.4</v>
       </c>
       <c r="I29" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J29" t="n">
-        <v>0.12</v>
+        <v>-31.08</v>
       </c>
       <c r="K29" t="n">
-        <v>28.62</v>
+        <v>-6.29</v>
       </c>
       <c r="L29" t="n">
-        <v>28.62</v>
+        <v>31.71</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>09:01:31</t>
+          <t>08:58:46</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1297,34 +1297,34 @@
         <v>2</v>
       </c>
       <c r="E30" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="F30" t="n">
-        <v>4.13</v>
+        <v>4.84</v>
       </c>
       <c r="G30" t="n">
-        <v>198.6</v>
+        <v>219.1</v>
       </c>
       <c r="H30" t="n">
-        <v>50.2</v>
+        <v>71</v>
       </c>
       <c r="I30" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="J30" t="n">
-        <v>26.42</v>
+        <v>13.56</v>
       </c>
       <c r="K30" t="n">
-        <v>4.69</v>
+        <v>-25.57</v>
       </c>
       <c r="L30" t="n">
-        <v>26.84</v>
+        <v>28.94</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>09:02:31</t>
+          <t>09:00:09</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1339,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="E31" t="n">
-        <v>1.49</v>
+        <v>1.43</v>
       </c>
       <c r="F31" t="n">
-        <v>4.32</v>
+        <v>4.94</v>
       </c>
       <c r="G31" t="n">
-        <v>212.5</v>
+        <v>204.3</v>
       </c>
       <c r="H31" t="n">
-        <v>45.2</v>
+        <v>34.3</v>
       </c>
       <c r="I31" t="n">
         <v>25</v>
       </c>
       <c r="J31" t="n">
-        <v>17.99</v>
+        <v>-20.94</v>
       </c>
       <c r="K31" t="n">
-        <v>-24.06</v>
+        <v>17.67</v>
       </c>
       <c r="L31" t="n">
-        <v>30.04</v>
+        <v>27.4</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>09:07:32</t>
+          <t>09:05:34</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1381,34 +1381,34 @@
         <v>1</v>
       </c>
       <c r="E32" t="n">
-        <v>1.41</v>
+        <v>1.56</v>
       </c>
       <c r="F32" t="n">
         <v>4.94</v>
       </c>
       <c r="G32" t="n">
-        <v>214.2</v>
+        <v>205.2</v>
       </c>
       <c r="H32" t="n">
-        <v>42.2</v>
+        <v>19.1</v>
       </c>
       <c r="I32" t="n">
-        <v>19</v>
+        <v>29</v>
       </c>
       <c r="J32" t="n">
-        <v>-29.34</v>
+        <v>46.68</v>
       </c>
       <c r="K32" t="n">
-        <v>-30.18</v>
+        <v>-13.84</v>
       </c>
       <c r="L32" t="n">
-        <v>42.09</v>
+        <v>48.69</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>09:10:04</t>
+          <t>09:07:07</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1426,31 +1426,31 @@
         <v>1.49</v>
       </c>
       <c r="F33" t="n">
-        <v>3.57</v>
+        <v>2.12</v>
       </c>
       <c r="G33" t="n">
-        <v>212.2</v>
+        <v>218.7</v>
       </c>
       <c r="H33" t="n">
-        <v>39.1</v>
+        <v>57.4</v>
       </c>
       <c r="I33" t="n">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>20</v>
+        <v>-48.97</v>
       </c>
       <c r="K33" t="n">
-        <v>-35.64</v>
+        <v>-14.33</v>
       </c>
       <c r="L33" t="n">
-        <v>40.87</v>
+        <v>51.03</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>09:10:54</t>
+          <t>09:09:11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1465,34 +1465,34 @@
         <v>3</v>
       </c>
       <c r="E34" t="n">
-        <v>1.39</v>
+        <v>1.75</v>
       </c>
       <c r="F34" t="n">
-        <v>4.94</v>
+        <v>3.81</v>
       </c>
       <c r="G34" t="n">
-        <v>196.1</v>
+        <v>223.5</v>
       </c>
       <c r="H34" t="n">
-        <v>40.4</v>
+        <v>50.5</v>
       </c>
       <c r="I34" t="n">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J34" t="n">
-        <v>1.75</v>
+        <v>-48.56</v>
       </c>
       <c r="K34" t="n">
-        <v>-35.03</v>
+        <v>-7.27</v>
       </c>
       <c r="L34" t="n">
-        <v>35.08</v>
+        <v>49.1</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>09:13:48</t>
+          <t>09:15:10</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1507,34 +1507,34 @@
         <v>1</v>
       </c>
       <c r="E35" t="n">
-        <v>1.44</v>
+        <v>1.57</v>
       </c>
       <c r="F35" t="n">
-        <v>4.94</v>
+        <v>4.05</v>
       </c>
       <c r="G35" t="n">
-        <v>216.2</v>
+        <v>201.7</v>
       </c>
       <c r="H35" t="n">
-        <v>91.8</v>
+        <v>100</v>
       </c>
       <c r="I35" t="n">
         <v>23</v>
       </c>
       <c r="J35" t="n">
-        <v>-39.03</v>
+        <v>35.95</v>
       </c>
       <c r="K35" t="n">
-        <v>-77.8</v>
+        <v>-56.5</v>
       </c>
       <c r="L35" t="n">
-        <v>87.04000000000001</v>
+        <v>66.95999999999999</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>09:15:00</t>
+          <t>09:16:55</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1549,34 +1549,34 @@
         <v>2</v>
       </c>
       <c r="E36" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="F36" t="n">
-        <v>4.94</v>
+        <v>4.32</v>
       </c>
       <c r="G36" t="n">
-        <v>215.8</v>
+        <v>210.1</v>
       </c>
       <c r="H36" t="n">
-        <v>61.3</v>
+        <v>31.2</v>
       </c>
       <c r="I36" t="n">
         <v>30</v>
       </c>
       <c r="J36" t="n">
-        <v>49.81</v>
+        <v>-36.85</v>
       </c>
       <c r="K36" t="n">
-        <v>25.47</v>
+        <v>-64.06</v>
       </c>
       <c r="L36" t="n">
-        <v>55.94</v>
+        <v>73.90000000000001</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>09:17:01</t>
+          <t>09:17:55</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1591,34 +1591,34 @@
         <v>3</v>
       </c>
       <c r="E37" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="F37" t="n">
-        <v>4.52</v>
+        <v>4.89</v>
       </c>
       <c r="G37" t="n">
-        <v>210.9</v>
+        <v>202.4</v>
       </c>
       <c r="H37" t="n">
-        <v>66.09999999999999</v>
+        <v>69.3</v>
       </c>
       <c r="I37" t="n">
-        <v>21</v>
+        <v>26</v>
       </c>
       <c r="J37" t="n">
-        <v>29.31</v>
+        <v>66.98</v>
       </c>
       <c r="K37" t="n">
-        <v>-66.14</v>
+        <v>-0.19</v>
       </c>
       <c r="L37" t="n">
-        <v>72.34</v>
+        <v>66.98</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>09:22:26</t>
+          <t>09:21:19</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1633,34 +1633,34 @@
         <v>1</v>
       </c>
       <c r="E38" t="n">
-        <v>1.63</v>
+        <v>1.22</v>
       </c>
       <c r="F38" t="n">
-        <v>4.49</v>
+        <v>1.76</v>
       </c>
       <c r="G38" t="n">
-        <v>200.9</v>
+        <v>217.8</v>
       </c>
       <c r="H38" t="n">
-        <v>75.3</v>
+        <v>45.8</v>
       </c>
       <c r="I38" t="n">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="J38" t="n">
-        <v>-93.23999999999999</v>
+        <v>-29.63</v>
       </c>
       <c r="K38" t="n">
-        <v>-35.26</v>
+        <v>-98.98</v>
       </c>
       <c r="L38" t="n">
-        <v>99.68000000000001</v>
+        <v>103.32</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>09:24:41</t>
+          <t>09:23:29</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1675,34 +1675,34 @@
         <v>2</v>
       </c>
       <c r="E39" t="n">
-        <v>1.5</v>
+        <v>1.6</v>
       </c>
       <c r="F39" t="n">
-        <v>3.43</v>
+        <v>4.94</v>
       </c>
       <c r="G39" t="n">
-        <v>208.2</v>
+        <v>220.1</v>
       </c>
       <c r="H39" t="n">
-        <v>11.1</v>
+        <v>70.59999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J39" t="n">
-        <v>60.97</v>
+        <v>86.41</v>
       </c>
       <c r="K39" t="n">
-        <v>-52.55</v>
+        <v>59.49</v>
       </c>
       <c r="L39" t="n">
-        <v>80.48999999999999</v>
+        <v>104.91</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>09:26:01</t>
+          <t>09:24:18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1717,34 +1717,34 @@
         <v>3</v>
       </c>
       <c r="E40" t="n">
-        <v>1.35</v>
+        <v>1.59</v>
       </c>
       <c r="F40" t="n">
-        <v>2.6</v>
+        <v>4.94</v>
       </c>
       <c r="G40" t="n">
-        <v>212.9</v>
+        <v>203.9</v>
       </c>
       <c r="H40" t="n">
-        <v>18.5</v>
+        <v>55</v>
       </c>
       <c r="I40" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J40" t="n">
-        <v>81.65000000000001</v>
+        <v>-89.70999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>31.94</v>
+        <v>-33.23</v>
       </c>
       <c r="L40" t="n">
-        <v>87.68000000000001</v>
+        <v>95.67</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>09:30:02</t>
+          <t>09:28:55</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1759,34 +1759,34 @@
         <v>1</v>
       </c>
       <c r="E41" t="n">
-        <v>1.62</v>
+        <v>1.77</v>
       </c>
       <c r="F41" t="n">
-        <v>2.43</v>
+        <v>4.94</v>
       </c>
       <c r="G41" t="n">
-        <v>200.8</v>
+        <v>223.2</v>
       </c>
       <c r="H41" t="n">
-        <v>27.5</v>
+        <v>86.40000000000001</v>
       </c>
       <c r="I41" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="J41" t="n">
-        <v>-43.75</v>
+        <v>-55.06</v>
       </c>
       <c r="K41" t="n">
-        <v>-74.31</v>
+        <v>-136.99</v>
       </c>
       <c r="L41" t="n">
-        <v>86.23</v>
+        <v>147.64</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>09:32:28</t>
+          <t>09:31:35</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1801,34 +1801,34 @@
         <v>2</v>
       </c>
       <c r="E42" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="F42" t="n">
         <v>4.94</v>
       </c>
       <c r="G42" t="n">
-        <v>206</v>
+        <v>204.8</v>
       </c>
       <c r="H42" t="n">
-        <v>29.5</v>
+        <v>46.1</v>
       </c>
       <c r="I42" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J42" t="n">
-        <v>-94.56999999999999</v>
+        <v>90.81999999999999</v>
       </c>
       <c r="K42" t="n">
-        <v>-95.91</v>
+        <v>99.52</v>
       </c>
       <c r="L42" t="n">
-        <v>134.7</v>
+        <v>134.74</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>09:33:17</t>
+          <t>09:33:26</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1843,34 +1843,34 @@
         <v>3</v>
       </c>
       <c r="E43" t="n">
-        <v>1.88</v>
+        <v>1.51</v>
       </c>
       <c r="F43" t="n">
-        <v>4.94</v>
+        <v>2.47</v>
       </c>
       <c r="G43" t="n">
-        <v>194.7</v>
+        <v>213.1</v>
       </c>
       <c r="H43" t="n">
-        <v>51.3</v>
+        <v>47.1</v>
       </c>
       <c r="I43" t="n">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="J43" t="n">
-        <v>-66.7</v>
+        <v>135.67</v>
       </c>
       <c r="K43" t="n">
-        <v>-85.91</v>
+        <v>108.73</v>
       </c>
       <c r="L43" t="n">
-        <v>108.76</v>
+        <v>173.86</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>09:44:31</t>
+          <t>09:45:22</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -1885,34 +1885,34 @@
         <v>1</v>
       </c>
       <c r="E44" t="n">
-        <v>1.86</v>
+        <v>1.43</v>
       </c>
       <c r="F44" t="n">
-        <v>4.94</v>
+        <v>3.99</v>
       </c>
       <c r="G44" t="n">
-        <v>205</v>
+        <v>211.1</v>
       </c>
       <c r="H44" t="n">
-        <v>56</v>
+        <v>27.7</v>
       </c>
       <c r="I44" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="J44" t="n">
-        <v>1.72</v>
+        <v>33.73</v>
       </c>
       <c r="K44" t="n">
-        <v>-44.45</v>
+        <v>0.47</v>
       </c>
       <c r="L44" t="n">
-        <v>44.48</v>
+        <v>33.74</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>09:46:35</t>
+          <t>09:47:43</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -1927,34 +1927,34 @@
         <v>2</v>
       </c>
       <c r="E45" t="n">
-        <v>1.57</v>
+        <v>1.65</v>
       </c>
       <c r="F45" t="n">
-        <v>4.46</v>
+        <v>4.94</v>
       </c>
       <c r="G45" t="n">
-        <v>194</v>
+        <v>212.1</v>
       </c>
       <c r="H45" t="n">
-        <v>31.5</v>
+        <v>45.3</v>
       </c>
       <c r="I45" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J45" t="n">
-        <v>18.89</v>
+        <v>27.02</v>
       </c>
       <c r="K45" t="n">
-        <v>-25.93</v>
+        <v>-17.54</v>
       </c>
       <c r="L45" t="n">
-        <v>32.09</v>
+        <v>32.21</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>09:48:19</t>
+          <t>09:49:35</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -1969,34 +1969,34 @@
         <v>3</v>
       </c>
       <c r="E46" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="F46" t="n">
-        <v>3.72</v>
+        <v>3.79</v>
       </c>
       <c r="G46" t="n">
-        <v>207.7</v>
+        <v>207.2</v>
       </c>
       <c r="H46" t="n">
-        <v>73</v>
+        <v>42.2</v>
       </c>
       <c r="I46" t="n">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="J46" t="n">
-        <v>-5.48</v>
+        <v>-23.13</v>
       </c>
       <c r="K46" t="n">
-        <v>-29.52</v>
+        <v>-15.83</v>
       </c>
       <c r="L46" t="n">
-        <v>30.02</v>
+        <v>28.03</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>09:52:25</t>
+          <t>09:54:07</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2011,34 +2011,34 @@
         <v>1</v>
       </c>
       <c r="E47" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="F47" t="n">
-        <v>1.9</v>
+        <v>4.94</v>
       </c>
       <c r="G47" t="n">
-        <v>207.2</v>
+        <v>204.1</v>
       </c>
       <c r="H47" t="n">
-        <v>25.2</v>
+        <v>31.9</v>
       </c>
       <c r="I47" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J47" t="n">
-        <v>-10.82</v>
+        <v>45.27</v>
       </c>
       <c r="K47" t="n">
-        <v>-44.31</v>
+        <v>-12.71</v>
       </c>
       <c r="L47" t="n">
-        <v>45.61</v>
+        <v>47.03</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>09:54:31</t>
+          <t>09:56:21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2053,34 +2053,34 @@
         <v>2</v>
       </c>
       <c r="E48" t="n">
-        <v>1.7</v>
+        <v>1.54</v>
       </c>
       <c r="F48" t="n">
-        <v>4.35</v>
+        <v>3.86</v>
       </c>
       <c r="G48" t="n">
-        <v>217.9</v>
+        <v>207</v>
       </c>
       <c r="H48" t="n">
-        <v>31.8</v>
+        <v>33.8</v>
       </c>
       <c r="I48" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="J48" t="n">
-        <v>-10.79</v>
+        <v>-8.67</v>
       </c>
       <c r="K48" t="n">
-        <v>48.57</v>
+        <v>-48.86</v>
       </c>
       <c r="L48" t="n">
-        <v>49.76</v>
+        <v>49.62</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>09:55:16</t>
+          <t>09:57:46</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2095,34 +2095,34 @@
         <v>3</v>
       </c>
       <c r="E49" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="F49" t="n">
-        <v>4.94</v>
+        <v>4.04</v>
       </c>
       <c r="G49" t="n">
-        <v>216.4</v>
+        <v>192.7</v>
       </c>
       <c r="H49" t="n">
-        <v>60.8</v>
+        <v>57.6</v>
       </c>
       <c r="I49" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="J49" t="n">
-        <v>-41.82</v>
+        <v>0.12</v>
       </c>
       <c r="K49" t="n">
-        <v>19.11</v>
+        <v>42.25</v>
       </c>
       <c r="L49" t="n">
-        <v>45.98</v>
+        <v>42.25</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>10:00:32</t>
+          <t>10:02:28</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2137,34 +2137,34 @@
         <v>1</v>
       </c>
       <c r="E50" t="n">
-        <v>1.57</v>
+        <v>1.66</v>
       </c>
       <c r="F50" t="n">
-        <v>3.31</v>
+        <v>2.79</v>
       </c>
       <c r="G50" t="n">
-        <v>211.1</v>
+        <v>215.6</v>
       </c>
       <c r="H50" t="n">
-        <v>5.3</v>
+        <v>64.2</v>
       </c>
       <c r="I50" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="J50" t="n">
-        <v>8.289999999999999</v>
+        <v>-5.75</v>
       </c>
       <c r="K50" t="n">
-        <v>55.78</v>
+        <v>52.04</v>
       </c>
       <c r="L50" t="n">
-        <v>56.39</v>
+        <v>52.36</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>10:02:39</t>
+          <t>10:04:20</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2179,34 +2179,34 @@
         <v>2</v>
       </c>
       <c r="E51" t="n">
-        <v>1.47</v>
+        <v>1.28</v>
       </c>
       <c r="F51" t="n">
-        <v>1.79</v>
+        <v>3.65</v>
       </c>
       <c r="G51" t="n">
-        <v>208.8</v>
+        <v>214.2</v>
       </c>
       <c r="H51" t="n">
-        <v>56</v>
+        <v>69.90000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="J51" t="n">
-        <v>47.51</v>
+        <v>50.42</v>
       </c>
       <c r="K51" t="n">
-        <v>-48.06</v>
+        <v>44.05</v>
       </c>
       <c r="L51" t="n">
-        <v>67.58</v>
+        <v>66.95</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>10:03:33</t>
+          <t>10:06:40</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2221,34 +2221,34 @@
         <v>3</v>
       </c>
       <c r="E52" t="n">
-        <v>2.4</v>
+        <v>1.72</v>
       </c>
       <c r="F52" t="n">
-        <v>4.94</v>
+        <v>3.19</v>
       </c>
       <c r="G52" t="n">
-        <v>215.8</v>
+        <v>200.6</v>
       </c>
       <c r="H52" t="n">
-        <v>46.4</v>
+        <v>57.4</v>
       </c>
       <c r="I52" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J52" t="n">
-        <v>-88.76000000000001</v>
+        <v>23.44</v>
       </c>
       <c r="K52" t="n">
-        <v>-4.97</v>
+        <v>71.79000000000001</v>
       </c>
       <c r="L52" t="n">
-        <v>88.90000000000001</v>
+        <v>75.52</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>10:07:14</t>
+          <t>10:10:59</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2263,34 +2263,34 @@
         <v>1</v>
       </c>
       <c r="E53" t="n">
-        <v>1.43</v>
+        <v>1.58</v>
       </c>
       <c r="F53" t="n">
-        <v>4.94</v>
+        <v>2.96</v>
       </c>
       <c r="G53" t="n">
-        <v>217.2</v>
+        <v>209.1</v>
       </c>
       <c r="H53" t="n">
-        <v>67.90000000000001</v>
+        <v>24.6</v>
       </c>
       <c r="I53" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>33.47</v>
+        <v>-58.62</v>
       </c>
       <c r="K53" t="n">
-        <v>-96.23</v>
+        <v>78.18000000000001</v>
       </c>
       <c r="L53" t="n">
-        <v>101.89</v>
+        <v>97.72</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>10:09:03</t>
+          <t>10:12:54</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -2305,34 +2305,34 @@
         <v>2</v>
       </c>
       <c r="E54" t="n">
-        <v>1.35</v>
+        <v>1.57</v>
       </c>
       <c r="F54" t="n">
-        <v>4.3</v>
+        <v>4.94</v>
       </c>
       <c r="G54" t="n">
-        <v>213.7</v>
+        <v>206.8</v>
       </c>
       <c r="H54" t="n">
-        <v>27.4</v>
+        <v>52.4</v>
       </c>
       <c r="I54" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J54" t="n">
-        <v>-18.24</v>
+        <v>-4.93</v>
       </c>
       <c r="K54" t="n">
-        <v>-93.12</v>
+        <v>-102.3</v>
       </c>
       <c r="L54" t="n">
-        <v>94.89</v>
+        <v>102.42</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>10:10:14</t>
+          <t>10:13:52</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2347,34 +2347,34 @@
         <v>3</v>
       </c>
       <c r="E55" t="n">
-        <v>1.65</v>
+        <v>1.73</v>
       </c>
       <c r="F55" t="n">
-        <v>2.48</v>
+        <v>4.94</v>
       </c>
       <c r="G55" t="n">
-        <v>215.3</v>
+        <v>211.6</v>
       </c>
       <c r="H55" t="n">
-        <v>58.4</v>
+        <v>83.8</v>
       </c>
       <c r="I55" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="J55" t="n">
-        <v>3.61</v>
+        <v>46.44</v>
       </c>
       <c r="K55" t="n">
-        <v>99.90000000000001</v>
+        <v>-75.55</v>
       </c>
       <c r="L55" t="n">
-        <v>99.97</v>
+        <v>88.68000000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>10:14:36</t>
+          <t>10:18:18</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2389,34 +2389,34 @@
         <v>1</v>
       </c>
       <c r="E56" t="n">
-        <v>1.32</v>
+        <v>1.42</v>
       </c>
       <c r="F56" t="n">
-        <v>1.62</v>
+        <v>4.94</v>
       </c>
       <c r="G56" t="n">
-        <v>201.9</v>
+        <v>206.1</v>
       </c>
       <c r="H56" t="n">
-        <v>38.9</v>
+        <v>66.5</v>
       </c>
       <c r="I56" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J56" t="n">
-        <v>10.89</v>
+        <v>-73.2</v>
       </c>
       <c r="K56" t="n">
-        <v>141.26</v>
+        <v>-175.93</v>
       </c>
       <c r="L56" t="n">
-        <v>141.68</v>
+        <v>190.55</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>10:15:59</t>
+          <t>10:20:38</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2431,34 +2431,34 @@
         <v>2</v>
       </c>
       <c r="E57" t="n">
-        <v>1.59</v>
+        <v>1.76</v>
       </c>
       <c r="F57" t="n">
-        <v>4.94</v>
+        <v>2.99</v>
       </c>
       <c r="G57" t="n">
-        <v>205.4</v>
+        <v>202</v>
       </c>
       <c r="H57" t="n">
-        <v>42.2</v>
+        <v>80.7</v>
       </c>
       <c r="I57" t="n">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="J57" t="n">
-        <v>41.2</v>
+        <v>-73.31</v>
       </c>
       <c r="K57" t="n">
-        <v>95.26000000000001</v>
+        <v>-119.12</v>
       </c>
       <c r="L57" t="n">
-        <v>103.78</v>
+        <v>139.87</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>10:17:57</t>
+          <t>10:23:01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -2473,34 +2473,34 @@
         <v>3</v>
       </c>
       <c r="E58" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="F58" t="n">
-        <v>4.57</v>
+        <v>4.94</v>
       </c>
       <c r="G58" t="n">
-        <v>205.9</v>
+        <v>199.6</v>
       </c>
       <c r="H58" t="n">
-        <v>65</v>
+        <v>60.4</v>
       </c>
       <c r="I58" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J58" t="n">
-        <v>147.21</v>
+        <v>-57.37</v>
       </c>
       <c r="K58" t="n">
-        <v>21.38</v>
+        <v>136.67</v>
       </c>
       <c r="L58" t="n">
-        <v>148.75</v>
+        <v>148.22</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>10:27:29</t>
+          <t>10:30:46</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2515,34 +2515,34 @@
         <v>1</v>
       </c>
       <c r="E59" t="n">
-        <v>1.49</v>
+        <v>1.75</v>
       </c>
       <c r="F59" t="n">
-        <v>2.71</v>
+        <v>3.68</v>
       </c>
       <c r="G59" t="n">
-        <v>216.1</v>
+        <v>201.8</v>
       </c>
       <c r="H59" t="n">
-        <v>46.2</v>
+        <v>55.7</v>
       </c>
       <c r="I59" t="n">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="J59" t="n">
-        <v>28.92</v>
+        <v>-11.59</v>
       </c>
       <c r="K59" t="n">
-        <v>17.52</v>
+        <v>-28.98</v>
       </c>
       <c r="L59" t="n">
-        <v>33.81</v>
+        <v>31.21</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>10:29:55</t>
+          <t>10:32:47</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -2557,34 +2557,34 @@
         <v>2</v>
       </c>
       <c r="E60" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="F60" t="n">
-        <v>4.94</v>
+        <v>2.96</v>
       </c>
       <c r="G60" t="n">
-        <v>214.4</v>
+        <v>221.4</v>
       </c>
       <c r="H60" t="n">
-        <v>54.9</v>
+        <v>80.5</v>
       </c>
       <c r="I60" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J60" t="n">
-        <v>-20.38</v>
+        <v>24.32</v>
       </c>
       <c r="K60" t="n">
-        <v>10.3</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="L60" t="n">
-        <v>22.84</v>
+        <v>26.21</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>10:31:28</t>
+          <t>10:34:24</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2599,34 +2599,34 @@
         <v>3</v>
       </c>
       <c r="E61" t="n">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="F61" t="n">
-        <v>3.81</v>
+        <v>3.54</v>
       </c>
       <c r="G61" t="n">
-        <v>206.2</v>
+        <v>208.3</v>
       </c>
       <c r="H61" t="n">
-        <v>43.2</v>
+        <v>63.2</v>
       </c>
       <c r="I61" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J61" t="n">
-        <v>-21.74</v>
+        <v>22.8</v>
       </c>
       <c r="K61" t="n">
-        <v>2.34</v>
+        <v>-4.28</v>
       </c>
       <c r="L61" t="n">
-        <v>21.86</v>
+        <v>23.2</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>10:36:50</t>
+          <t>10:37:55</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -2641,34 +2641,34 @@
         <v>1</v>
       </c>
       <c r="E62" t="n">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="F62" t="n">
-        <v>4.7</v>
+        <v>4.94</v>
       </c>
       <c r="G62" t="n">
-        <v>201.3</v>
+        <v>212</v>
       </c>
       <c r="H62" t="n">
-        <v>56.5</v>
+        <v>67.5</v>
       </c>
       <c r="I62" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J62" t="n">
-        <v>-17.09</v>
+        <v>7.92</v>
       </c>
       <c r="K62" t="n">
-        <v>-37.88</v>
+        <v>-45.43</v>
       </c>
       <c r="L62" t="n">
-        <v>41.56</v>
+        <v>46.12</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>10:38:20</t>
+          <t>10:38:44</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -2683,34 +2683,34 @@
         <v>2</v>
       </c>
       <c r="E63" t="n">
-        <v>1.69</v>
+        <v>1.5</v>
       </c>
       <c r="F63" t="n">
         <v>4.94</v>
       </c>
       <c r="G63" t="n">
-        <v>210.2</v>
+        <v>203.1</v>
       </c>
       <c r="H63" t="n">
-        <v>78.7</v>
+        <v>67.8</v>
       </c>
       <c r="I63" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="J63" t="n">
-        <v>-13.28</v>
+        <v>-55.12</v>
       </c>
       <c r="K63" t="n">
-        <v>-29.57</v>
+        <v>-9.33</v>
       </c>
       <c r="L63" t="n">
-        <v>32.41</v>
+        <v>55.91</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>10:40:09</t>
+          <t>10:39:49</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2725,34 +2725,34 @@
         <v>3</v>
       </c>
       <c r="E64" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="F64" t="n">
-        <v>4.94</v>
+        <v>3.6</v>
       </c>
       <c r="G64" t="n">
-        <v>189.6</v>
+        <v>199.2</v>
       </c>
       <c r="H64" t="n">
-        <v>72.40000000000001</v>
+        <v>95</v>
       </c>
       <c r="I64" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="J64" t="n">
-        <v>28.87</v>
+        <v>-51.97</v>
       </c>
       <c r="K64" t="n">
-        <v>31.4</v>
+        <v>0.26</v>
       </c>
       <c r="L64" t="n">
-        <v>42.66</v>
+        <v>51.97</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>10:44:33</t>
+          <t>10:44:40</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -2767,34 +2767,34 @@
         <v>1</v>
       </c>
       <c r="E65" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="F65" t="n">
-        <v>4.94</v>
+        <v>2.6</v>
       </c>
       <c r="G65" t="n">
-        <v>217.2</v>
+        <v>201.6</v>
       </c>
       <c r="H65" t="n">
-        <v>62.8</v>
+        <v>61.8</v>
       </c>
       <c r="I65" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J65" t="n">
-        <v>79.78</v>
+        <v>26.42</v>
       </c>
       <c r="K65" t="n">
-        <v>-31.83</v>
+        <v>71.06999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>85.90000000000001</v>
+        <v>75.83</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>10:45:51</t>
+          <t>10:46:45</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -2809,34 +2809,34 @@
         <v>2</v>
       </c>
       <c r="E66" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="F66" t="n">
-        <v>4.94</v>
+        <v>4.69</v>
       </c>
       <c r="G66" t="n">
-        <v>214.7</v>
+        <v>207</v>
       </c>
       <c r="H66" t="n">
-        <v>24.8</v>
+        <v>24.2</v>
       </c>
       <c r="I66" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J66" t="n">
-        <v>0.23</v>
+        <v>54.23</v>
       </c>
       <c r="K66" t="n">
-        <v>76.72</v>
+        <v>-26.78</v>
       </c>
       <c r="L66" t="n">
-        <v>76.72</v>
+        <v>60.49</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>10:47:42</t>
+          <t>10:48:25</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -2851,34 +2851,34 @@
         <v>3</v>
       </c>
       <c r="E67" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="F67" t="n">
-        <v>3.89</v>
+        <v>4.83</v>
       </c>
       <c r="G67" t="n">
-        <v>213.8</v>
+        <v>203.7</v>
       </c>
       <c r="H67" t="n">
-        <v>32.2</v>
+        <v>55</v>
       </c>
       <c r="I67" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="J67" t="n">
-        <v>27.78</v>
+        <v>39.79</v>
       </c>
       <c r="K67" t="n">
-        <v>-53.95</v>
+        <v>-50.71</v>
       </c>
       <c r="L67" t="n">
-        <v>60.68</v>
+        <v>64.45999999999999</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>10:52:58</t>
+          <t>10:51:52</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2893,34 +2893,34 @@
         <v>1</v>
       </c>
       <c r="E68" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="F68" t="n">
-        <v>4.94</v>
+        <v>2.96</v>
       </c>
       <c r="G68" t="n">
-        <v>195.4</v>
+        <v>210.4</v>
       </c>
       <c r="H68" t="n">
-        <v>44.7</v>
+        <v>22.5</v>
       </c>
       <c r="I68" t="n">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="J68" t="n">
-        <v>67.83</v>
+        <v>75.95</v>
       </c>
       <c r="K68" t="n">
-        <v>77.27</v>
+        <v>-59.09</v>
       </c>
       <c r="L68" t="n">
-        <v>102.81</v>
+        <v>96.23</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>10:54:56</t>
+          <t>10:52:52</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -2935,34 +2935,34 @@
         <v>2</v>
       </c>
       <c r="E69" t="n">
-        <v>1.49</v>
+        <v>2.26</v>
       </c>
       <c r="F69" t="n">
-        <v>4.39</v>
+        <v>4.94</v>
       </c>
       <c r="G69" t="n">
-        <v>209.9</v>
+        <v>205.2</v>
       </c>
       <c r="H69" t="n">
-        <v>42.8</v>
+        <v>71.90000000000001</v>
       </c>
       <c r="I69" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="J69" t="n">
-        <v>-71.18000000000001</v>
+        <v>-7.76</v>
       </c>
       <c r="K69" t="n">
-        <v>-44.04</v>
+        <v>171.82</v>
       </c>
       <c r="L69" t="n">
-        <v>83.7</v>
+        <v>171.99</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>10:57:07</t>
+          <t>10:55:23</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -2977,34 +2977,34 @@
         <v>3</v>
       </c>
       <c r="E70" t="n">
-        <v>1.49</v>
+        <v>1.63</v>
       </c>
       <c r="F70" t="n">
         <v>4.94</v>
       </c>
       <c r="G70" t="n">
-        <v>206.6</v>
+        <v>218.4</v>
       </c>
       <c r="H70" t="n">
-        <v>52.9</v>
+        <v>60.1</v>
       </c>
       <c r="I70" t="n">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="J70" t="n">
-        <v>-99.97</v>
+        <v>-64.73</v>
       </c>
       <c r="K70" t="n">
-        <v>-68.58</v>
+        <v>113.63</v>
       </c>
       <c r="L70" t="n">
-        <v>121.23</v>
+        <v>130.77</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>11:01:11</t>
+          <t>10:59:34</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3019,34 +3019,34 @@
         <v>1</v>
       </c>
       <c r="E71" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="F71" t="n">
-        <v>4</v>
+        <v>2.12</v>
       </c>
       <c r="G71" t="n">
-        <v>213.2</v>
+        <v>205</v>
       </c>
       <c r="H71" t="n">
-        <v>86.8</v>
+        <v>47.2</v>
       </c>
       <c r="I71" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J71" t="n">
-        <v>-163.28</v>
+        <v>188.6</v>
       </c>
       <c r="K71" t="n">
-        <v>65.91</v>
+        <v>122.33</v>
       </c>
       <c r="L71" t="n">
-        <v>176.08</v>
+        <v>224.8</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>11:02:25</t>
+          <t>11:02:01</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -3061,34 +3061,34 @@
         <v>2</v>
       </c>
       <c r="E72" t="n">
-        <v>1.58</v>
+        <v>1.8</v>
       </c>
       <c r="F72" t="n">
-        <v>3.88</v>
+        <v>4.94</v>
       </c>
       <c r="G72" t="n">
-        <v>198.4</v>
+        <v>208.4</v>
       </c>
       <c r="H72" t="n">
-        <v>42.7</v>
+        <v>67.09999999999999</v>
       </c>
       <c r="I72" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="J72" t="n">
-        <v>-107.87</v>
+        <v>146.62</v>
       </c>
       <c r="K72" t="n">
-        <v>-108.69</v>
+        <v>64.45</v>
       </c>
       <c r="L72" t="n">
-        <v>153.13</v>
+        <v>160.16</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>11:04:21</t>
+          <t>11:04:32</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -3103,34 +3103,34 @@
         <v>3</v>
       </c>
       <c r="E73" t="n">
-        <v>1.6</v>
+        <v>1.71</v>
       </c>
       <c r="F73" t="n">
         <v>4.94</v>
       </c>
       <c r="G73" t="n">
-        <v>215.4</v>
+        <v>207.4</v>
       </c>
       <c r="H73" t="n">
-        <v>56.2</v>
+        <v>64.7</v>
       </c>
       <c r="I73" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="J73" t="n">
-        <v>29.7</v>
+        <v>145.91</v>
       </c>
       <c r="K73" t="n">
-        <v>-133.27</v>
+        <v>21.67</v>
       </c>
       <c r="L73" t="n">
-        <v>136.54</v>
+        <v>147.51</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>11:13:57</t>
+          <t>11:16:33</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -3145,34 +3145,34 @@
         <v>1</v>
       </c>
       <c r="E74" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="F74" t="n">
-        <v>4.94</v>
+        <v>4.48</v>
       </c>
       <c r="G74" t="n">
-        <v>219.9</v>
+        <v>218.7</v>
       </c>
       <c r="H74" t="n">
-        <v>44.2</v>
+        <v>59.1</v>
       </c>
       <c r="I74" t="n">
-        <v>22</v>
+        <v>30</v>
       </c>
       <c r="J74" t="n">
-        <v>-17.84</v>
+        <v>-20.7</v>
       </c>
       <c r="K74" t="n">
-        <v>-12.72</v>
+        <v>-21.16</v>
       </c>
       <c r="L74" t="n">
-        <v>21.92</v>
+        <v>29.6</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>11:15:59</t>
+          <t>11:17:57</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3187,34 +3187,34 @@
         <v>2</v>
       </c>
       <c r="E75" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="F75" t="n">
-        <v>2.79</v>
+        <v>3.77</v>
       </c>
       <c r="G75" t="n">
-        <v>198.7</v>
+        <v>207.4</v>
       </c>
       <c r="H75" t="n">
-        <v>48.3</v>
+        <v>60.1</v>
       </c>
       <c r="I75" t="n">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>6.06</v>
+        <v>-13.78</v>
       </c>
       <c r="K75" t="n">
-        <v>19.74</v>
+        <v>22.86</v>
       </c>
       <c r="L75" t="n">
-        <v>20.65</v>
+        <v>26.69</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>11:18:10</t>
+          <t>11:19:41</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -3229,34 +3229,34 @@
         <v>3</v>
       </c>
       <c r="E76" t="n">
-        <v>1.81</v>
+        <v>1.74</v>
       </c>
       <c r="F76" t="n">
         <v>4.94</v>
       </c>
       <c r="G76" t="n">
-        <v>193.3</v>
+        <v>206.5</v>
       </c>
       <c r="H76" t="n">
-        <v>44.6</v>
+        <v>28.5</v>
       </c>
       <c r="I76" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J76" t="n">
-        <v>-31.87</v>
+        <v>-17.99</v>
       </c>
       <c r="K76" t="n">
-        <v>-10.79</v>
+        <v>28.45</v>
       </c>
       <c r="L76" t="n">
-        <v>33.65</v>
+        <v>33.66</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>11:22:35</t>
+          <t>11:24:26</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -3271,34 +3271,34 @@
         <v>1</v>
       </c>
       <c r="E77" t="n">
-        <v>1.57</v>
+        <v>1.46</v>
       </c>
       <c r="F77" t="n">
-        <v>4.94</v>
+        <v>4.48</v>
       </c>
       <c r="G77" t="n">
-        <v>213.7</v>
+        <v>205.1</v>
       </c>
       <c r="H77" t="n">
-        <v>54</v>
+        <v>44.6</v>
       </c>
       <c r="I77" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="J77" t="n">
-        <v>-33.91</v>
+        <v>19.15</v>
       </c>
       <c r="K77" t="n">
-        <v>-18.14</v>
+        <v>46.07</v>
       </c>
       <c r="L77" t="n">
-        <v>38.46</v>
+        <v>49.89</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>11:24:26</t>
+          <t>11:27:05</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3313,34 +3313,34 @@
         <v>2</v>
       </c>
       <c r="E78" t="n">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="F78" t="n">
-        <v>4.46</v>
+        <v>4.94</v>
       </c>
       <c r="G78" t="n">
-        <v>222.1</v>
+        <v>203.9</v>
       </c>
       <c r="H78" t="n">
-        <v>81.8</v>
+        <v>91.59999999999999</v>
       </c>
       <c r="I78" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="J78" t="n">
-        <v>-23.92</v>
+        <v>-27.54</v>
       </c>
       <c r="K78" t="n">
-        <v>12.66</v>
+        <v>-31.19</v>
       </c>
       <c r="L78" t="n">
-        <v>27.07</v>
+        <v>41.61</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>11:26:54</t>
+          <t>11:27:39</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3355,34 +3355,34 @@
         <v>3</v>
       </c>
       <c r="E79" t="n">
-        <v>1.6</v>
+        <v>1.54</v>
       </c>
       <c r="F79" t="n">
-        <v>2.8</v>
+        <v>4.94</v>
       </c>
       <c r="G79" t="n">
-        <v>217.6</v>
+        <v>203.1</v>
       </c>
       <c r="H79" t="n">
-        <v>10.4</v>
+        <v>56.2</v>
       </c>
       <c r="I79" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="J79" t="n">
-        <v>31.9</v>
+        <v>46.53</v>
       </c>
       <c r="K79" t="n">
-        <v>-7.4</v>
+        <v>-5.21</v>
       </c>
       <c r="L79" t="n">
-        <v>32.75</v>
+        <v>46.82</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>11:31:26</t>
+          <t>11:31:18</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3400,31 +3400,31 @@
         <v>1.5</v>
       </c>
       <c r="F80" t="n">
-        <v>2.83</v>
+        <v>4.4</v>
       </c>
       <c r="G80" t="n">
-        <v>186.3</v>
+        <v>211.8</v>
       </c>
       <c r="H80" t="n">
-        <v>48.6</v>
+        <v>44.7</v>
       </c>
       <c r="I80" t="n">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="J80" t="n">
-        <v>-61.06</v>
+        <v>61.29</v>
       </c>
       <c r="K80" t="n">
-        <v>-37.86</v>
+        <v>47.02</v>
       </c>
       <c r="L80" t="n">
-        <v>71.84999999999999</v>
+        <v>77.25</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>11:33:22</t>
+          <t>11:33:36</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3439,34 +3439,34 @@
         <v>2</v>
       </c>
       <c r="E81" t="n">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="F81" t="n">
         <v>4.94</v>
       </c>
       <c r="G81" t="n">
-        <v>211.5</v>
+        <v>201.1</v>
       </c>
       <c r="H81" t="n">
-        <v>39.7</v>
+        <v>62.1</v>
       </c>
       <c r="I81" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J81" t="n">
-        <v>-40.62</v>
+        <v>-23.06</v>
       </c>
       <c r="K81" t="n">
-        <v>51.26</v>
+        <v>-76.3</v>
       </c>
       <c r="L81" t="n">
-        <v>65.41</v>
+        <v>79.70999999999999</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>11:35:10</t>
+          <t>11:35:02</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3481,34 +3481,34 @@
         <v>3</v>
       </c>
       <c r="E82" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="F82" t="n">
         <v>4.94</v>
       </c>
       <c r="G82" t="n">
-        <v>208.9</v>
+        <v>201.6</v>
       </c>
       <c r="H82" t="n">
-        <v>54.4</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="I82" t="n">
-        <v>19</v>
+        <v>31</v>
       </c>
       <c r="J82" t="n">
-        <v>-45.08</v>
+        <v>-0.74</v>
       </c>
       <c r="K82" t="n">
-        <v>-42.7</v>
+        <v>-75.84999999999999</v>
       </c>
       <c r="L82" t="n">
-        <v>62.09</v>
+        <v>75.86</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>11:39:43</t>
+          <t>11:39:44</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3523,34 +3523,34 @@
         <v>1</v>
       </c>
       <c r="E83" t="n">
-        <v>1.66</v>
+        <v>2.09</v>
       </c>
       <c r="F83" t="n">
         <v>4.94</v>
       </c>
       <c r="G83" t="n">
-        <v>207.7</v>
+        <v>203.3</v>
       </c>
       <c r="H83" t="n">
-        <v>100</v>
+        <v>66.7</v>
       </c>
       <c r="I83" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="J83" t="n">
-        <v>-103.33</v>
+        <v>65.37</v>
       </c>
       <c r="K83" t="n">
-        <v>-41.39</v>
+        <v>-156.38</v>
       </c>
       <c r="L83" t="n">
-        <v>111.31</v>
+        <v>169.49</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>11:40:35</t>
+          <t>11:40:55</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3565,34 +3565,34 @@
         <v>2</v>
       </c>
       <c r="E84" t="n">
-        <v>1.66</v>
+        <v>1.56</v>
       </c>
       <c r="F84" t="n">
-        <v>1.96</v>
+        <v>4.94</v>
       </c>
       <c r="G84" t="n">
-        <v>201.9</v>
+        <v>201</v>
       </c>
       <c r="H84" t="n">
-        <v>48.2</v>
+        <v>42.5</v>
       </c>
       <c r="I84" t="n">
-        <v>30</v>
+        <v>22</v>
       </c>
       <c r="J84" t="n">
-        <v>-93.06</v>
+        <v>-40.55</v>
       </c>
       <c r="K84" t="n">
-        <v>-63.66</v>
+        <v>-107.54</v>
       </c>
       <c r="L84" t="n">
-        <v>112.75</v>
+        <v>114.93</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>11:42:51</t>
+          <t>11:43:28</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3607,34 +3607,34 @@
         <v>3</v>
       </c>
       <c r="E85" t="n">
-        <v>1.72</v>
+        <v>1.58</v>
       </c>
       <c r="F85" t="n">
-        <v>4.6</v>
+        <v>4.85</v>
       </c>
       <c r="G85" t="n">
-        <v>219.5</v>
+        <v>212</v>
       </c>
       <c r="H85" t="n">
-        <v>72.3</v>
+        <v>96.5</v>
       </c>
       <c r="I85" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="J85" t="n">
-        <v>63.59</v>
+        <v>-112.04</v>
       </c>
       <c r="K85" t="n">
-        <v>-93.70999999999999</v>
+        <v>-103.95</v>
       </c>
       <c r="L85" t="n">
-        <v>113.25</v>
+        <v>152.84</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>11:47:31</t>
+          <t>11:47:53</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3649,34 +3649,34 @@
         <v>1</v>
       </c>
       <c r="E86" t="n">
-        <v>1.53</v>
+        <v>1.6</v>
       </c>
       <c r="F86" t="n">
-        <v>3.38</v>
+        <v>4.52</v>
       </c>
       <c r="G86" t="n">
-        <v>230.7</v>
+        <v>212.5</v>
       </c>
       <c r="H86" t="n">
-        <v>49.8</v>
+        <v>69.2</v>
       </c>
       <c r="I86" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J86" t="n">
-        <v>33.82</v>
+        <v>-83.89</v>
       </c>
       <c r="K86" t="n">
-        <v>-112.33</v>
+        <v>147.84</v>
       </c>
       <c r="L86" t="n">
-        <v>117.31</v>
+        <v>169.99</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>11:49:04</t>
+          <t>11:49:06</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3691,34 +3691,34 @@
         <v>2</v>
       </c>
       <c r="E87" t="n">
-        <v>2.13</v>
+        <v>3.01</v>
       </c>
       <c r="F87" t="n">
-        <v>4.43</v>
+        <v>4.94</v>
       </c>
       <c r="G87" t="n">
-        <v>211.8</v>
+        <v>197.6</v>
       </c>
       <c r="H87" t="n">
-        <v>32.4</v>
+        <v>43.2</v>
       </c>
       <c r="I87" t="n">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="J87" t="n">
-        <v>64.17</v>
+        <v>-174.82</v>
       </c>
       <c r="K87" t="n">
-        <v>-85.94</v>
+        <v>140.4</v>
       </c>
       <c r="L87" t="n">
-        <v>107.25</v>
+        <v>224.22</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>11:50:49</t>
+          <t>11:51:03</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3733,28 +3733,28 @@
         <v>3</v>
       </c>
       <c r="E88" t="n">
-        <v>1.56</v>
+        <v>1.98</v>
       </c>
       <c r="F88" t="n">
-        <v>4.07</v>
+        <v>4.94</v>
       </c>
       <c r="G88" t="n">
-        <v>205.4</v>
+        <v>204.1</v>
       </c>
       <c r="H88" t="n">
-        <v>47.2</v>
+        <v>40.6</v>
       </c>
       <c r="I88" t="n">
         <v>21</v>
       </c>
       <c r="J88" t="n">
-        <v>104.5</v>
+        <v>-111.02</v>
       </c>
       <c r="K88" t="n">
-        <v>-23.99</v>
+        <v>71.88</v>
       </c>
       <c r="L88" t="n">
-        <v>107.21</v>
+        <v>132.26</v>
       </c>
     </row>
   </sheetData>

--- a/output/2024-10-27.xlsx
+++ b/output/2024-10-27.xlsx
@@ -640,13 +640,13 @@
         <v>28</v>
       </c>
       <c r="J14" t="n">
-        <v>-12.56</v>
+        <v>-12.79</v>
       </c>
       <c r="K14" t="n">
-        <v>44.73</v>
+        <v>45.54</v>
       </c>
       <c r="L14" t="n">
-        <v>46.46</v>
+        <v>47.31</v>
       </c>
     </row>
     <row r="15">
@@ -682,13 +682,13 @@
         <v>25</v>
       </c>
       <c r="J15" t="n">
-        <v>32.69</v>
+        <v>37.03</v>
       </c>
       <c r="K15" t="n">
-        <v>3.01</v>
+        <v>3.41</v>
       </c>
       <c r="L15" t="n">
-        <v>32.83</v>
+        <v>37.19</v>
       </c>
     </row>
     <row r="16">
@@ -724,13 +724,13 @@
         <v>25</v>
       </c>
       <c r="J16" t="n">
-        <v>2.93</v>
+        <v>3.11</v>
       </c>
       <c r="K16" t="n">
-        <v>39.01</v>
+        <v>41.53</v>
       </c>
       <c r="L16" t="n">
-        <v>39.12</v>
+        <v>41.65</v>
       </c>
     </row>
     <row r="17">
@@ -766,13 +766,13 @@
         <v>25</v>
       </c>
       <c r="J17" t="n">
-        <v>-40.6</v>
+        <v>-45.98</v>
       </c>
       <c r="K17" t="n">
-        <v>19.98</v>
+        <v>22.62</v>
       </c>
       <c r="L17" t="n">
-        <v>45.25</v>
+        <v>51.24</v>
       </c>
     </row>
     <row r="18">
@@ -808,13 +808,13 @@
         <v>26</v>
       </c>
       <c r="J18" t="n">
-        <v>-58.52</v>
+        <v>-60.36</v>
       </c>
       <c r="K18" t="n">
-        <v>27.45</v>
+        <v>28.32</v>
       </c>
       <c r="L18" t="n">
-        <v>64.64</v>
+        <v>66.67</v>
       </c>
     </row>
     <row r="19">
@@ -850,13 +850,13 @@
         <v>22</v>
       </c>
       <c r="J19" t="n">
-        <v>52.88</v>
+        <v>58.6</v>
       </c>
       <c r="K19" t="n">
-        <v>3.71</v>
+        <v>4.11</v>
       </c>
       <c r="L19" t="n">
-        <v>53.01</v>
+        <v>58.75</v>
       </c>
     </row>
     <row r="20">
@@ -892,13 +892,13 @@
         <v>23</v>
       </c>
       <c r="J20" t="n">
-        <v>49.96</v>
+        <v>56.92</v>
       </c>
       <c r="K20" t="n">
-        <v>73.59</v>
+        <v>83.84999999999999</v>
       </c>
       <c r="L20" t="n">
-        <v>88.95</v>
+        <v>101.35</v>
       </c>
     </row>
     <row r="21">
@@ -934,13 +934,13 @@
         <v>24</v>
       </c>
       <c r="J21" t="n">
-        <v>-71.51000000000001</v>
+        <v>-83.94</v>
       </c>
       <c r="K21" t="n">
-        <v>27.84</v>
+        <v>32.68</v>
       </c>
       <c r="L21" t="n">
-        <v>76.73999999999999</v>
+        <v>90.08</v>
       </c>
     </row>
     <row r="22">
@@ -976,13 +976,13 @@
         <v>22</v>
       </c>
       <c r="J22" t="n">
-        <v>-106.58</v>
+        <v>-116.97</v>
       </c>
       <c r="K22" t="n">
-        <v>14.88</v>
+        <v>16.32</v>
       </c>
       <c r="L22" t="n">
-        <v>107.62</v>
+        <v>118.1</v>
       </c>
     </row>
     <row r="23">
@@ -1018,13 +1018,13 @@
         <v>24</v>
       </c>
       <c r="J23" t="n">
-        <v>126.09</v>
+        <v>133.91</v>
       </c>
       <c r="K23" t="n">
-        <v>166.29</v>
+        <v>176.61</v>
       </c>
       <c r="L23" t="n">
-        <v>208.69</v>
+        <v>221.64</v>
       </c>
     </row>
     <row r="24">
@@ -1060,13 +1060,13 @@
         <v>27</v>
       </c>
       <c r="J24" t="n">
-        <v>46.81</v>
+        <v>57.65</v>
       </c>
       <c r="K24" t="n">
-        <v>-82.01000000000001</v>
+        <v>-101</v>
       </c>
       <c r="L24" t="n">
-        <v>94.43000000000001</v>
+        <v>116.3</v>
       </c>
     </row>
     <row r="25">
@@ -1102,13 +1102,13 @@
         <v>24</v>
       </c>
       <c r="J25" t="n">
-        <v>-98.27</v>
+        <v>-120.35</v>
       </c>
       <c r="K25" t="n">
-        <v>-37.46</v>
+        <v>-45.87</v>
       </c>
       <c r="L25" t="n">
-        <v>105.17</v>
+        <v>128.8</v>
       </c>
     </row>
     <row r="26">
@@ -1144,13 +1144,13 @@
         <v>24</v>
       </c>
       <c r="J26" t="n">
-        <v>222.7</v>
+        <v>251.54</v>
       </c>
       <c r="K26" t="n">
-        <v>69.06999999999999</v>
+        <v>78.01000000000001</v>
       </c>
       <c r="L26" t="n">
-        <v>233.16</v>
+        <v>263.36</v>
       </c>
     </row>
     <row r="27">
@@ -1186,13 +1186,13 @@
         <v>26</v>
       </c>
       <c r="J27" t="n">
-        <v>-150.04</v>
+        <v>-176</v>
       </c>
       <c r="K27" t="n">
-        <v>-103.05</v>
+        <v>-120.89</v>
       </c>
       <c r="L27" t="n">
-        <v>182.02</v>
+        <v>213.52</v>
       </c>
     </row>
     <row r="28">
@@ -1228,13 +1228,13 @@
         <v>23</v>
       </c>
       <c r="J28" t="n">
-        <v>130.22</v>
+        <v>170.29</v>
       </c>
       <c r="K28" t="n">
-        <v>48.26</v>
+        <v>63.11</v>
       </c>
       <c r="L28" t="n">
-        <v>138.87</v>
+        <v>181.61</v>
       </c>
     </row>
     <row r="29">
@@ -1270,13 +1270,13 @@
         <v>26</v>
       </c>
       <c r="J29" t="n">
-        <v>30.49</v>
+        <v>32.44</v>
       </c>
       <c r="K29" t="n">
-        <v>40.41</v>
+        <v>42.98</v>
       </c>
       <c r="L29" t="n">
-        <v>50.62</v>
+        <v>53.85</v>
       </c>
     </row>
     <row r="30">
@@ -1312,13 +1312,13 @@
         <v>26</v>
       </c>
       <c r="J30" t="n">
-        <v>-16.86</v>
+        <v>-17.23</v>
       </c>
       <c r="K30" t="n">
-        <v>41.54</v>
+        <v>42.46</v>
       </c>
       <c r="L30" t="n">
-        <v>44.83</v>
+        <v>45.82</v>
       </c>
     </row>
     <row r="31">
@@ -1354,13 +1354,13 @@
         <v>28</v>
       </c>
       <c r="J31" t="n">
-        <v>-30.78</v>
+        <v>-34.64</v>
       </c>
       <c r="K31" t="n">
-        <v>1.38</v>
+        <v>1.55</v>
       </c>
       <c r="L31" t="n">
-        <v>30.81</v>
+        <v>34.68</v>
       </c>
     </row>
     <row r="32">
@@ -1396,13 +1396,13 @@
         <v>22</v>
       </c>
       <c r="J32" t="n">
-        <v>-32.23</v>
+        <v>-37.27</v>
       </c>
       <c r="K32" t="n">
-        <v>-32.53</v>
+        <v>-37.61</v>
       </c>
       <c r="L32" t="n">
-        <v>45.79</v>
+        <v>52.95</v>
       </c>
     </row>
     <row r="33">
@@ -1438,13 +1438,13 @@
         <v>27</v>
       </c>
       <c r="J33" t="n">
-        <v>56.63</v>
+        <v>59.35</v>
       </c>
       <c r="K33" t="n">
-        <v>28.41</v>
+        <v>29.78</v>
       </c>
       <c r="L33" t="n">
-        <v>63.36</v>
+        <v>66.40000000000001</v>
       </c>
     </row>
     <row r="34">
@@ -1480,13 +1480,13 @@
         <v>23</v>
       </c>
       <c r="J34" t="n">
-        <v>-75.01000000000001</v>
+        <v>-80.81999999999999</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.19</v>
+        <v>-0.21</v>
       </c>
       <c r="L34" t="n">
-        <v>75.01000000000001</v>
+        <v>80.81999999999999</v>
       </c>
     </row>
     <row r="35">
@@ -1522,13 +1522,13 @@
         <v>27</v>
       </c>
       <c r="J35" t="n">
-        <v>-23.8</v>
+        <v>-25.81</v>
       </c>
       <c r="K35" t="n">
-        <v>99.34999999999999</v>
+        <v>107.72</v>
       </c>
       <c r="L35" t="n">
-        <v>102.16</v>
+        <v>110.77</v>
       </c>
     </row>
     <row r="36">
@@ -1564,13 +1564,13 @@
         <v>25</v>
       </c>
       <c r="J36" t="n">
-        <v>-79</v>
+        <v>-89.73</v>
       </c>
       <c r="K36" t="n">
-        <v>-16.49</v>
+        <v>-18.73</v>
       </c>
       <c r="L36" t="n">
-        <v>80.7</v>
+        <v>91.66</v>
       </c>
     </row>
     <row r="37">
@@ -1606,13 +1606,13 @@
         <v>27</v>
       </c>
       <c r="J37" t="n">
-        <v>16.8</v>
+        <v>20.29</v>
       </c>
       <c r="K37" t="n">
-        <v>-58.61</v>
+        <v>-70.78</v>
       </c>
       <c r="L37" t="n">
-        <v>60.97</v>
+        <v>73.63</v>
       </c>
     </row>
     <row r="38">
@@ -1648,13 +1648,13 @@
         <v>26</v>
       </c>
       <c r="J38" t="n">
-        <v>-84.20999999999999</v>
+        <v>-101.11</v>
       </c>
       <c r="K38" t="n">
-        <v>-62.23</v>
+        <v>-74.72</v>
       </c>
       <c r="L38" t="n">
-        <v>104.71</v>
+        <v>125.73</v>
       </c>
     </row>
     <row r="39">
@@ -1690,13 +1690,13 @@
         <v>22</v>
       </c>
       <c r="J39" t="n">
-        <v>-100.59</v>
+        <v>-125.94</v>
       </c>
       <c r="K39" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="L39" t="n">
-        <v>100.59</v>
+        <v>125.94</v>
       </c>
     </row>
     <row r="40">
@@ -1732,13 +1732,13 @@
         <v>22</v>
       </c>
       <c r="J40" t="n">
-        <v>-56.45</v>
+        <v>-71.95999999999999</v>
       </c>
       <c r="K40" t="n">
-        <v>-68.2</v>
+        <v>-86.94</v>
       </c>
       <c r="L40" t="n">
-        <v>88.53</v>
+        <v>112.86</v>
       </c>
     </row>
     <row r="41">
@@ -1774,13 +1774,13 @@
         <v>28</v>
       </c>
       <c r="J41" t="n">
-        <v>143.99</v>
+        <v>177.15</v>
       </c>
       <c r="K41" t="n">
-        <v>-29.43</v>
+        <v>-36.21</v>
       </c>
       <c r="L41" t="n">
-        <v>146.97</v>
+        <v>180.81</v>
       </c>
     </row>
     <row r="42">
@@ -1816,13 +1816,13 @@
         <v>28</v>
       </c>
       <c r="J42" t="n">
-        <v>-179.98</v>
+        <v>-204.71</v>
       </c>
       <c r="K42" t="n">
-        <v>-51.34</v>
+        <v>-58.39</v>
       </c>
       <c r="L42" t="n">
-        <v>187.16</v>
+        <v>212.87</v>
       </c>
     </row>
     <row r="43">
@@ -1858,13 +1858,13 @@
         <v>24</v>
       </c>
       <c r="J43" t="n">
-        <v>-57.2</v>
+        <v>-73.91</v>
       </c>
       <c r="K43" t="n">
-        <v>121.89</v>
+        <v>157.51</v>
       </c>
       <c r="L43" t="n">
-        <v>134.64</v>
+        <v>173.99</v>
       </c>
     </row>
     <row r="44">
@@ -1900,13 +1900,13 @@
         <v>25</v>
       </c>
       <c r="J44" t="n">
-        <v>29.99</v>
+        <v>31.36</v>
       </c>
       <c r="K44" t="n">
-        <v>-38.75</v>
+        <v>-40.52</v>
       </c>
       <c r="L44" t="n">
-        <v>49</v>
+        <v>51.24</v>
       </c>
     </row>
     <row r="45">
@@ -1942,13 +1942,13 @@
         <v>23</v>
       </c>
       <c r="J45" t="n">
-        <v>35.19</v>
+        <v>38.8</v>
       </c>
       <c r="K45" t="n">
-        <v>30.74</v>
+        <v>33.9</v>
       </c>
       <c r="L45" t="n">
-        <v>46.73</v>
+        <v>51.52</v>
       </c>
     </row>
     <row r="46">
@@ -1984,13 +1984,13 @@
         <v>23</v>
       </c>
       <c r="J46" t="n">
-        <v>8.42</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="K46" t="n">
-        <v>-61.92</v>
+        <v>-61.65</v>
       </c>
       <c r="L46" t="n">
-        <v>62.49</v>
+        <v>62.21</v>
       </c>
     </row>
     <row r="47">
@@ -2026,13 +2026,13 @@
         <v>28</v>
       </c>
       <c r="J47" t="n">
-        <v>-6.22</v>
+        <v>-6.53</v>
       </c>
       <c r="K47" t="n">
-        <v>-58.6</v>
+        <v>-61.5</v>
       </c>
       <c r="L47" t="n">
-        <v>58.93</v>
+        <v>61.84</v>
       </c>
     </row>
     <row r="48">
@@ -2068,13 +2068,13 @@
         <v>24</v>
       </c>
       <c r="J48" t="n">
-        <v>43</v>
+        <v>48.63</v>
       </c>
       <c r="K48" t="n">
-        <v>-23.1</v>
+        <v>-26.12</v>
       </c>
       <c r="L48" t="n">
-        <v>48.81</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="49">
@@ -2110,13 +2110,13 @@
         <v>27</v>
       </c>
       <c r="J49" t="n">
-        <v>-57.64</v>
+        <v>-61.86</v>
       </c>
       <c r="K49" t="n">
-        <v>-18.28</v>
+        <v>-19.62</v>
       </c>
       <c r="L49" t="n">
-        <v>60.47</v>
+        <v>64.90000000000001</v>
       </c>
     </row>
     <row r="50">
@@ -2152,13 +2152,13 @@
         <v>25</v>
       </c>
       <c r="J50" t="n">
-        <v>22.69</v>
+        <v>25.8</v>
       </c>
       <c r="K50" t="n">
-        <v>-84.31</v>
+        <v>-95.83</v>
       </c>
       <c r="L50" t="n">
-        <v>87.31</v>
+        <v>99.23999999999999</v>
       </c>
     </row>
     <row r="51">
@@ -2194,13 +2194,13 @@
         <v>27</v>
       </c>
       <c r="J51" t="n">
-        <v>124.93</v>
+        <v>130.71</v>
       </c>
       <c r="K51" t="n">
-        <v>-12.59</v>
+        <v>-13.17</v>
       </c>
       <c r="L51" t="n">
-        <v>125.56</v>
+        <v>131.37</v>
       </c>
     </row>
     <row r="52">
@@ -2236,13 +2236,13 @@
         <v>24</v>
       </c>
       <c r="J52" t="n">
-        <v>29.9</v>
+        <v>36.13</v>
       </c>
       <c r="K52" t="n">
-        <v>-77.36</v>
+        <v>-93.45999999999999</v>
       </c>
       <c r="L52" t="n">
-        <v>82.94</v>
+        <v>100.2</v>
       </c>
     </row>
     <row r="53">
@@ -2278,13 +2278,13 @@
         <v>25</v>
       </c>
       <c r="J53" t="n">
-        <v>48.93</v>
+        <v>56.43</v>
       </c>
       <c r="K53" t="n">
-        <v>-118.88</v>
+        <v>-137.12</v>
       </c>
       <c r="L53" t="n">
-        <v>128.56</v>
+        <v>148.28</v>
       </c>
     </row>
     <row r="54">
@@ -2320,13 +2320,13 @@
         <v>23</v>
       </c>
       <c r="J54" t="n">
-        <v>-120.94</v>
+        <v>-143.22</v>
       </c>
       <c r="K54" t="n">
-        <v>-14.2</v>
+        <v>-16.81</v>
       </c>
       <c r="L54" t="n">
-        <v>121.77</v>
+        <v>144.2</v>
       </c>
     </row>
     <row r="55">
@@ -2362,13 +2362,13 @@
         <v>25</v>
       </c>
       <c r="J55" t="n">
-        <v>70.41</v>
+        <v>77.25</v>
       </c>
       <c r="K55" t="n">
-        <v>150.45</v>
+        <v>165.07</v>
       </c>
       <c r="L55" t="n">
-        <v>166.11</v>
+        <v>182.25</v>
       </c>
     </row>
     <row r="56">
@@ -2404,13 +2404,13 @@
         <v>26</v>
       </c>
       <c r="J56" t="n">
-        <v>221.4</v>
+        <v>252.1</v>
       </c>
       <c r="K56" t="n">
-        <v>21.55</v>
+        <v>24.53</v>
       </c>
       <c r="L56" t="n">
-        <v>222.45</v>
+        <v>253.29</v>
       </c>
     </row>
     <row r="57">
@@ -2446,13 +2446,13 @@
         <v>22</v>
       </c>
       <c r="J57" t="n">
-        <v>57.12</v>
+        <v>73.56999999999999</v>
       </c>
       <c r="K57" t="n">
-        <v>-135.46</v>
+        <v>-174.47</v>
       </c>
       <c r="L57" t="n">
-        <v>147.01</v>
+        <v>189.34</v>
       </c>
     </row>
     <row r="58">
@@ -2488,13 +2488,13 @@
         <v>26</v>
       </c>
       <c r="J58" t="n">
-        <v>-63.26</v>
+        <v>-80.5</v>
       </c>
       <c r="K58" t="n">
-        <v>-123.72</v>
+        <v>-157.43</v>
       </c>
       <c r="L58" t="n">
-        <v>138.95</v>
+        <v>176.82</v>
       </c>
     </row>
     <row r="59">
@@ -2530,13 +2530,13 @@
         <v>27</v>
       </c>
       <c r="J59" t="n">
-        <v>-10.04</v>
+        <v>-11.36</v>
       </c>
       <c r="K59" t="n">
-        <v>-32.11</v>
+        <v>-36.32</v>
       </c>
       <c r="L59" t="n">
-        <v>33.65</v>
+        <v>38.05</v>
       </c>
     </row>
     <row r="60">
@@ -2572,13 +2572,13 @@
         <v>28</v>
       </c>
       <c r="J60" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="K60" t="n">
-        <v>44.5</v>
+        <v>45.81</v>
       </c>
       <c r="L60" t="n">
-        <v>44.53</v>
+        <v>45.83</v>
       </c>
     </row>
     <row r="61">
@@ -2614,13 +2614,13 @@
         <v>26</v>
       </c>
       <c r="J61" t="n">
-        <v>26.62</v>
+        <v>27.09</v>
       </c>
       <c r="K61" t="n">
-        <v>41.37</v>
+        <v>42.09</v>
       </c>
       <c r="L61" t="n">
-        <v>49.19</v>
+        <v>50.06</v>
       </c>
     </row>
     <row r="62">
@@ -2656,13 +2656,13 @@
         <v>28</v>
       </c>
       <c r="J62" t="n">
-        <v>47.14</v>
+        <v>51.08</v>
       </c>
       <c r="K62" t="n">
-        <v>20.93</v>
+        <v>22.68</v>
       </c>
       <c r="L62" t="n">
-        <v>51.58</v>
+        <v>55.89</v>
       </c>
     </row>
     <row r="63">
@@ -2698,13 +2698,13 @@
         <v>24</v>
       </c>
       <c r="J63" t="n">
-        <v>33.61</v>
+        <v>36.09</v>
       </c>
       <c r="K63" t="n">
-        <v>-54.36</v>
+        <v>-58.37</v>
       </c>
       <c r="L63" t="n">
-        <v>63.91</v>
+        <v>68.62</v>
       </c>
     </row>
     <row r="64">
@@ -2740,13 +2740,13 @@
         <v>26</v>
       </c>
       <c r="J64" t="n">
-        <v>40.09</v>
+        <v>44.15</v>
       </c>
       <c r="K64" t="n">
-        <v>30.64</v>
+        <v>33.74</v>
       </c>
       <c r="L64" t="n">
-        <v>50.46</v>
+        <v>55.57</v>
       </c>
     </row>
     <row r="65">
@@ -2782,13 +2782,13 @@
         <v>24</v>
       </c>
       <c r="J65" t="n">
-        <v>48.63</v>
+        <v>52.8</v>
       </c>
       <c r="K65" t="n">
-        <v>-90.73999999999999</v>
+        <v>-98.52</v>
       </c>
       <c r="L65" t="n">
-        <v>102.95</v>
+        <v>111.77</v>
       </c>
     </row>
     <row r="66">
@@ -2824,13 +2824,13 @@
         <v>26</v>
       </c>
       <c r="J66" t="n">
-        <v>-46.82</v>
+        <v>-49.83</v>
       </c>
       <c r="K66" t="n">
-        <v>87.22</v>
+        <v>92.84</v>
       </c>
       <c r="L66" t="n">
-        <v>98.98999999999999</v>
+        <v>105.36</v>
       </c>
     </row>
     <row r="67">
@@ -2866,13 +2866,13 @@
         <v>25</v>
       </c>
       <c r="J67" t="n">
-        <v>40.81</v>
+        <v>46.62</v>
       </c>
       <c r="K67" t="n">
-        <v>-72.81999999999999</v>
+        <v>-83.18000000000001</v>
       </c>
       <c r="L67" t="n">
-        <v>83.48</v>
+        <v>95.34999999999999</v>
       </c>
     </row>
     <row r="68">
@@ -2908,13 +2908,13 @@
         <v>26</v>
       </c>
       <c r="J68" t="n">
-        <v>-54.73</v>
+        <v>-63.7</v>
       </c>
       <c r="K68" t="n">
-        <v>-107.33</v>
+        <v>-124.92</v>
       </c>
       <c r="L68" t="n">
-        <v>120.48</v>
+        <v>140.23</v>
       </c>
     </row>
     <row r="69">
@@ -2950,13 +2950,13 @@
         <v>27</v>
       </c>
       <c r="J69" t="n">
-        <v>44.79</v>
+        <v>57.27</v>
       </c>
       <c r="K69" t="n">
-        <v>-69</v>
+        <v>-88.23999999999999</v>
       </c>
       <c r="L69" t="n">
-        <v>82.26000000000001</v>
+        <v>105.19</v>
       </c>
     </row>
     <row r="70">
@@ -2992,13 +2992,13 @@
         <v>22</v>
       </c>
       <c r="J70" t="n">
-        <v>-86.08</v>
+        <v>-112.95</v>
       </c>
       <c r="K70" t="n">
-        <v>-3.97</v>
+        <v>-5.21</v>
       </c>
       <c r="L70" t="n">
-        <v>86.17</v>
+        <v>113.07</v>
       </c>
     </row>
     <row r="71">
@@ -3034,13 +3034,13 @@
         <v>28</v>
       </c>
       <c r="J71" t="n">
-        <v>199.6</v>
+        <v>234.45</v>
       </c>
       <c r="K71" t="n">
-        <v>-46.07</v>
+        <v>-54.11</v>
       </c>
       <c r="L71" t="n">
-        <v>204.84</v>
+        <v>240.61</v>
       </c>
     </row>
     <row r="72">
@@ -3076,13 +3076,13 @@
         <v>26</v>
       </c>
       <c r="J72" t="n">
-        <v>2.1</v>
+        <v>2.78</v>
       </c>
       <c r="K72" t="n">
-        <v>-119.71</v>
+        <v>-158.48</v>
       </c>
       <c r="L72" t="n">
-        <v>119.73</v>
+        <v>158.51</v>
       </c>
     </row>
     <row r="73">
@@ -3118,13 +3118,13 @@
         <v>25</v>
       </c>
       <c r="J73" t="n">
-        <v>115.45</v>
+        <v>156.54</v>
       </c>
       <c r="K73" t="n">
-        <v>26.42</v>
+        <v>35.82</v>
       </c>
       <c r="L73" t="n">
-        <v>118.44</v>
+        <v>160.58</v>
       </c>
     </row>
     <row r="74">
@@ -3160,13 +3160,13 @@
         <v>26</v>
       </c>
       <c r="J74" t="n">
-        <v>37.43</v>
+        <v>40.69</v>
       </c>
       <c r="K74" t="n">
-        <v>17.5</v>
+        <v>19.02</v>
       </c>
       <c r="L74" t="n">
-        <v>41.32</v>
+        <v>44.92</v>
       </c>
     </row>
     <row r="75">
@@ -3202,13 +3202,13 @@
         <v>24</v>
       </c>
       <c r="J75" t="n">
-        <v>-37.12</v>
+        <v>-36.59</v>
       </c>
       <c r="K75" t="n">
-        <v>50.5</v>
+        <v>49.78</v>
       </c>
       <c r="L75" t="n">
-        <v>62.68</v>
+        <v>61.78</v>
       </c>
     </row>
     <row r="76">
@@ -3244,13 +3244,13 @@
         <v>24</v>
       </c>
       <c r="J76" t="n">
-        <v>-43.15</v>
+        <v>-46.5</v>
       </c>
       <c r="K76" t="n">
-        <v>-12.57</v>
+        <v>-13.54</v>
       </c>
       <c r="L76" t="n">
-        <v>44.94</v>
+        <v>48.43</v>
       </c>
     </row>
     <row r="77">
@@ -3286,13 +3286,13 @@
         <v>28</v>
       </c>
       <c r="J77" t="n">
-        <v>-50.25</v>
+        <v>-55.41</v>
       </c>
       <c r="K77" t="n">
-        <v>-18.79</v>
+        <v>-20.72</v>
       </c>
       <c r="L77" t="n">
-        <v>53.65</v>
+        <v>59.15</v>
       </c>
     </row>
     <row r="78">
@@ -3328,13 +3328,13 @@
         <v>26</v>
       </c>
       <c r="J78" t="n">
-        <v>-36.01</v>
+        <v>-41.49</v>
       </c>
       <c r="K78" t="n">
-        <v>-26.52</v>
+        <v>-30.56</v>
       </c>
       <c r="L78" t="n">
-        <v>44.72</v>
+        <v>51.53</v>
       </c>
     </row>
     <row r="79">
@@ -3370,13 +3370,13 @@
         <v>24</v>
       </c>
       <c r="J79" t="n">
-        <v>25.66</v>
+        <v>29.46</v>
       </c>
       <c r="K79" t="n">
-        <v>41.76</v>
+        <v>47.94</v>
       </c>
       <c r="L79" t="n">
-        <v>49.02</v>
+        <v>56.26</v>
       </c>
     </row>
     <row r="80">
@@ -3412,13 +3412,13 @@
         <v>27</v>
       </c>
       <c r="J80" t="n">
-        <v>-75.34</v>
+        <v>-86.31</v>
       </c>
       <c r="K80" t="n">
-        <v>19.56</v>
+        <v>22.4</v>
       </c>
       <c r="L80" t="n">
-        <v>77.84</v>
+        <v>89.17</v>
       </c>
     </row>
     <row r="81">
@@ -3454,13 +3454,13 @@
         <v>24</v>
       </c>
       <c r="J81" t="n">
-        <v>27.24</v>
+        <v>31.3</v>
       </c>
       <c r="K81" t="n">
-        <v>-83.92</v>
+        <v>-96.43000000000001</v>
       </c>
       <c r="L81" t="n">
-        <v>88.23</v>
+        <v>101.38</v>
       </c>
     </row>
     <row r="82">
@@ -3496,13 +3496,13 @@
         <v>26</v>
       </c>
       <c r="J82" t="n">
-        <v>-23.66</v>
+        <v>-24.02</v>
       </c>
       <c r="K82" t="n">
-        <v>134.49</v>
+        <v>136.57</v>
       </c>
       <c r="L82" t="n">
-        <v>136.55</v>
+        <v>138.66</v>
       </c>
     </row>
     <row r="83">
@@ -3538,13 +3538,13 @@
         <v>24</v>
       </c>
       <c r="J83" t="n">
-        <v>80.11</v>
+        <v>92</v>
       </c>
       <c r="K83" t="n">
-        <v>-112.76</v>
+        <v>-129.49</v>
       </c>
       <c r="L83" t="n">
-        <v>138.32</v>
+        <v>158.85</v>
       </c>
     </row>
     <row r="84">
@@ -3580,13 +3580,13 @@
         <v>28</v>
       </c>
       <c r="J84" t="n">
-        <v>-122.31</v>
+        <v>-139.08</v>
       </c>
       <c r="K84" t="n">
-        <v>-43.33</v>
+        <v>-49.27</v>
       </c>
       <c r="L84" t="n">
-        <v>129.76</v>
+        <v>147.54</v>
       </c>
     </row>
     <row r="85">
@@ -3622,13 +3622,13 @@
         <v>26</v>
       </c>
       <c r="J85" t="n">
-        <v>-90.09999999999999</v>
+        <v>-111.33</v>
       </c>
       <c r="K85" t="n">
-        <v>40.42</v>
+        <v>49.94</v>
       </c>
       <c r="L85" t="n">
-        <v>98.75</v>
+        <v>122.01</v>
       </c>
     </row>
     <row r="86">
@@ -3664,13 +3664,13 @@
         <v>25</v>
       </c>
       <c r="J86" t="n">
-        <v>3.43</v>
+        <v>4.01</v>
       </c>
       <c r="K86" t="n">
-        <v>-199.81</v>
+        <v>-233.83</v>
       </c>
       <c r="L86" t="n">
-        <v>199.84</v>
+        <v>233.87</v>
       </c>
     </row>
     <row r="87">
@@ -3706,13 +3706,13 @@
         <v>22</v>
       </c>
       <c r="J87" t="n">
-        <v>139.78</v>
+        <v>171.56</v>
       </c>
       <c r="K87" t="n">
-        <v>-113.92</v>
+        <v>-139.82</v>
       </c>
       <c r="L87" t="n">
-        <v>180.32</v>
+        <v>221.32</v>
       </c>
     </row>
     <row r="88">
@@ -3748,13 +3748,13 @@
         <v>22</v>
       </c>
       <c r="J88" t="n">
-        <v>-31.17</v>
+        <v>-36.04</v>
       </c>
       <c r="K88" t="n">
-        <v>245.56</v>
+        <v>283.92</v>
       </c>
       <c r="L88" t="n">
-        <v>247.53</v>
+        <v>286.2</v>
       </c>
     </row>
   </sheetData>
